--- a/utilities/calibration/workbook_templates/04_CoordinatedDailyActivityPattern_2023_blank.xlsx
+++ b/utilities/calibration/workbook_templates/04_CoordinatedDailyActivityPattern_2023_blank.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\travel-model-one\utilities\calibration\workbook_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{224AA7D1-6253-4440-8332-3EA899DB7DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7C2DFD-A6F2-4D6B-8497-E54DE804CF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration" sheetId="1" r:id="rId1"/>
     <sheet name="modeldata" sheetId="2" r:id="rId2"/>
     <sheet name="BATS 2023" sheetId="3" r:id="rId3"/>
-    <sheet name="TM1 v03 Targets" sheetId="6" r:id="rId4"/>
+    <sheet name="TM1 v03 Targets" sheetId="6" state="hidden" r:id="rId4"/>
     <sheet name="PersonType Chart" sheetId="5" r:id="rId5"/>
   </sheets>
   <externalReferences>
@@ -31,7 +31,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="6" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -53,6 +53,30 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Melody Tsao</author>
+  </authors>
+  <commentList>
+    <comment ref="D18" authorId="0" shapeId="0" xr:uid="{1D46B84C-B797-4451-A092-8EBD1927B57D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">CHTS Targets from 1.5.2 Calibration Workbook
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>PBS&amp;J Employee</author>
@@ -111,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="50">
   <si>
     <t>H</t>
   </si>
@@ -259,6 +283,9 @@
   <si>
     <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20260821_NoMon_rmo/ctramp_2023/BATS_Summaries/dap_summaries.csv</t>
   </si>
+  <si>
+    <t>**BATS 2023 was under-reporting mandatory tours for students under 18, most likely due to proxy reporting. As a result, we will not be using BATS CDAP share for students under 18 and keep the targets from the previous calibration (CHTS)</t>
+  </si>
 </sst>
 </file>
 
@@ -270,7 +297,7 @@
     <numFmt numFmtId="166" formatCode="0.0000;[Red]\-0.0000"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -379,6 +406,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -501,7 +540,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -597,15 +636,16 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1980,7 +2020,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8668550" cy="6291303"/>
+    <xdr:ext cx="8677362" cy="6300482"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -2293,7 +2333,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{425DF6BC-449A-4A16-B9F3-1C22AC562EC2}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{425DF6BC-449A-4A16-B9F3-1C22AC562EC2}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="I5:M15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -5648,19 +5688,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="B1:M77"/>
+  <dimension ref="B1:M79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
     <col min="8" max="8" width="24.140625" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
     <col min="15" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10" bestFit="1" customWidth="1"/>
   </cols>
@@ -6011,7 +6052,7 @@
       <c r="C16" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="74">
         <v>5095.9923076611367</v>
       </c>
     </row>
@@ -6022,174 +6063,172 @@
       <c r="C17" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="74">
         <v>562978.37455945229</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18">
+      <c r="B18" s="70">
         <v>6</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="70" t="s">
         <v>0</v>
       </c>
       <c r="D18" s="2">
+        <v>17630.20679</v>
+      </c>
+      <c r="E18" s="2">
         <v>41115.091661171064</v>
       </c>
-      <c r="E18" s="2"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19">
+      <c r="B19" s="70">
         <v>6</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="70" t="s">
         <v>1</v>
       </c>
       <c r="D19" s="2">
+        <v>123094.58867</v>
+      </c>
+      <c r="E19" s="2">
         <v>32780.663158173164</v>
       </c>
-      <c r="E19" s="2"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20">
+      <c r="B20" s="70">
         <v>6</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="70" t="s">
         <v>2</v>
       </c>
       <c r="D20" s="2">
+        <v>17712.811699999998</v>
+      </c>
+      <c r="E20" s="2">
         <v>41918.179611378931</v>
       </c>
-      <c r="E20" s="2"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21">
+      <c r="B21" s="70">
         <v>7</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="70" t="s">
         <v>0</v>
       </c>
       <c r="D21" s="2">
+        <v>85466.730259999997</v>
+      </c>
+      <c r="E21" s="2">
         <v>247900.7678317161</v>
       </c>
-      <c r="E21" s="2"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22">
+      <c r="B22" s="70">
         <v>7</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="70" t="s">
         <v>1</v>
       </c>
       <c r="D22" s="2">
+        <v>665066.56470999995</v>
+      </c>
+      <c r="E22" s="2">
         <v>140853.46659383521</v>
       </c>
-      <c r="E22" s="2"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23">
+      <c r="B23" s="70">
         <v>7</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="70" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="2">
+        <v>64858.529419999999</v>
+      </c>
+      <c r="E23" s="2">
         <v>140850.42326779067</v>
       </c>
-      <c r="E23" s="2"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24">
+      <c r="B24" s="70">
         <v>8</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="70" t="s">
         <v>0</v>
       </c>
       <c r="D24" s="2">
+        <v>121625.49533999999</v>
+      </c>
+      <c r="E24" s="2">
         <v>157345.89475843927</v>
       </c>
-      <c r="E24" s="2"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="70">
         <v>8</v>
       </c>
-      <c r="C25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25">
+      <c r="C25" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2">
+        <v>138048.92214000001</v>
+      </c>
+      <c r="E25" s="70">
         <v>64377.458058831013</v>
       </c>
-      <c r="E25" s="2"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B26">
+      <c r="B26" s="70">
         <v>8</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
+        <v>145623.69245999999</v>
+      </c>
+      <c r="E26" s="70">
         <v>39919.065974013021</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="70" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>20972.980538993601</v>
-      </c>
-      <c r="E30">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>101791.443381039</v>
-      </c>
-      <c r="E31">
-        <v>410</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.25">
@@ -6197,41 +6236,41 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>56525.7782478925</v>
+        <v>20972.980538993601</v>
       </c>
       <c r="E32">
-        <v>265</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>9363.2104923139996</v>
+        <v>101791.443381039</v>
       </c>
       <c r="E33">
-        <v>31</v>
+        <v>410</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
         <v>2</v>
       </c>
-      <c r="C34" t="s">
-        <v>1</v>
-      </c>
       <c r="D34">
-        <v>29187.200693063402</v>
+        <v>56525.7782478925</v>
       </c>
       <c r="E34">
-        <v>58</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
@@ -6239,41 +6278,41 @@
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>28107.324162689001</v>
+        <v>9363.2104923139996</v>
       </c>
       <c r="E35">
-        <v>84</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>2587.17097574738</v>
+        <v>29187.200693063402</v>
       </c>
       <c r="E36">
-        <v>8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37">
-        <v>5272.2016418558496</v>
+        <v>28107.324162689001</v>
       </c>
       <c r="E37">
-        <v>22</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
@@ -6281,97 +6320,97 @@
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>14187.895576548101</v>
+        <v>2587.17097574738</v>
       </c>
       <c r="E38">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>10909.387874141699</v>
+        <v>5272.2016418558496</v>
       </c>
       <c r="E39">
-        <v>55</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40" t="s">
         <v>2</v>
       </c>
       <c r="D40">
-        <v>38765.573310295011</v>
+        <v>14187.895576548101</v>
       </c>
       <c r="E40">
-        <v>140</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" t="s">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>34940.3033849606</v>
+        <v>10909.387874141699</v>
       </c>
       <c r="E41">
-        <v>110</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" t="s">
         <v>2</v>
       </c>
       <c r="D42">
-        <v>52565.235958389538</v>
+        <v>38765.573310295011</v>
       </c>
       <c r="E42">
-        <v>262</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" t="s">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>3795.8709036518198</v>
+        <v>34940.3033849606</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>6531.0686161737603</v>
+        <v>52565.235958389538</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.25">
@@ -6379,41 +6418,41 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>4233.5977867305201</v>
+        <v>3795.8709036518198</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>31643.1944620621</v>
+        <v>6531.0686161737603</v>
       </c>
       <c r="E46">
-        <v>38</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47">
-        <v>14117.8259404212</v>
+        <v>4233.5977867305201</v>
       </c>
       <c r="E47">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.25">
@@ -6421,41 +6460,41 @@
         <v>7</v>
       </c>
       <c r="C48" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>16081.6986499751</v>
+        <v>31643.1944620621</v>
       </c>
       <c r="E48">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C49" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>20577.984808375099</v>
+        <v>14117.8259404212</v>
       </c>
       <c r="E49">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50">
-        <v>8248.9312060110606</v>
+        <v>16081.6986499751</v>
       </c>
       <c r="E50">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.25">
@@ -6463,65 +6502,65 @@
         <v>8</v>
       </c>
       <c r="C51" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>20577.984808375099</v>
+      </c>
+      <c r="E51">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <v>8</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>8248.9312060110606</v>
+      </c>
+      <c r="E52">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
         <v>2</v>
       </c>
-      <c r="D51">
+      <c r="D53">
         <v>4558.7508507235698</v>
       </c>
-      <c r="E51">
+      <c r="E53">
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="1" t="s">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B56" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" t="s">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
         <v>40</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C57" t="s">
         <v>41</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D57" t="s">
         <v>42</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E57" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56">
-        <v>63549.153434615902</v>
-      </c>
-      <c r="E56">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B57">
-        <v>1</v>
-      </c>
-      <c r="C57" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57">
-        <v>210535.026176057</v>
-      </c>
-      <c r="E57">
-        <v>671</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.25">
@@ -6529,41 +6568,41 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>121351.542268502</v>
+        <v>63549.153434615902</v>
       </c>
       <c r="E58">
-        <v>416</v>
+        <v>268</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59">
-        <v>20968.7890230091</v>
+        <v>210535.026176057</v>
       </c>
       <c r="E59">
-        <v>49</v>
+        <v>671</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
         <v>2</v>
       </c>
-      <c r="C60" t="s">
-        <v>1</v>
-      </c>
       <c r="D60">
-        <v>62137.604970189903</v>
+        <v>121351.542268502</v>
       </c>
       <c r="E60">
-        <v>92</v>
+        <v>416</v>
       </c>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.25">
@@ -6571,41 +6610,41 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>56617.428037848404</v>
+        <v>20968.7890230091</v>
       </c>
       <c r="E61">
-        <v>133</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62">
-        <v>4916.5079167325503</v>
+        <v>62137.604970189903</v>
       </c>
       <c r="E62">
-        <v>19</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63">
-        <v>11219.7352089292</v>
+        <v>56617.428037848404</v>
       </c>
       <c r="E63">
-        <v>33</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.25">
@@ -6613,97 +6652,97 @@
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>30372.661147028601</v>
+        <v>4916.5079167325503</v>
       </c>
       <c r="E64">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>33377.814186217001</v>
+        <v>11219.7352089292</v>
       </c>
       <c r="E65">
-        <v>100</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C66" t="s">
         <v>2</v>
       </c>
       <c r="D66">
-        <v>70367.585458441914</v>
+        <v>30372.661147028601</v>
       </c>
       <c r="E66">
-        <v>202</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C67" t="s">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>69883.099397594095</v>
+        <v>33377.814186217001</v>
       </c>
       <c r="E67">
-        <v>202</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68" t="s">
         <v>2</v>
       </c>
       <c r="D68">
-        <v>132239.30044086539</v>
+        <v>70367.585458441914</v>
       </c>
       <c r="E68">
-        <v>513</v>
+        <v>202</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69" t="s">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>7719.92068896827</v>
+        <v>69883.099397594095</v>
       </c>
       <c r="E69">
-        <v>10</v>
+        <v>202</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C70" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70">
-        <v>6670.6837531622796</v>
+        <v>132239.30044086539</v>
       </c>
       <c r="E70">
-        <v>5</v>
+        <v>513</v>
       </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.25">
@@ -6711,41 +6750,41 @@
         <v>6</v>
       </c>
       <c r="C71" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>4233.5977867305201</v>
+        <v>7719.92068896827</v>
       </c>
       <c r="E71">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B72">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C72" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>47157.520468889401</v>
+        <v>6670.6837531622796</v>
       </c>
       <c r="E72">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B73">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C73" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73">
-        <v>27508.592579624699</v>
+        <v>4233.5977867305201</v>
       </c>
       <c r="E73">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.25">
@@ -6753,41 +6792,41 @@
         <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>26449.980666032399</v>
+        <v>47157.520468889401</v>
       </c>
       <c r="E74">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B75">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C75" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
-        <v>31749.7412333293</v>
+        <v>27508.592579624699</v>
       </c>
       <c r="E75">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B76">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C76" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76">
-        <v>13066.8121666193</v>
+        <v>26449.980666032399</v>
       </c>
       <c r="E76">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.25">
@@ -6795,17 +6834,46 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>31749.7412333293</v>
+      </c>
+      <c r="E77">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B78">
+        <v>8</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>13066.8121666193</v>
+      </c>
+      <c r="E78">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B79">
+        <v>8</v>
+      </c>
+      <c r="C79" t="s">
         <v>2</v>
       </c>
-      <c r="D77">
+      <c r="D79">
         <v>11381.3647679572</v>
       </c>
-      <c r="E77">
+      <c r="E79">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -6831,19 +6899,19 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
       <c r="F2" s="60"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="50" t="s">
@@ -7112,19 +7180,19 @@
       <c r="F13" s="50"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="72" t="s">
+      <c r="A14" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
       <c r="F14" s="60"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73"/>
-      <c r="K14" s="73"/>
-      <c r="L14" s="73"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="71"/>
+      <c r="L14" s="71"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="50" t="s">
@@ -7386,19 +7454,19 @@
       <c r="A25" s="57"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="73" t="s">
+      <c r="A27" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="73"/>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
+      <c r="B27" s="71"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
       <c r="F27" s="56"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="73"/>
-      <c r="J27" s="73"/>
-      <c r="K27" s="73"/>
-      <c r="L27" s="73"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="71"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="46" t="s">
@@ -7428,20 +7496,20 @@
       <c r="A29" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="71">
+      <c r="B29" s="72">
         <v>0.79</v>
       </c>
-      <c r="C29" s="71">
+      <c r="C29" s="72">
         <v>0.12</v>
       </c>
-      <c r="D29" s="71">
+      <c r="D29" s="72">
         <v>0.09</v>
       </c>
-      <c r="E29" s="71">
+      <c r="E29" s="72">
         <f>SUM(B29:D29)</f>
         <v>1</v>
       </c>
-      <c r="F29" s="71">
+      <c r="F29" s="72">
         <v>0.47599999999999998</v>
       </c>
       <c r="I29" s="64"/>
@@ -7453,11 +7521,11 @@
       <c r="A30" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
       <c r="I30" s="64"/>
       <c r="J30" s="64"/>
       <c r="K30" s="64"/>
@@ -7492,20 +7560,20 @@
       <c r="A32" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B32" s="71">
-        <v>0</v>
-      </c>
-      <c r="C32" s="71">
+      <c r="B32" s="72">
+        <v>0</v>
+      </c>
+      <c r="C32" s="72">
         <v>0.8</v>
       </c>
-      <c r="D32" s="71">
+      <c r="D32" s="72">
         <v>0.2</v>
       </c>
-      <c r="E32" s="71">
+      <c r="E32" s="72">
         <f>SUM(B32:D32)</f>
         <v>1</v>
       </c>
-      <c r="F32" s="71">
+      <c r="F32" s="72">
         <v>0.22600000000000001</v>
       </c>
       <c r="I32" s="64"/>
@@ -7517,11 +7585,11 @@
       <c r="A33" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
+      <c r="B33" s="72"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="72"/>
       <c r="I33" s="64"/>
       <c r="J33" s="64"/>
       <c r="K33" s="64"/>
@@ -7531,20 +7599,20 @@
       <c r="A34" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B34" s="71">
+      <c r="B34" s="72">
         <v>0.65</v>
       </c>
-      <c r="C34" s="71">
+      <c r="C34" s="72">
         <v>0.2</v>
       </c>
-      <c r="D34" s="71">
+      <c r="D34" s="72">
         <v>0.15</v>
       </c>
-      <c r="E34" s="71">
+      <c r="E34" s="72">
         <f>SUM(B34:D34)</f>
         <v>1</v>
       </c>
-      <c r="F34" s="71">
+      <c r="F34" s="72">
         <v>0.246</v>
       </c>
       <c r="I34" s="64"/>
@@ -7556,11 +7624,11 @@
       <c r="A35" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
       <c r="I35" s="64"/>
       <c r="J35" s="64"/>
       <c r="K35" s="64"/>
@@ -7570,11 +7638,11 @@
       <c r="A36" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B36" s="71"/>
-      <c r="C36" s="71"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
+      <c r="B36" s="72"/>
+      <c r="C36" s="72"/>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="72"/>
       <c r="I36" s="64"/>
       <c r="J36" s="64"/>
       <c r="K36" s="64"/>
@@ -7634,11 +7702,11 @@
       <c r="F40" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="H40" s="73"/>
-      <c r="I40" s="73"/>
-      <c r="J40" s="73"/>
-      <c r="K40" s="73"/>
-      <c r="L40" s="73"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="71"/>
+      <c r="L40" s="71"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="46" t="s">
@@ -7926,11 +7994,11 @@
         <f>E40</f>
         <v>Total</v>
       </c>
-      <c r="H52" s="73"/>
-      <c r="I52" s="73"/>
-      <c r="J52" s="73"/>
-      <c r="K52" s="73"/>
-      <c r="L52" s="73"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="71"/>
+      <c r="K52" s="71"/>
+      <c r="L52" s="71"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="50" t="str">
@@ -8188,11 +8256,11 @@
         <f>SUM(E41:E42)/$E$49</f>
         <v>0.47599999999999992</v>
       </c>
-      <c r="H64" s="73"/>
-      <c r="I64" s="73"/>
-      <c r="J64" s="73"/>
-      <c r="K64" s="73"/>
-      <c r="L64" s="73"/>
+      <c r="H64" s="71"/>
+      <c r="I64" s="71"/>
+      <c r="J64" s="71"/>
+      <c r="K64" s="71"/>
+      <c r="L64" s="71"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="48" t="s">
@@ -8330,12 +8398,17 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="H52:L52"/>
-    <mergeCell ref="H64:L64"/>
-    <mergeCell ref="H40:L40"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="A27:E27"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="H27:L27"/>
     <mergeCell ref="F29:F30"/>
@@ -8343,17 +8416,12 @@
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="D32:D33"/>
     <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="H52:L52"/>
+    <mergeCell ref="H64:L64"/>
+    <mergeCell ref="H40:L40"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="F34:F36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/utilities/calibration/workbook_templates/04_CoordinatedDailyActivityPattern_2023_blank.xlsx
+++ b/utilities/calibration/workbook_templates/04_CoordinatedDailyActivityPattern_2023_blank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\travel-model-one\utilities\calibration\workbook_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\travel-model-one-tm1.7_calibration\utilities\calibration\workbook_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BD3BB6-AF7D-4689-B12E-0186BD5E3238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D98C216-63F8-429E-A504-7C491D81ABF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="18" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="86">
   <si>
     <t>H</t>
   </si>
@@ -240,19 +240,10 @@
     <t>North Bay</t>
   </si>
   <si>
-    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20260821_NoMon_rmo/ctramp_2023/BATS_Summaries/dap_summaries.csv</t>
-  </si>
-  <si>
     <t>wfh_choice</t>
   </si>
   <si>
-    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20260821_NoMon_rmo/ctramp_2023/BATS_Summaries/BATS2023_person_type_summary_north_bay</t>
-  </si>
-  <si>
     <t>Solano/Napa</t>
-  </si>
-  <si>
-    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20260821_NoMon_rmo/ctramp_2023/BATS_Summaries/BATS2023_person_type_summary_solano_napa</t>
   </si>
   <si>
     <t>Sum of num_pers</t>
@@ -265,9 +256,6 @@
   </si>
   <si>
     <t>N Total</t>
-  </si>
-  <si>
-    <t>Source: M:\Development\Travel Model One\Calibration\Version 1.7\2023_BATS_Summaries\pipeline_mt_20260821_NoMon_rmo\2023 BATS WFH Rates.xlsx</t>
   </si>
   <si>
     <t>Home County Name</t>
@@ -283,9 +271,6 @@
   </si>
   <si>
     <t>Weighted Workers</t>
-  </si>
-  <si>
-    <t>WFH Rate</t>
   </si>
   <si>
     <t>Alameda</t>
@@ -361,6 +346,30 @@
   </si>
   <si>
     <t>N_WFH_1</t>
+  </si>
+  <si>
+    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20261008_NoMon_rmo/ctramp_2023/BATS_Summaries/dap_summaries.csv</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>CDAP</t>
+  </si>
+  <si>
+    <t>CHTS Values</t>
+  </si>
+  <si>
+    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20261008_NoMon_rmo/ctramp_2023/BATS_Summaries/BATS2023_person_type_summary_north_bay</t>
+  </si>
+  <si>
+    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20261008_NoMon_rmo/ctramp_2023/BATS_Summaries/BATS2023_person_type_summary_solano_napa</t>
+  </si>
+  <si>
+    <t>WFH Share</t>
+  </si>
+  <si>
+    <t>Source: M:\Development\Travel Model One\Calibration\Version 1.7\2023_BATS_Summaries\pipeline_mt_20261008_NoMon_rmo\2023 BATS WFH Rates.xlsx</t>
   </si>
 </sst>
 </file>
@@ -652,7 +661,7 @@
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -791,15 +800,17 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -807,14 +818,17 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="2" xr:uid="{CB21E4C0-D945-46EE-9A00-BE0A2B1C7632}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+    </dxf>
     <dxf>
       <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <font>
-        <sz val="10"/>
-      </font>
+      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -960,19 +974,19 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>1012773.346684529</c:v>
+                  <c:v>1230105.2348854889</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>227294.5588336706</c:v>
+                  <c:v>286903.59631397587</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>92621.767416518094</c:v>
+                  <c:v>90646.683137778877</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1475.6137896048408</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4051.085649701276</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>123094.58867</c:v>
@@ -1047,19 +1061,19 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>1197300.8246903126</c:v>
+                  <c:v>1343636.9371095512</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>279370.49790520186</c:v>
+                  <c:v>303270.18710574182</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>167120.28099272039</c:v>
+                  <c:v>198575.94101364535</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>431774.14292043669</c:v>
+                  <c:v>485574.30636942881</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>546572.11236746656</c:v>
+                  <c:v>580519.78521612787</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>17712.811699999998</c:v>
@@ -1134,19 +1148,19 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>557330.22619732516</c:v>
+                  <c:v>667739.48886334617</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>124392.50344448088</c:v>
+                  <c:v>114592.55289354955</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>64173.937822535387</c:v>
+                  <c:v>68345.75347247794</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>211570.34375830065</c:v>
+                  <c:v>255989.88428071633</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>332378.65690771444</c:v>
+                  <c:v>365408.67686414684</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>17630.20679</c:v>
@@ -2314,7 +2328,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Melody Tsao" refreshedDate="46296.699230208331" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="32" xr:uid="{84CD7BB2-9CA5-4AA6-9C9F-5CF4C2983D11}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Melody Tsao" refreshedDate="46317.604928472225" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="32" xr:uid="{84CD7BB2-9CA5-4AA6-9C9F-5CF4C2983D11}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B2:E34" sheet="BATS 2023"/>
   </cacheSource>
@@ -2345,7 +2359,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="num_pers" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="603.94457618764409" maxValue="1012169.4021083413"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="1229608.9493126601"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -2362,303 +2376,199 @@
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="271316.59622341208"/>
+    <n v="311650.04052777553"/>
   </r>
   <r>
     <x v="0"/>
     <x v="0"/>
     <x v="1"/>
-    <n v="286013.62997391314"/>
+    <n v="356089.44833557063"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="1012169.4021083413"/>
+    <n v="1229608.9493126601"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
     <x v="1"/>
-    <n v="603.94457618764409"/>
+    <n v="496.28557282869974"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="608665.62727682234"/>
+    <n v="663899.41953010834"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
     <x v="1"/>
-    <n v="588635.19741349027"/>
+    <n v="679737.51757944282"/>
   </r>
   <r>
     <x v="1"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="89626.740726589473"/>
+    <n v="83561.221108939819"/>
   </r>
   <r>
     <x v="1"/>
     <x v="0"/>
     <x v="1"/>
-    <n v="34765.762717891412"/>
+    <n v="31031.331784609742"/>
   </r>
   <r>
     <x v="1"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="227294.5588336706"/>
+    <n v="286903.59631397587"/>
   </r>
   <r>
     <x v="1"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="204304.20592620916"/>
+    <n v="230858.03226023554"/>
   </r>
   <r>
     <x v="1"/>
     <x v="2"/>
     <x v="1"/>
-    <n v="75066.291978992711"/>
+    <n v="72412.154845506258"/>
   </r>
   <r>
     <x v="2"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="55794.542626377515"/>
+    <n v="61904.494709690123"/>
   </r>
   <r>
     <x v="2"/>
     <x v="0"/>
     <x v="1"/>
-    <n v="8379.3951961578732"/>
+    <n v="6441.2587627878174"/>
   </r>
   <r>
     <x v="2"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="83737.789756864193"/>
+    <n v="86787.19392694821"/>
   </r>
   <r>
     <x v="2"/>
     <x v="1"/>
     <x v="1"/>
-    <n v="8883.9776596539086"/>
+    <n v="3859.4892108306631"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="138701.40986357236"/>
+    <n v="171454.29096303752"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
     <x v="1"/>
-    <n v="28418.871129148032"/>
+    <n v="27121.650050607841"/>
   </r>
   <r>
     <x v="3"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="211570.34375830065"/>
+    <n v="255989.88428071633"/>
   </r>
   <r>
     <x v="3"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="1475.6137896048408"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="3"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="431774.14292043669"/>
+    <n v="485574.30636942881"/>
   </r>
   <r>
     <x v="4"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="332378.65690771444"/>
+    <n v="365408.67686414684"/>
   </r>
   <r>
     <x v="4"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="4051.085649701276"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="4"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="546572.11236746656"/>
+    <n v="580519.78521612787"/>
   </r>
   <r>
     <x v="5"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="17630.20679"/>
+    <n v="74995.978217831318"/>
   </r>
   <r>
     <x v="5"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="123094.58867"/>
+    <n v="27888.048166248853"/>
   </r>
   <r>
     <x v="5"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="17712.811699999998"/>
+    <n v="59294.409690902619"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4891.8330184189444"/>
   </r>
   <r>
     <x v="6"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="85466.730259999997"/>
+    <n v="387248.05504112464"/>
   </r>
   <r>
     <x v="6"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="665066.56470999995"/>
+    <n v="156147.04247572814"/>
   </r>
   <r>
     <x v="6"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="64858.529419999999"/>
+    <n v="169505.952664399"/>
   </r>
   <r>
     <x v="7"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="121625.49533999999"/>
+    <n v="251728.81883796302"/>
   </r>
   <r>
     <x v="7"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="138048.92214000001"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="2"/>
-    <x v="0"/>
-    <n v="145623.69245999999"/>
+    <n v="60599.900261288341"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7349260-2F73-420D-852A-7C0C729E408C}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="I5:M15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of num_pers" fld="3" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="1">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="0">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC85B2BF-B5A3-41FF-B478-F9EFC1F3C73E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC85B2BF-B5A3-41FF-B478-F9EFC1F3C73E}" name="PivotTable1" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="P4:Z15" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -2765,6 +2675,113 @@
   <dataFields count="1">
     <dataField name="Sum of num_pers" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA3A1326-2495-4C73-860A-CEF4C23C2B41}" name="PivotTable5" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="I5:M15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of num_pers" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="0">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="2">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3139,19 +3156,19 @@
       </c>
       <c r="C5" s="9">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A5,'BATS 2023'!$C$3:$C$34,calibration!C$3)</f>
-        <v>1012773.346684529</v>
+        <v>1230105.2348854889</v>
       </c>
       <c r="D5" s="10">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A5,'BATS 2023'!$C$3:$C$34,calibration!D$3)</f>
-        <v>1197300.8246903126</v>
+        <v>1343636.9371095512</v>
       </c>
       <c r="E5" s="11">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A5,'BATS 2023'!$C$3:$C$34,calibration!E$3)</f>
-        <v>557330.22619732516</v>
+        <v>667739.48886334617</v>
       </c>
       <c r="F5" s="5">
         <f t="shared" ref="F5:F13" si="0">SUM(C5:E5)</f>
-        <v>2767404.3975721668</v>
+        <v>3241481.6608583862</v>
       </c>
       <c r="H5" s="9">
         <f>modeldata!C3</f>
@@ -3171,19 +3188,19 @@
       </c>
       <c r="M5" s="9">
         <f>IFERROR(H5-C5,0)</f>
-        <v>-1012772.346684529</v>
+        <v>-1230104.2348854889</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N13" si="1">IFERROR(I5-D5,0)</f>
-        <v>-1197299.8246903126</v>
+        <v>-1343635.9371095512</v>
       </c>
       <c r="O5" s="11">
         <f t="shared" ref="O5:O13" si="2">IFERROR(J5-E5,0)</f>
-        <v>-557329.22619732516</v>
+        <v>-667738.48886334617</v>
       </c>
       <c r="P5" s="5">
         <f t="shared" ref="P5:P13" si="3">IFERROR(K5-F5,0)</f>
-        <v>-2767401.3975721668</v>
+        <v>-3241478.6608583862</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -3195,19 +3212,19 @@
       </c>
       <c r="C6" s="12">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A6,'BATS 2023'!$C$3:$C$34,calibration!C$3)</f>
-        <v>227294.5588336706</v>
+        <v>286903.59631397587</v>
       </c>
       <c r="D6" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A6,'BATS 2023'!$C$3:$C$34,calibration!D$3)</f>
-        <v>279370.49790520186</v>
+        <v>303270.18710574182</v>
       </c>
       <c r="E6" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A6,'BATS 2023'!$C$3:$C$34,calibration!E$3)</f>
-        <v>124392.50344448088</v>
+        <v>114592.55289354955</v>
       </c>
       <c r="F6" s="5">
         <f t="shared" si="0"/>
-        <v>631057.56018335326</v>
+        <v>704766.33631326724</v>
       </c>
       <c r="H6" s="12">
         <f>modeldata!C4</f>
@@ -3227,19 +3244,19 @@
       </c>
       <c r="M6" s="12">
         <f t="shared" ref="M6:M13" si="5">IFERROR(H6-C6,0)</f>
-        <v>-227293.5588336706</v>
+        <v>-286902.59631397587</v>
       </c>
       <c r="N6" s="5">
         <f t="shared" si="1"/>
-        <v>-279369.49790520186</v>
+        <v>-303269.18710574182</v>
       </c>
       <c r="O6" s="13">
         <f t="shared" si="2"/>
-        <v>-124391.50344448088</v>
+        <v>-114591.55289354955</v>
       </c>
       <c r="P6" s="5">
         <f t="shared" si="3"/>
-        <v>-631054.56018335326</v>
+        <v>-704763.33631326724</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
@@ -3251,19 +3268,19 @@
       </c>
       <c r="C7" s="12">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A7,'BATS 2023'!$C$3:$C$34,calibration!C$3)</f>
-        <v>92621.767416518094</v>
+        <v>90646.683137778877</v>
       </c>
       <c r="D7" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A7,'BATS 2023'!$C$3:$C$34,calibration!D$3)</f>
-        <v>167120.28099272039</v>
+        <v>198575.94101364535</v>
       </c>
       <c r="E7" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A7,'BATS 2023'!$C$3:$C$34,calibration!E$3)</f>
-        <v>64173.937822535387</v>
+        <v>68345.75347247794</v>
       </c>
       <c r="F7" s="5">
         <f t="shared" si="0"/>
-        <v>323915.98623177386</v>
+        <v>357568.37762390217</v>
       </c>
       <c r="H7" s="12">
         <f>modeldata!C5</f>
@@ -3283,19 +3300,19 @@
       </c>
       <c r="M7" s="12">
         <f t="shared" si="5"/>
-        <v>-92620.767416518094</v>
+        <v>-90645.683137778877</v>
       </c>
       <c r="N7" s="5">
         <f t="shared" si="1"/>
-        <v>-167119.28099272039</v>
+        <v>-198574.94101364535</v>
       </c>
       <c r="O7" s="13">
         <f t="shared" si="2"/>
-        <v>-64172.937822535387</v>
+        <v>-68344.75347247794</v>
       </c>
       <c r="P7" s="5">
         <f t="shared" si="3"/>
-        <v>-323912.98623177386</v>
+        <v>-357565.37762390217</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -3307,19 +3324,19 @@
       </c>
       <c r="C8" s="12">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A8,'BATS 2023'!$C$3:$C$34,calibration!C$3)</f>
-        <v>1475.6137896048408</v>
+        <v>0</v>
       </c>
       <c r="D8" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A8,'BATS 2023'!$C$3:$C$34,calibration!D$3)</f>
-        <v>431774.14292043669</v>
+        <v>485574.30636942881</v>
       </c>
       <c r="E8" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A8,'BATS 2023'!$C$3:$C$34,calibration!E$3)</f>
-        <v>211570.34375830065</v>
+        <v>255989.88428071633</v>
       </c>
       <c r="F8" s="5">
         <f t="shared" si="0"/>
-        <v>644820.10046834219</v>
+        <v>741564.19065014517</v>
       </c>
       <c r="H8" s="12">
         <f>modeldata!C6</f>
@@ -3339,19 +3356,19 @@
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>-1474.6137896048408</v>
+        <v>1</v>
       </c>
       <c r="N8" s="5">
         <f t="shared" si="1"/>
-        <v>-431773.14292043669</v>
+        <v>-485573.30636942881</v>
       </c>
       <c r="O8" s="13">
         <f t="shared" si="2"/>
-        <v>-211569.34375830065</v>
+        <v>-255988.88428071633</v>
       </c>
       <c r="P8" s="5">
         <f t="shared" si="3"/>
-        <v>-644817.10046834219</v>
+        <v>-741561.19065014517</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
@@ -3363,19 +3380,19 @@
       </c>
       <c r="C9" s="12">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A9,'BATS 2023'!$C$3:$C$34,calibration!C$3)</f>
-        <v>4051.085649701276</v>
+        <v>0</v>
       </c>
       <c r="D9" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A9,'BATS 2023'!$C$3:$C$34,calibration!D$3)</f>
-        <v>546572.11236746656</v>
+        <v>580519.78521612787</v>
       </c>
       <c r="E9" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A9,'BATS 2023'!$C$3:$C$34,calibration!E$3)</f>
-        <v>332378.65690771444</v>
+        <v>365408.67686414684</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="0"/>
-        <v>883001.8549248823</v>
+        <v>945928.46208027471</v>
       </c>
       <c r="H9" s="12">
         <f>modeldata!C7</f>
@@ -3395,19 +3412,19 @@
       </c>
       <c r="M9" s="12">
         <f t="shared" si="5"/>
-        <v>-4050.085649701276</v>
+        <v>1</v>
       </c>
       <c r="N9" s="5">
         <f t="shared" si="1"/>
-        <v>-546571.11236746656</v>
+        <v>-580518.78521612787</v>
       </c>
       <c r="O9" s="13">
         <f t="shared" si="2"/>
-        <v>-332377.65690771444</v>
+        <v>-365407.67686414684</v>
       </c>
       <c r="P9" s="5">
         <f t="shared" si="3"/>
-        <v>-882998.8549248823</v>
+        <v>-945925.46208027471</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
@@ -3584,19 +3601,19 @@
       </c>
       <c r="C13" s="5">
         <f>SUM(C5:C12)</f>
-        <v>2264426.4478940237</v>
+        <v>2533865.5898572435</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" ref="D13:E13" si="6">SUM(D5:D12)</f>
-        <v>2850332.892456138</v>
+        <v>3139772.1903944951</v>
       </c>
       <c r="E13" s="5">
         <f t="shared" si="6"/>
-        <v>1514568.1005203566</v>
+        <v>1696798.7887642367</v>
       </c>
       <c r="F13" s="5">
         <f t="shared" si="0"/>
-        <v>6629327.4408705188</v>
+        <v>7370436.5690159751</v>
       </c>
       <c r="H13" s="5">
         <f>SUM(H5:H12)</f>
@@ -3616,19 +3633,19 @@
       </c>
       <c r="M13" s="5">
         <f t="shared" si="5"/>
-        <v>-2264418.4478940237</v>
+        <v>-2533857.5898572435</v>
       </c>
       <c r="N13" s="5">
         <f t="shared" si="1"/>
-        <v>-2850324.892456138</v>
+        <v>-3139764.1903944951</v>
       </c>
       <c r="O13" s="5">
         <f t="shared" si="2"/>
-        <v>-1514560.1005203566</v>
+        <v>-1696790.7887642367</v>
       </c>
       <c r="P13" s="5">
         <f t="shared" si="3"/>
-        <v>-6629303.4408705188</v>
+        <v>-7370412.5690159751</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
@@ -3678,15 +3695,15 @@
       </c>
       <c r="C17" s="18">
         <f>C5/$F5</f>
-        <v>0.36596507094266062</v>
+        <v>0.37948856837269324</v>
       </c>
       <c r="D17" s="19">
         <f t="shared" ref="D17:E17" si="8">D5/$F5</f>
-        <v>0.43264396982988829</v>
+        <v>0.41451320034731859</v>
       </c>
       <c r="E17" s="20">
         <f t="shared" si="8"/>
-        <v>0.20139095922745112</v>
+        <v>0.2059982312799882</v>
       </c>
       <c r="F17" s="17">
         <f>F5/$F5</f>
@@ -3710,15 +3727,15 @@
       </c>
       <c r="M17" s="18">
         <f>IFERROR(H17-C17,0)</f>
-        <v>-3.2631737609327305E-2</v>
+        <v>-4.6155235039359921E-2</v>
       </c>
       <c r="N17" s="19">
         <f t="shared" ref="N17:N25" si="10">IFERROR(I17-D17,0)</f>
-        <v>-9.9310636496554971E-2</v>
+        <v>-8.1179867013985274E-2</v>
       </c>
       <c r="O17" s="20">
         <f t="shared" ref="O17:O25" si="11">IFERROR(J17-E17,0)</f>
-        <v>0.13194237410588219</v>
+        <v>0.12733510205334511</v>
       </c>
       <c r="P17" s="17">
         <f t="shared" ref="P17:P25" si="12">IFERROR(K17-F17,0)</f>
@@ -3731,15 +3748,15 @@
       </c>
       <c r="C18" s="21">
         <f t="shared" ref="C18:F18" si="13">C6/$F6</f>
-        <v>0.36018039110034644</v>
+        <v>0.40709038092654837</v>
       </c>
       <c r="D18" s="17">
         <f t="shared" si="13"/>
-        <v>0.44270208540728201</v>
+        <v>0.43031310021445013</v>
       </c>
       <c r="E18" s="22">
         <f t="shared" si="13"/>
-        <v>0.19711752349237166</v>
+        <v>0.1625965188590015</v>
       </c>
       <c r="F18" s="17">
         <f t="shared" si="13"/>
@@ -3763,15 +3780,15 @@
       </c>
       <c r="M18" s="21">
         <f t="shared" ref="M18:M25" si="15">IFERROR(H18-C18,0)</f>
-        <v>-2.6847057767013127E-2</v>
+        <v>-7.3757047593215053E-2</v>
       </c>
       <c r="N18" s="17">
         <f t="shared" si="10"/>
-        <v>-0.10936875207394869</v>
+        <v>-9.6979766881116813E-2</v>
       </c>
       <c r="O18" s="22">
         <f t="shared" si="11"/>
-        <v>0.13621580984096165</v>
+        <v>0.17073681447433181</v>
       </c>
       <c r="P18" s="17">
         <f t="shared" si="12"/>
@@ -3784,15 +3801,15 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:F19" si="16">C7/$F7</f>
-        <v>0.2859437982484872</v>
+        <v>0.25350866802075805</v>
       </c>
       <c r="D19" s="17">
         <f t="shared" si="16"/>
-        <v>0.51593711979729107</v>
+        <v>0.55535095785934308</v>
       </c>
       <c r="E19" s="22">
         <f t="shared" si="16"/>
-        <v>0.19811908195422182</v>
+        <v>0.19114037411989887</v>
       </c>
       <c r="F19" s="17">
         <f t="shared" si="16"/>
@@ -3816,15 +3833,15 @@
       </c>
       <c r="M19" s="21">
         <f t="shared" si="15"/>
-        <v>4.7389535084846113E-2</v>
+        <v>7.982466531257526E-2</v>
       </c>
       <c r="N19" s="17">
         <f t="shared" si="10"/>
-        <v>-0.18260378646395775</v>
+        <v>-0.22201762452600976</v>
       </c>
       <c r="O19" s="22">
         <f t="shared" si="11"/>
-        <v>0.1352142513791115</v>
+        <v>0.14219295921343444</v>
       </c>
       <c r="P19" s="17">
         <f t="shared" si="12"/>
@@ -3837,15 +3854,15 @@
       </c>
       <c r="C20" s="21">
         <f t="shared" ref="C20:F20" si="18">C8/$F8</f>
-        <v>2.288411587252136E-3</v>
+        <v>0</v>
       </c>
       <c r="D20" s="17">
         <f t="shared" si="18"/>
-        <v>0.66960403778795496</v>
+        <v>0.65479740323452706</v>
       </c>
       <c r="E20" s="22">
         <f t="shared" si="18"/>
-        <v>0.32810755062479291</v>
+        <v>0.34520259676547288</v>
       </c>
       <c r="F20" s="17">
         <f t="shared" si="18"/>
@@ -3869,15 +3886,15 @@
       </c>
       <c r="M20" s="21">
         <f t="shared" si="15"/>
-        <v>0.33104492174608119</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N20" s="17">
         <f t="shared" si="10"/>
-        <v>-0.33627070445462165</v>
+        <v>-0.32146406990119375</v>
       </c>
       <c r="O20" s="22">
         <f t="shared" si="11"/>
-        <v>5.2257827085404052E-3</v>
+        <v>-1.1869263432139565E-2</v>
       </c>
       <c r="P20" s="17">
         <f t="shared" si="12"/>
@@ -3890,15 +3907,15 @@
       </c>
       <c r="C21" s="21">
         <f t="shared" ref="C21:F21" si="20">C9/$F9</f>
-        <v>4.587856330206583E-3</v>
+        <v>0</v>
       </c>
       <c r="D21" s="17">
         <f t="shared" si="20"/>
-        <v>0.61899316441862273</v>
+        <v>0.61370368742204418</v>
       </c>
       <c r="E21" s="22">
         <f t="shared" si="20"/>
-        <v>0.37641897925117063</v>
+        <v>0.38629631257795582</v>
       </c>
       <c r="F21" s="17">
         <f t="shared" si="20"/>
@@ -3922,15 +3939,15 @@
       </c>
       <c r="M21" s="21">
         <f t="shared" si="15"/>
-        <v>0.32874547700312673</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N21" s="17">
         <f t="shared" si="10"/>
-        <v>-0.28565983108528942</v>
+        <v>-0.28037035408871086</v>
       </c>
       <c r="O21" s="22">
         <f t="shared" si="11"/>
-        <v>-4.3085645917837312E-2</v>
+        <v>-5.296297924462251E-2</v>
       </c>
       <c r="P21" s="17">
         <f t="shared" si="12"/>
@@ -4102,15 +4119,15 @@
       </c>
       <c r="C25" s="17">
         <f t="shared" ref="C25:F25" si="28">C13/$F13</f>
-        <v>0.34157710085846571</v>
+        <v>0.34378772086706111</v>
       </c>
       <c r="D25" s="17">
         <f t="shared" si="28"/>
-        <v>0.42995807913839468</v>
+        <v>0.42599541573881089</v>
       </c>
       <c r="E25" s="17">
         <f t="shared" si="28"/>
-        <v>0.2284648200031395</v>
+        <v>0.23021686339412806</v>
       </c>
       <c r="F25" s="17">
         <f t="shared" si="28"/>
@@ -4134,15 +4151,15 @@
       </c>
       <c r="M25" s="17">
         <f t="shared" si="15"/>
-        <v>-8.243767525132395E-3</v>
+        <v>-1.0454387533727794E-2</v>
       </c>
       <c r="N25" s="17">
         <f t="shared" si="10"/>
-        <v>-9.6624745805061363E-2</v>
+        <v>-9.2662082405477575E-2</v>
       </c>
       <c r="O25" s="17">
         <f t="shared" si="11"/>
-        <v>0.10486851333019381</v>
+        <v>0.10311646993920526</v>
       </c>
       <c r="P25" s="17">
         <f t="shared" si="12"/>
@@ -4468,11 +4485,11 @@
     </row>
     <row r="41" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B41" s="69" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H41" s="69"/>
       <c r="K41" s="69" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="M41" s="69"/>
     </row>
@@ -4583,58 +4600,58 @@
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C45" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M45" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="N45" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O45" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="P45" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="S45" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="T45" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="U45" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="V45" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="X45" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.2">
@@ -4646,31 +4663,31 @@
       </c>
       <c r="C46" s="9">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A46,'BATS 2023'!$C$3:$C$34,C$42,'BATS 2023'!$D$3:$D$34,C$43)</f>
-        <v>1012169.4021083413</v>
+        <v>1229608.9493126601</v>
       </c>
       <c r="D46" s="10">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A46,'BATS 2023'!$C$3:$C$34,D$42,'BATS 2023'!$D$3:$D$34,D$43)</f>
-        <v>603.94457618764409</v>
+        <v>496.28557282869974</v>
       </c>
       <c r="E46" s="10">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A46,'BATS 2023'!$C$3:$C$34,E$42,'BATS 2023'!$D$3:$D$34,E$43)</f>
-        <v>608665.62727682234</v>
+        <v>663899.41953010834</v>
       </c>
       <c r="F46" s="10">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A46,'BATS 2023'!$C$3:$C$34,F$42,'BATS 2023'!$D$3:$D$34,F$43)</f>
-        <v>588635.19741349027</v>
+        <v>679737.51757944282</v>
       </c>
       <c r="G46" s="10">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A46,'BATS 2023'!$C$3:$C$34,G$42,'BATS 2023'!$D$3:$D$34,G$43)</f>
-        <v>271316.59622341208</v>
+        <v>311650.04052777553</v>
       </c>
       <c r="H46" s="11">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A46,'BATS 2023'!$C$3:$C$34,H$42,'BATS 2023'!$D$3:$D$34,H$43)</f>
-        <v>286013.62997391314</v>
+        <v>356089.44833557063</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" ref="I46:I54" si="32">SUM(C46:H46)</f>
-        <v>2767404.3975721668</v>
+        <v>3241481.6608583862</v>
       </c>
       <c r="K46" s="9">
         <f>modeldata!D15</f>
@@ -4702,27 +4719,27 @@
       </c>
       <c r="S46" s="9">
         <f>IFERROR(K46-C46,0)</f>
-        <v>-1012168.4021083413</v>
+        <v>-1229607.9493126601</v>
       </c>
       <c r="T46" s="10">
         <f t="shared" ref="T46:X46" si="33">IFERROR(L46-D46,0)</f>
-        <v>-602.94457618764409</v>
+        <v>-495.28557282869974</v>
       </c>
       <c r="U46" s="10">
         <f t="shared" si="33"/>
-        <v>-608664.62727682234</v>
+        <v>-663898.41953010834</v>
       </c>
       <c r="V46" s="10">
         <f t="shared" si="33"/>
-        <v>-588634.19741349027</v>
+        <v>-679736.51757944282</v>
       </c>
       <c r="W46" s="10">
         <f t="shared" si="33"/>
-        <v>-271315.59622341208</v>
+        <v>-311649.04052777553</v>
       </c>
       <c r="X46" s="11">
         <f t="shared" si="33"/>
-        <v>-286012.62997391314</v>
+        <v>-356088.44833557063</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.2">
@@ -4734,7 +4751,7 @@
       </c>
       <c r="C47" s="12">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A47,'BATS 2023'!$C$3:$C$34,C$42,'BATS 2023'!$D$3:$D$34,C$43)</f>
-        <v>227294.5588336706</v>
+        <v>286903.59631397587</v>
       </c>
       <c r="D47" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A47,'BATS 2023'!$C$3:$C$34,D$42,'BATS 2023'!$D$3:$D$34,D$43)</f>
@@ -4742,23 +4759,23 @@
       </c>
       <c r="E47" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A47,'BATS 2023'!$C$3:$C$34,E$42,'BATS 2023'!$D$3:$D$34,E$43)</f>
-        <v>204304.20592620916</v>
+        <v>230858.03226023554</v>
       </c>
       <c r="F47" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A47,'BATS 2023'!$C$3:$C$34,F$42,'BATS 2023'!$D$3:$D$34,F$43)</f>
-        <v>75066.291978992711</v>
+        <v>72412.154845506258</v>
       </c>
       <c r="G47" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A47,'BATS 2023'!$C$3:$C$34,G$42,'BATS 2023'!$D$3:$D$34,G$43)</f>
-        <v>89626.740726589473</v>
+        <v>83561.221108939819</v>
       </c>
       <c r="H47" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A47,'BATS 2023'!$C$3:$C$34,H$42,'BATS 2023'!$D$3:$D$34,H$43)</f>
-        <v>34765.762717891412</v>
+        <v>31031.331784609742</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" si="32"/>
-        <v>631057.56018335337</v>
+        <v>704766.33631326724</v>
       </c>
       <c r="K47" s="12">
         <f>modeldata!D16</f>
@@ -4790,7 +4807,7 @@
       </c>
       <c r="S47" s="12">
         <f t="shared" ref="S47:S53" si="35">IFERROR(K47-C47,0)</f>
-        <v>-227293.5588336706</v>
+        <v>-286902.59631397587</v>
       </c>
       <c r="T47" s="5">
         <f t="shared" ref="T47:T53" si="36">IFERROR(L47-D47,0)</f>
@@ -4798,19 +4815,19 @@
       </c>
       <c r="U47" s="5">
         <f t="shared" ref="U47:U53" si="37">IFERROR(M47-E47,0)</f>
-        <v>-204303.20592620916</v>
+        <v>-230857.03226023554</v>
       </c>
       <c r="V47" s="5">
         <f t="shared" ref="V47:V53" si="38">IFERROR(N47-F47,0)</f>
-        <v>-75065.291978992711</v>
+        <v>-72411.154845506258</v>
       </c>
       <c r="W47" s="5">
         <f t="shared" ref="W47:W53" si="39">IFERROR(O47-G47,0)</f>
-        <v>-89625.740726589473</v>
+        <v>-83560.221108939819</v>
       </c>
       <c r="X47" s="13">
         <f t="shared" ref="X47:X53" si="40">IFERROR(P47-H47,0)</f>
-        <v>-34764.762717891412</v>
+        <v>-31030.331784609742</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.2">
@@ -4822,31 +4839,31 @@
       </c>
       <c r="C48" s="12">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A48,'BATS 2023'!$C$3:$C$34,C$42,'BATS 2023'!$D$3:$D$34,C$43)</f>
-        <v>83737.789756864193</v>
+        <v>86787.19392694821</v>
       </c>
       <c r="D48" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A48,'BATS 2023'!$C$3:$C$34,D$42,'BATS 2023'!$D$3:$D$34,D$43)</f>
-        <v>8883.9776596539086</v>
+        <v>3859.4892108306631</v>
       </c>
       <c r="E48" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A48,'BATS 2023'!$C$3:$C$34,E$42,'BATS 2023'!$D$3:$D$34,E$43)</f>
-        <v>138701.40986357236</v>
+        <v>171454.29096303752</v>
       </c>
       <c r="F48" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A48,'BATS 2023'!$C$3:$C$34,F$42,'BATS 2023'!$D$3:$D$34,F$43)</f>
-        <v>28418.871129148032</v>
+        <v>27121.650050607841</v>
       </c>
       <c r="G48" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A48,'BATS 2023'!$C$3:$C$34,G$42,'BATS 2023'!$D$3:$D$34,G$43)</f>
-        <v>55794.542626377515</v>
+        <v>61904.494709690123</v>
       </c>
       <c r="H48" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A48,'BATS 2023'!$C$3:$C$34,H$42,'BATS 2023'!$D$3:$D$34,H$43)</f>
-        <v>8379.3951961578732</v>
+        <v>6441.2587627878174</v>
       </c>
       <c r="I48" s="5">
         <f t="shared" si="32"/>
-        <v>323915.98623177386</v>
+        <v>357568.37762390217</v>
       </c>
       <c r="K48" s="12">
         <f>modeldata!D17</f>
@@ -4878,27 +4895,27 @@
       </c>
       <c r="S48" s="12">
         <f t="shared" si="35"/>
-        <v>-83736.789756864193</v>
+        <v>-86786.19392694821</v>
       </c>
       <c r="T48" s="5">
         <f t="shared" si="36"/>
-        <v>-8882.9776596539086</v>
+        <v>-3858.4892108306631</v>
       </c>
       <c r="U48" s="5">
         <f t="shared" si="37"/>
-        <v>-138700.40986357236</v>
+        <v>-171453.29096303752</v>
       </c>
       <c r="V48" s="5">
         <f t="shared" si="38"/>
-        <v>-28417.871129148032</v>
+        <v>-27120.650050607841</v>
       </c>
       <c r="W48" s="5">
         <f t="shared" si="39"/>
-        <v>-55793.542626377515</v>
+        <v>-61903.494709690123</v>
       </c>
       <c r="X48" s="13">
         <f t="shared" si="40"/>
-        <v>-8378.3951961578732</v>
+        <v>-6440.2587627878174</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.2">
@@ -4910,7 +4927,7 @@
       </c>
       <c r="C49" s="12">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A49,'BATS 2023'!$C$3:$C$34,C$42,'BATS 2023'!$D$3:$D$34,C$43)</f>
-        <v>1475.6137896048408</v>
+        <v>0</v>
       </c>
       <c r="D49" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A49,'BATS 2023'!$C$3:$C$34,D$42,'BATS 2023'!$D$3:$D$34,D$43)</f>
@@ -4918,7 +4935,7 @@
       </c>
       <c r="E49" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A49,'BATS 2023'!$C$3:$C$34,E$42,'BATS 2023'!$D$3:$D$34,E$43)</f>
-        <v>431774.14292043669</v>
+        <v>485574.30636942881</v>
       </c>
       <c r="F49" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A49,'BATS 2023'!$C$3:$C$34,F$42,'BATS 2023'!$D$3:$D$34,F$43)</f>
@@ -4926,7 +4943,7 @@
       </c>
       <c r="G49" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A49,'BATS 2023'!$C$3:$C$34,G$42,'BATS 2023'!$D$3:$D$34,G$43)</f>
-        <v>211570.34375830065</v>
+        <v>255989.88428071633</v>
       </c>
       <c r="H49" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A49,'BATS 2023'!$C$3:$C$34,H$42,'BATS 2023'!$D$3:$D$34,H$43)</f>
@@ -4934,7 +4951,7 @@
       </c>
       <c r="I49" s="5">
         <f t="shared" si="32"/>
-        <v>644820.10046834219</v>
+        <v>741564.19065014517</v>
       </c>
       <c r="K49" s="12">
         <f>modeldata!D18</f>
@@ -4966,7 +4983,7 @@
       </c>
       <c r="S49" s="12">
         <f t="shared" si="35"/>
-        <v>-1474.6137896048408</v>
+        <v>1</v>
       </c>
       <c r="T49" s="5">
         <f t="shared" si="36"/>
@@ -4974,7 +4991,7 @@
       </c>
       <c r="U49" s="5">
         <f t="shared" si="37"/>
-        <v>-431773.14292043669</v>
+        <v>-485573.30636942881</v>
       </c>
       <c r="V49" s="5">
         <f t="shared" si="38"/>
@@ -4982,7 +4999,7 @@
       </c>
       <c r="W49" s="5">
         <f t="shared" si="39"/>
-        <v>-211569.34375830065</v>
+        <v>-255988.88428071633</v>
       </c>
       <c r="X49" s="13">
         <f t="shared" si="40"/>
@@ -4998,7 +5015,7 @@
       </c>
       <c r="C50" s="12">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A50,'BATS 2023'!$C$3:$C$34,C$42,'BATS 2023'!$D$3:$D$34,C$43)</f>
-        <v>4051.085649701276</v>
+        <v>0</v>
       </c>
       <c r="D50" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A50,'BATS 2023'!$C$3:$C$34,D$42,'BATS 2023'!$D$3:$D$34,D$43)</f>
@@ -5006,7 +5023,7 @@
       </c>
       <c r="E50" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A50,'BATS 2023'!$C$3:$C$34,E$42,'BATS 2023'!$D$3:$D$34,E$43)</f>
-        <v>546572.11236746656</v>
+        <v>580519.78521612787</v>
       </c>
       <c r="F50" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A50,'BATS 2023'!$C$3:$C$34,F$42,'BATS 2023'!$D$3:$D$34,F$43)</f>
@@ -5014,7 +5031,7 @@
       </c>
       <c r="G50" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A50,'BATS 2023'!$C$3:$C$34,G$42,'BATS 2023'!$D$3:$D$34,G$43)</f>
-        <v>332378.65690771444</v>
+        <v>365408.67686414684</v>
       </c>
       <c r="H50" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A50,'BATS 2023'!$C$3:$C$34,H$42,'BATS 2023'!$D$3:$D$34,H$43)</f>
@@ -5022,7 +5039,7 @@
       </c>
       <c r="I50" s="5">
         <f t="shared" si="32"/>
-        <v>883001.8549248823</v>
+        <v>945928.46208027471</v>
       </c>
       <c r="K50" s="12">
         <f>modeldata!D19</f>
@@ -5054,7 +5071,7 @@
       </c>
       <c r="S50" s="12">
         <f t="shared" si="35"/>
-        <v>-4050.085649701276</v>
+        <v>1</v>
       </c>
       <c r="T50" s="5">
         <f t="shared" si="36"/>
@@ -5062,7 +5079,7 @@
       </c>
       <c r="U50" s="5">
         <f t="shared" si="37"/>
-        <v>-546571.11236746656</v>
+        <v>-580518.78521612787</v>
       </c>
       <c r="V50" s="5">
         <f t="shared" si="38"/>
@@ -5070,7 +5087,7 @@
       </c>
       <c r="W50" s="5">
         <f t="shared" si="39"/>
-        <v>-332377.65690771444</v>
+        <v>-365407.67686414684</v>
       </c>
       <c r="X50" s="13">
         <f t="shared" si="40"/>
@@ -5347,31 +5364,31 @@
       </c>
       <c r="C54" s="5">
         <f>SUM(C46:C53)</f>
-        <v>2254938.5256581819</v>
+        <v>2529509.8150735842</v>
       </c>
       <c r="D54" s="5">
         <f t="shared" ref="D54" si="41">SUM(D46:D53)</f>
-        <v>9487.9222358415536</v>
+        <v>4355.7747836593626</v>
       </c>
       <c r="E54" s="5">
         <f t="shared" ref="E54" si="42">SUM(E46:E53)</f>
-        <v>2158212.5319345072</v>
+        <v>2360500.8679189379</v>
       </c>
       <c r="F54" s="5">
         <f t="shared" ref="F54" si="43">SUM(F46:F53)</f>
-        <v>692120.36052163108</v>
+        <v>779271.32247555698</v>
       </c>
       <c r="G54" s="5">
         <f t="shared" ref="G54" si="44">SUM(G46:G53)</f>
-        <v>1185409.312632394</v>
+        <v>1303236.7498812687</v>
       </c>
       <c r="H54" s="5">
         <f t="shared" ref="H54" si="45">SUM(H46:H53)</f>
-        <v>329158.78788796242</v>
+        <v>393562.03888296819</v>
       </c>
       <c r="I54" s="5">
         <f t="shared" si="32"/>
-        <v>6629327.4408705188</v>
+        <v>7370436.5690159751</v>
       </c>
       <c r="K54" s="5">
         <f>SUM(K46:K53)</f>
@@ -5399,19 +5416,19 @@
       </c>
       <c r="S54" s="5">
         <f>IFERROR(K54-C54,0)</f>
-        <v>-2254930.5256581819</v>
+        <v>-2529501.8150735842</v>
       </c>
       <c r="T54" s="5">
         <f>IFERROR(L54-D54,0)</f>
-        <v>-9479.9222358415536</v>
+        <v>-4347.7747836593626</v>
       </c>
       <c r="U54" s="5">
         <f>IFERROR(M54-E54,0)</f>
-        <v>-2158204.5319345072</v>
+        <v>-2360492.8679189379</v>
       </c>
       <c r="V54" s="5">
         <f>IFERROR(N54-I54,0)</f>
-        <v>-6629319.4408705188</v>
+        <v>-7370428.5690159751</v>
       </c>
       <c r="W54" s="5">
         <f t="shared" ref="W54:X54" si="47">IFERROR(O54-J54,0)</f>
@@ -5489,58 +5506,58 @@
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C58" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M58" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="N58" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O58" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="P58" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="S58" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="T58" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="U58" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="V58" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="W58" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="X58" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.2">
@@ -5549,31 +5566,31 @@
       </c>
       <c r="C59" s="18">
         <f t="shared" ref="C59:E67" si="48">C46/$I46</f>
-        <v>0.36574683591466201</v>
+        <v>0.37933546382830491</v>
       </c>
       <c r="D59" s="19">
         <f t="shared" si="48"/>
-        <v>2.1823502799861211E-4</v>
+        <v>1.5310454438828352E-4</v>
       </c>
       <c r="E59" s="19">
         <f t="shared" si="48"/>
-        <v>0.21994097711588606</v>
+        <v>0.20481356644612303</v>
       </c>
       <c r="F59" s="19">
         <f t="shared" ref="F59:H59" si="49">F46/$I46</f>
-        <v>0.21270299271400223</v>
+        <v>0.20969963390119553</v>
       </c>
       <c r="G59" s="19">
         <f t="shared" si="49"/>
-        <v>9.804009723386907E-2</v>
+        <v>9.6144317054456696E-2</v>
       </c>
       <c r="H59" s="20">
         <f t="shared" si="49"/>
-        <v>0.10335086199358207</v>
+        <v>0.10985391422553152</v>
       </c>
       <c r="I59" s="17">
         <f>SUM(C59:H59)</f>
-        <v>1.0000000000000002</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="K59" s="18">
         <f>IFERROR(K46/$Q46,0)</f>
@@ -5605,31 +5622,31 @@
       </c>
       <c r="S59" s="18">
         <f t="shared" ref="S59:S67" si="51">IFERROR(K59-C59,0)</f>
-        <v>-0.19908016924799535</v>
+        <v>-0.21266879716163825</v>
       </c>
       <c r="T59" s="19">
         <f t="shared" ref="T59:T67" si="52">IFERROR(L59-D59,0)</f>
-        <v>0.16644843163866804</v>
+        <v>0.16651356212227839</v>
       </c>
       <c r="U59" s="19">
         <f t="shared" ref="U59:U67" si="53">IFERROR(M59-E59,0)</f>
-        <v>-5.3274310449219403E-2</v>
+        <v>-3.8146899779456372E-2</v>
       </c>
       <c r="V59" s="19">
         <f t="shared" ref="V59:X67" si="54">IFERROR(N59-F59,0)</f>
-        <v>-4.6036326047335568E-2</v>
+        <v>-4.3032967234528874E-2</v>
       </c>
       <c r="W59" s="19">
         <f t="shared" si="54"/>
-        <v>6.8626569432797588E-2</v>
+        <v>7.0522349612209961E-2</v>
       </c>
       <c r="X59" s="20">
         <f t="shared" si="54"/>
-        <v>6.3315804673084591E-2</v>
+        <v>5.6812752441135136E-2</v>
       </c>
       <c r="Y59" s="93">
         <f>IFERROR(Q59-I59,0)</f>
-        <v>-3.3306690738754696E-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.2">
@@ -5638,7 +5655,7 @@
       </c>
       <c r="C60" s="21">
         <f t="shared" si="48"/>
-        <v>0.36018039110034639</v>
+        <v>0.40709038092654837</v>
       </c>
       <c r="D60" s="17">
         <f t="shared" si="48"/>
@@ -5646,23 +5663,23 @@
       </c>
       <c r="E60" s="17">
         <f t="shared" si="48"/>
-        <v>0.3237489237381907</v>
+        <v>0.32756676981464056</v>
       </c>
       <c r="F60" s="17">
         <f t="shared" ref="F60:H60" si="55">F47/$I47</f>
-        <v>0.11895316166909124</v>
+        <v>0.10274633039980956</v>
       </c>
       <c r="G60" s="17">
         <f t="shared" si="55"/>
-        <v>0.14202625304187541</v>
+        <v>0.11856585197593351</v>
       </c>
       <c r="H60" s="22">
         <f t="shared" si="55"/>
-        <v>5.5091270450496214E-2</v>
+        <v>4.4030666883068004E-2</v>
       </c>
       <c r="I60" s="17">
         <f t="shared" ref="I60:I66" si="56">SUM(C60:H60)</f>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="K60" s="21">
         <f t="shared" ref="K60:P60" si="57">IFERROR(K47/$Q47,0)</f>
@@ -5694,7 +5711,7 @@
       </c>
       <c r="S60" s="21">
         <f t="shared" si="51"/>
-        <v>-0.19351372443367973</v>
+        <v>-0.24042371425988171</v>
       </c>
       <c r="T60" s="17">
         <f t="shared" si="52"/>
@@ -5702,23 +5719,23 @@
       </c>
       <c r="U60" s="17">
         <f t="shared" si="53"/>
-        <v>-0.15708225707152404</v>
+        <v>-0.1609001031479739</v>
       </c>
       <c r="V60" s="17">
         <f t="shared" si="54"/>
-        <v>4.7713504997575415E-2</v>
+        <v>6.39203362668571E-2</v>
       </c>
       <c r="W60" s="17">
         <f t="shared" si="54"/>
-        <v>2.4640413624791246E-2</v>
+        <v>4.8100814690733143E-2</v>
       </c>
       <c r="X60" s="22">
         <f t="shared" si="54"/>
-        <v>0.11157539621617044</v>
+        <v>0.12263599978359865</v>
       </c>
       <c r="Y60" s="93">
         <f t="shared" ref="Y60:Y66" si="59">IFERROR(Q60-I60,0)</f>
-        <v>0</v>
+        <v>-1.1102230246251565E-16</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.2">
@@ -5727,31 +5744,31 @@
       </c>
       <c r="C61" s="21">
         <f t="shared" si="48"/>
-        <v>0.25851700229746211</v>
+        <v>0.24271495847497113</v>
       </c>
       <c r="D61" s="17">
         <f t="shared" si="48"/>
-        <v>2.7426795951025072E-2</v>
+        <v>1.0793709545786942E-2</v>
       </c>
       <c r="E61" s="17">
         <f t="shared" si="48"/>
-        <v>0.42820180466278801</v>
+        <v>0.47950071005265654</v>
       </c>
       <c r="F61" s="17">
         <f t="shared" ref="F61:H61" si="60">F48/$I48</f>
-        <v>8.7735315134503056E-2</v>
+        <v>7.5850247806686519E-2</v>
       </c>
       <c r="G61" s="17">
         <f t="shared" si="60"/>
-        <v>0.17225004321476883</v>
+        <v>0.17312631257007452</v>
       </c>
       <c r="H61" s="22">
         <f t="shared" si="60"/>
-        <v>2.5869038739452972E-2</v>
+        <v>1.8014061549824371E-2</v>
       </c>
       <c r="I61" s="17">
         <f t="shared" si="56"/>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="K61" s="21">
         <f t="shared" ref="K61:P61" si="61">IFERROR(K48/$Q48,0)</f>
@@ -5783,31 +5800,31 @@
       </c>
       <c r="S61" s="21">
         <f t="shared" si="51"/>
-        <v>-9.1850335630795449E-2</v>
+        <v>-7.6048291808304469E-2</v>
       </c>
       <c r="T61" s="17">
         <f t="shared" si="52"/>
-        <v>0.13923987071564159</v>
+        <v>0.15587295712087973</v>
       </c>
       <c r="U61" s="17">
         <f t="shared" si="53"/>
-        <v>-0.26153513799612138</v>
+        <v>-0.31283404338598986</v>
       </c>
       <c r="V61" s="17">
         <f t="shared" si="54"/>
-        <v>7.8931351532163602E-2</v>
+        <v>9.0816418859980139E-2</v>
       </c>
       <c r="W61" s="17">
         <f t="shared" si="54"/>
-        <v>-5.5833765481021758E-3</v>
+        <v>-6.4596459034078624E-3</v>
       </c>
       <c r="X61" s="22">
         <f t="shared" si="54"/>
-        <v>0.14079762792721368</v>
+        <v>0.14865260511684228</v>
       </c>
       <c r="Y61" s="93">
         <f t="shared" si="59"/>
-        <v>-1.1102230246251565E-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.2">
@@ -5816,7 +5833,7 @@
       </c>
       <c r="C62" s="21">
         <f t="shared" si="48"/>
-        <v>2.288411587252136E-3</v>
+        <v>0</v>
       </c>
       <c r="D62" s="17">
         <f t="shared" si="48"/>
@@ -5824,7 +5841,7 @@
       </c>
       <c r="E62" s="17">
         <f t="shared" si="48"/>
-        <v>0.66960403778795496</v>
+        <v>0.65479740323452706</v>
       </c>
       <c r="F62" s="17">
         <f t="shared" ref="F62:H62" si="62">F49/$I49</f>
@@ -5832,7 +5849,7 @@
       </c>
       <c r="G62" s="17">
         <f t="shared" si="62"/>
-        <v>0.32810755062479291</v>
+        <v>0.34520259676547288</v>
       </c>
       <c r="H62" s="22">
         <f t="shared" si="62"/>
@@ -5872,7 +5889,7 @@
       </c>
       <c r="S62" s="21">
         <f t="shared" si="51"/>
-        <v>0.16437825507941453</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="T62" s="17">
         <f t="shared" si="52"/>
@@ -5880,7 +5897,7 @@
       </c>
       <c r="U62" s="17">
         <f t="shared" si="53"/>
-        <v>-0.50293737112128833</v>
+        <v>-0.48813073656786043</v>
       </c>
       <c r="V62" s="17">
         <f t="shared" si="54"/>
@@ -5888,7 +5905,7 @@
       </c>
       <c r="W62" s="17">
         <f t="shared" si="54"/>
-        <v>-0.16144088395812625</v>
+        <v>-0.17853593009880622</v>
       </c>
       <c r="X62" s="22">
         <f t="shared" si="54"/>
@@ -5905,7 +5922,7 @@
       </c>
       <c r="C63" s="21">
         <f t="shared" si="48"/>
-        <v>4.587856330206583E-3</v>
+        <v>0</v>
       </c>
       <c r="D63" s="17">
         <f t="shared" si="48"/>
@@ -5913,7 +5930,7 @@
       </c>
       <c r="E63" s="17">
         <f t="shared" si="48"/>
-        <v>0.61899316441862273</v>
+        <v>0.61370368742204418</v>
       </c>
       <c r="F63" s="17">
         <f t="shared" ref="F63:H63" si="64">F50/$I50</f>
@@ -5921,7 +5938,7 @@
       </c>
       <c r="G63" s="17">
         <f t="shared" si="64"/>
-        <v>0.37641897925117063</v>
+        <v>0.38629631257795582</v>
       </c>
       <c r="H63" s="22">
         <f t="shared" si="64"/>
@@ -5929,7 +5946,7 @@
       </c>
       <c r="I63" s="17">
         <f t="shared" si="56"/>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="K63" s="21">
         <f t="shared" ref="K63:P63" si="65">IFERROR(K50/$Q50,0)</f>
@@ -5961,7 +5978,7 @@
       </c>
       <c r="S63" s="21">
         <f t="shared" si="51"/>
-        <v>0.16207881033646007</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="T63" s="17">
         <f t="shared" si="52"/>
@@ -5969,7 +5986,7 @@
       </c>
       <c r="U63" s="17">
         <f t="shared" si="53"/>
-        <v>-0.4523264977519561</v>
+        <v>-0.44703702075537755</v>
       </c>
       <c r="V63" s="17">
         <f t="shared" si="54"/>
@@ -5977,7 +5994,7 @@
       </c>
       <c r="W63" s="17">
         <f t="shared" si="54"/>
-        <v>-0.20975231258450397</v>
+        <v>-0.21962964591128917</v>
       </c>
       <c r="X63" s="22">
         <f t="shared" si="54"/>
@@ -5985,7 +6002,7 @@
       </c>
       <c r="Y63" s="93">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>-1.1102230246251565E-16</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.2">
@@ -6261,31 +6278,31 @@
       </c>
       <c r="C67" s="17">
         <f t="shared" si="48"/>
-        <v>0.34014589651376137</v>
+        <v>0.34319674165668834</v>
       </c>
       <c r="D67" s="17">
         <f t="shared" si="48"/>
-        <v>1.4312043447043345E-3</v>
+        <v>5.9097921037273111E-4</v>
       </c>
       <c r="E67" s="17">
         <f t="shared" si="48"/>
-        <v>0.32555527709023607</v>
+        <v>0.32026608543679358</v>
       </c>
       <c r="F67" s="17">
         <f>F54/$I54</f>
-        <v>0.10440280204815867</v>
+        <v>0.10572933030201728</v>
       </c>
       <c r="G67" s="17">
         <f>G54/$I54</f>
-        <v>0.17881290722256646</v>
+        <v>0.17681947842273657</v>
       </c>
       <c r="H67" s="17">
         <f>H54/$I54</f>
-        <v>4.9651912780573029E-2</v>
+        <v>5.3397384971391529E-2</v>
       </c>
       <c r="I67" s="17">
         <f>SUM(C67:H67)</f>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="K67" s="17">
         <f>IFERROR(K54/$N54,0)</f>
@@ -6313,27 +6330,27 @@
       </c>
       <c r="S67" s="17">
         <f t="shared" si="51"/>
-        <v>0.65985410348623863</v>
+        <v>0.65680325834331166</v>
       </c>
       <c r="T67" s="17">
         <f t="shared" si="52"/>
-        <v>0.99856879565529566</v>
+        <v>0.99940902078962723</v>
       </c>
       <c r="U67" s="17">
         <f t="shared" si="53"/>
-        <v>0.67444472290976387</v>
+        <v>0.67973391456320642</v>
       </c>
       <c r="V67" s="17">
         <f t="shared" si="54"/>
-        <v>0.89559719795184134</v>
+        <v>0.89427066969798275</v>
       </c>
       <c r="W67" s="17">
         <f t="shared" si="54"/>
-        <v>0.82118709277743351</v>
+        <v>0.8231805215772634</v>
       </c>
       <c r="X67" s="17">
         <f t="shared" si="54"/>
-        <v>0.95034808721942698</v>
+        <v>0.94660261502860843</v>
       </c>
     </row>
   </sheetData>
@@ -6517,22 +6534,22 @@
         <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6748,7 +6765,7 @@
   <sheetData>
     <row r="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="2:26" x14ac:dyDescent="0.25">
@@ -6759,7 +6776,7 @@
         <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>40</v>
@@ -6776,7 +6793,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>271316.59622341208</v>
+        <v>311650.04052777553</v>
       </c>
     </row>
     <row r="4" spans="2:26" x14ac:dyDescent="0.25">
@@ -6790,10 +6807,10 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>286013.62997391314</v>
+        <v>356089.44833557063</v>
       </c>
       <c r="P4" s="74" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Q4" s="74" t="s">
         <v>5</v>
@@ -6810,10 +6827,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1012169.4021083413</v>
+        <v>1229608.9493126601</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>5</v>
@@ -6825,19 +6842,19 @@
         <v>0</v>
       </c>
       <c r="S5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="T5" t="s">
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="W5" t="s">
         <v>2</v>
       </c>
       <c r="Y5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Z5" t="s">
         <v>4</v>
@@ -6854,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>603.94457618764409</v>
+        <v>496.28557282869974</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>3</v>
@@ -6904,7 +6921,7 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>608665.62727682234</v>
+        <v>663899.41953010834</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>6</v>
@@ -6913,49 +6930,49 @@
         <v>1</v>
       </c>
       <c r="J7" s="85">
-        <v>557330.22619732516</v>
+        <v>667739.48886334617</v>
       </c>
       <c r="K7" s="85">
-        <v>1012773.346684529</v>
+        <v>1230105.2348854889</v>
       </c>
       <c r="L7" s="85">
-        <v>1197300.8246903126</v>
+        <v>1343636.9371095512</v>
       </c>
       <c r="M7" s="85">
-        <v>2767404.3975721668</v>
+        <v>3241481.6608583862</v>
       </c>
       <c r="P7" s="75">
         <v>1</v>
       </c>
-      <c r="Q7">
-        <v>271316.59622341208</v>
-      </c>
-      <c r="R7">
-        <v>286013.62997391314</v>
-      </c>
-      <c r="S7">
-        <v>557330.22619732516</v>
-      </c>
-      <c r="T7">
-        <v>1012169.4021083413</v>
-      </c>
-      <c r="U7">
-        <v>603.94457618764409</v>
-      </c>
-      <c r="V7">
-        <v>1012773.346684529</v>
-      </c>
-      <c r="W7">
-        <v>608665.62727682234</v>
-      </c>
-      <c r="X7">
-        <v>588635.19741349027</v>
-      </c>
-      <c r="Y7">
-        <v>1197300.8246903126</v>
-      </c>
-      <c r="Z7">
-        <v>2767404.3975721668</v>
+      <c r="Q7" s="97">
+        <v>311650.04052777553</v>
+      </c>
+      <c r="R7" s="97">
+        <v>356089.44833557063</v>
+      </c>
+      <c r="S7" s="97">
+        <v>667739.48886334617</v>
+      </c>
+      <c r="T7" s="97">
+        <v>1229608.9493126601</v>
+      </c>
+      <c r="U7" s="97">
+        <v>496.28557282869974</v>
+      </c>
+      <c r="V7" s="97">
+        <v>1230105.2348854889</v>
+      </c>
+      <c r="W7" s="97">
+        <v>663899.41953010834</v>
+      </c>
+      <c r="X7" s="97">
+        <v>679737.51757944282</v>
+      </c>
+      <c r="Y7" s="97">
+        <v>1343636.9371095512</v>
+      </c>
+      <c r="Z7" s="97">
+        <v>3241481.6608583862</v>
       </c>
     </row>
     <row r="8" spans="2:26" x14ac:dyDescent="0.25">
@@ -6969,7 +6986,7 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>588635.19741349027</v>
+        <v>679737.51757944282</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>7</v>
@@ -6978,46 +6995,47 @@
         <v>2</v>
       </c>
       <c r="J8" s="85">
-        <v>124392.50344448088</v>
+        <v>114592.55289354955</v>
       </c>
       <c r="K8" s="85">
-        <v>227294.5588336706</v>
+        <v>286903.59631397587</v>
       </c>
       <c r="L8" s="85">
-        <v>279370.49790520186</v>
+        <v>303270.18710574182</v>
       </c>
       <c r="M8" s="85">
-        <v>631057.56018335337</v>
+        <v>704766.33631326724</v>
       </c>
       <c r="P8" s="75">
         <v>2</v>
       </c>
-      <c r="Q8">
-        <v>89626.740726589473</v>
-      </c>
-      <c r="R8">
-        <v>34765.762717891412</v>
-      </c>
-      <c r="S8">
-        <v>124392.50344448088</v>
-      </c>
-      <c r="T8">
-        <v>227294.5588336706</v>
-      </c>
-      <c r="V8">
-        <v>227294.5588336706</v>
-      </c>
-      <c r="W8">
-        <v>204304.20592620916</v>
-      </c>
-      <c r="X8">
-        <v>75066.291978992711</v>
-      </c>
-      <c r="Y8">
-        <v>279370.49790520186</v>
-      </c>
-      <c r="Z8">
-        <v>631057.56018335349</v>
+      <c r="Q8" s="97">
+        <v>83561.221108939819</v>
+      </c>
+      <c r="R8" s="97">
+        <v>31031.331784609742</v>
+      </c>
+      <c r="S8" s="97">
+        <v>114592.55289354955</v>
+      </c>
+      <c r="T8" s="97">
+        <v>286903.59631397587</v>
+      </c>
+      <c r="U8" s="97"/>
+      <c r="V8" s="97">
+        <v>286903.59631397587</v>
+      </c>
+      <c r="W8" s="97">
+        <v>230858.03226023554</v>
+      </c>
+      <c r="X8" s="97">
+        <v>72412.154845506258</v>
+      </c>
+      <c r="Y8" s="97">
+        <v>303270.18710574182</v>
+      </c>
+      <c r="Z8" s="97">
+        <v>704766.33631326724</v>
       </c>
     </row>
     <row r="9" spans="2:26" x14ac:dyDescent="0.25">
@@ -7031,7 +7049,7 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>89626.740726589473</v>
+        <v>83561.221108939819</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>8</v>
@@ -7040,49 +7058,49 @@
         <v>3</v>
       </c>
       <c r="J9" s="85">
-        <v>64173.937822535387</v>
+        <v>68345.75347247794</v>
       </c>
       <c r="K9" s="85">
-        <v>92621.767416518094</v>
+        <v>90646.683137778877</v>
       </c>
       <c r="L9" s="85">
-        <v>167120.28099272039</v>
+        <v>198575.94101364535</v>
       </c>
       <c r="M9" s="85">
-        <v>323915.98623177386</v>
+        <v>357568.37762390217</v>
       </c>
       <c r="P9" s="75">
         <v>3</v>
       </c>
-      <c r="Q9">
-        <v>55794.542626377515</v>
-      </c>
-      <c r="R9">
-        <v>8379.3951961578732</v>
-      </c>
-      <c r="S9">
-        <v>64173.937822535387</v>
-      </c>
-      <c r="T9">
-        <v>83737.789756864193</v>
-      </c>
-      <c r="U9">
-        <v>8883.9776596539086</v>
-      </c>
-      <c r="V9">
-        <v>92621.767416518094</v>
-      </c>
-      <c r="W9">
-        <v>138701.40986357236</v>
-      </c>
-      <c r="X9">
-        <v>28418.871129148032</v>
-      </c>
-      <c r="Y9">
-        <v>167120.28099272039</v>
-      </c>
-      <c r="Z9">
-        <v>323915.98623177392</v>
+      <c r="Q9" s="97">
+        <v>61904.494709690123</v>
+      </c>
+      <c r="R9" s="97">
+        <v>6441.2587627878174</v>
+      </c>
+      <c r="S9" s="97">
+        <v>68345.75347247794</v>
+      </c>
+      <c r="T9" s="97">
+        <v>86787.19392694821</v>
+      </c>
+      <c r="U9" s="97">
+        <v>3859.4892108306631</v>
+      </c>
+      <c r="V9" s="97">
+        <v>90646.683137778877</v>
+      </c>
+      <c r="W9" s="97">
+        <v>171454.29096303752</v>
+      </c>
+      <c r="X9" s="97">
+        <v>27121.650050607841</v>
+      </c>
+      <c r="Y9" s="97">
+        <v>198575.94101364535</v>
+      </c>
+      <c r="Z9" s="97">
+        <v>357568.37762390217</v>
       </c>
     </row>
     <row r="10" spans="2:26" x14ac:dyDescent="0.25">
@@ -7096,7 +7114,7 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>34765.762717891412</v>
+        <v>31031.331784609742</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>9</v>
@@ -7105,40 +7123,43 @@
         <v>4</v>
       </c>
       <c r="J10" s="85">
-        <v>211570.34375830065</v>
+        <v>255989.88428071633</v>
       </c>
       <c r="K10" s="85">
-        <v>1475.6137896048408</v>
+        <v>0</v>
       </c>
       <c r="L10" s="85">
-        <v>431774.14292043669</v>
+        <v>485574.30636942881</v>
       </c>
       <c r="M10" s="85">
-        <v>644820.10046834219</v>
+        <v>741564.19065014517</v>
       </c>
       <c r="P10" s="75">
         <v>4</v>
       </c>
-      <c r="Q10">
-        <v>211570.34375830065</v>
-      </c>
-      <c r="S10">
-        <v>211570.34375830065</v>
-      </c>
-      <c r="T10">
-        <v>1475.6137896048408</v>
-      </c>
-      <c r="V10">
-        <v>1475.6137896048408</v>
-      </c>
-      <c r="W10">
-        <v>431774.14292043669</v>
-      </c>
-      <c r="Y10">
-        <v>431774.14292043669</v>
-      </c>
-      <c r="Z10">
-        <v>644820.10046834219</v>
+      <c r="Q10" s="97">
+        <v>255989.88428071633</v>
+      </c>
+      <c r="R10" s="97"/>
+      <c r="S10" s="97">
+        <v>255989.88428071633</v>
+      </c>
+      <c r="T10" s="97">
+        <v>0</v>
+      </c>
+      <c r="U10" s="97"/>
+      <c r="V10" s="97">
+        <v>0</v>
+      </c>
+      <c r="W10" s="97">
+        <v>485574.30636942881</v>
+      </c>
+      <c r="X10" s="97"/>
+      <c r="Y10" s="97">
+        <v>485574.30636942881</v>
+      </c>
+      <c r="Z10" s="97">
+        <v>741564.19065014517</v>
       </c>
     </row>
     <row r="11" spans="2:26" x14ac:dyDescent="0.25">
@@ -7152,7 +7173,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>227294.5588336706</v>
+        <v>286903.59631397587</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>10</v>
@@ -7161,40 +7182,43 @@
         <v>5</v>
       </c>
       <c r="J11" s="85">
-        <v>332378.65690771444</v>
+        <v>365408.67686414684</v>
       </c>
       <c r="K11" s="85">
-        <v>4051.085649701276</v>
+        <v>0</v>
       </c>
       <c r="L11" s="85">
-        <v>546572.11236746656</v>
+        <v>580519.78521612787</v>
       </c>
       <c r="M11" s="85">
-        <v>883001.8549248823</v>
+        <v>945928.46208027471</v>
       </c>
       <c r="P11" s="75">
         <v>5</v>
       </c>
-      <c r="Q11">
-        <v>332378.65690771444</v>
-      </c>
-      <c r="S11">
-        <v>332378.65690771444</v>
-      </c>
-      <c r="T11">
-        <v>4051.085649701276</v>
-      </c>
-      <c r="V11">
-        <v>4051.085649701276</v>
-      </c>
-      <c r="W11">
-        <v>546572.11236746656</v>
-      </c>
-      <c r="Y11">
-        <v>546572.11236746656</v>
-      </c>
-      <c r="Z11">
-        <v>883001.8549248823</v>
+      <c r="Q11" s="97">
+        <v>365408.67686414684</v>
+      </c>
+      <c r="R11" s="97"/>
+      <c r="S11" s="97">
+        <v>365408.67686414684</v>
+      </c>
+      <c r="T11" s="97">
+        <v>0</v>
+      </c>
+      <c r="U11" s="97"/>
+      <c r="V11" s="97">
+        <v>0</v>
+      </c>
+      <c r="W11" s="97">
+        <v>580519.78521612787</v>
+      </c>
+      <c r="X11" s="97"/>
+      <c r="Y11" s="97">
+        <v>580519.78521612787</v>
+      </c>
+      <c r="Z11" s="97">
+        <v>945928.46208027471</v>
       </c>
     </row>
     <row r="12" spans="2:26" x14ac:dyDescent="0.25">
@@ -7208,7 +7232,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>204304.20592620916</v>
+        <v>230858.03226023554</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>11</v>
@@ -7217,40 +7241,45 @@
         <v>6</v>
       </c>
       <c r="J12" s="85">
-        <v>17630.20679</v>
+        <v>74995.978217831318</v>
       </c>
       <c r="K12" s="85">
-        <v>123094.58867</v>
+        <v>27888.048166248853</v>
       </c>
       <c r="L12" s="85">
-        <v>17712.811699999998</v>
+        <v>64186.242709321567</v>
       </c>
       <c r="M12" s="85">
-        <v>158437.60715999999</v>
+        <v>167070.26909340173</v>
       </c>
       <c r="P12" s="75">
         <v>6</v>
       </c>
-      <c r="Q12">
-        <v>17630.20679</v>
-      </c>
-      <c r="S12">
-        <v>17630.20679</v>
-      </c>
-      <c r="T12">
-        <v>123094.58867</v>
-      </c>
-      <c r="V12">
-        <v>123094.58867</v>
-      </c>
-      <c r="W12">
-        <v>17712.811699999998</v>
-      </c>
-      <c r="Y12">
-        <v>17712.811699999998</v>
-      </c>
-      <c r="Z12">
-        <v>158437.60715999999</v>
+      <c r="Q12" s="97">
+        <v>74995.978217831318</v>
+      </c>
+      <c r="R12" s="97"/>
+      <c r="S12" s="97">
+        <v>74995.978217831318</v>
+      </c>
+      <c r="T12" s="97">
+        <v>27888.048166248853</v>
+      </c>
+      <c r="U12" s="97"/>
+      <c r="V12" s="97">
+        <v>27888.048166248853</v>
+      </c>
+      <c r="W12" s="97">
+        <v>59294.409690902619</v>
+      </c>
+      <c r="X12" s="97">
+        <v>4891.8330184189444</v>
+      </c>
+      <c r="Y12" s="97">
+        <v>64186.242709321567</v>
+      </c>
+      <c r="Z12" s="97">
+        <v>167070.26909340176</v>
       </c>
     </row>
     <row r="13" spans="2:26" x14ac:dyDescent="0.25">
@@ -7264,7 +7293,7 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>75066.291978992711</v>
+        <v>72412.154845506258</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>12</v>
@@ -7273,40 +7302,43 @@
         <v>7</v>
       </c>
       <c r="J13" s="85">
-        <v>85466.730259999997</v>
+        <v>387248.05504112464</v>
       </c>
       <c r="K13" s="85">
-        <v>665066.56470999995</v>
+        <v>156147.04247572814</v>
       </c>
       <c r="L13" s="85">
-        <v>64858.529419999999</v>
+        <v>169505.952664399</v>
       </c>
       <c r="M13" s="85">
-        <v>815391.82438999997</v>
+        <v>712901.05018125172</v>
       </c>
       <c r="P13" s="75">
         <v>7</v>
       </c>
-      <c r="Q13">
-        <v>85466.730259999997</v>
-      </c>
-      <c r="S13">
-        <v>85466.730259999997</v>
-      </c>
-      <c r="T13">
-        <v>665066.56470999995</v>
-      </c>
-      <c r="V13">
-        <v>665066.56470999995</v>
-      </c>
-      <c r="W13">
-        <v>64858.529419999999</v>
-      </c>
-      <c r="Y13">
-        <v>64858.529419999999</v>
-      </c>
-      <c r="Z13">
-        <v>815391.82438999997</v>
+      <c r="Q13" s="97">
+        <v>387248.05504112464</v>
+      </c>
+      <c r="R13" s="97"/>
+      <c r="S13" s="97">
+        <v>387248.05504112464</v>
+      </c>
+      <c r="T13" s="97">
+        <v>156147.04247572814</v>
+      </c>
+      <c r="U13" s="97"/>
+      <c r="V13" s="97">
+        <v>156147.04247572814</v>
+      </c>
+      <c r="W13" s="97">
+        <v>169505.952664399</v>
+      </c>
+      <c r="X13" s="97"/>
+      <c r="Y13" s="97">
+        <v>169505.952664399</v>
+      </c>
+      <c r="Z13" s="97">
+        <v>712901.05018125172</v>
       </c>
     </row>
     <row r="14" spans="2:26" x14ac:dyDescent="0.25">
@@ -7320,7 +7352,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>55794.542626377515</v>
+        <v>61904.494709690123</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -7329,40 +7361,37 @@
         <v>8</v>
       </c>
       <c r="J14" s="85">
-        <v>121625.49533999999</v>
+        <v>251728.81883796302</v>
       </c>
       <c r="K14" s="85">
-        <v>138048.92214000001</v>
-      </c>
-      <c r="L14" s="85">
-        <v>145623.69245999999</v>
-      </c>
+        <v>60599.900261288341</v>
+      </c>
+      <c r="L14" s="85"/>
       <c r="M14" s="85">
-        <v>405298.10993999999</v>
+        <v>312328.71909925138</v>
       </c>
       <c r="P14" s="75">
         <v>8</v>
       </c>
-      <c r="Q14">
-        <v>121625.49533999999</v>
-      </c>
-      <c r="S14">
-        <v>121625.49533999999</v>
-      </c>
-      <c r="T14">
-        <v>138048.92214000001</v>
-      </c>
-      <c r="V14">
-        <v>138048.92214000001</v>
-      </c>
-      <c r="W14">
-        <v>145623.69245999999</v>
-      </c>
-      <c r="Y14">
-        <v>145623.69245999999</v>
-      </c>
-      <c r="Z14">
-        <v>405298.10993999999</v>
+      <c r="Q14" s="97">
+        <v>251728.81883796302</v>
+      </c>
+      <c r="R14" s="97"/>
+      <c r="S14" s="97">
+        <v>251728.81883796302</v>
+      </c>
+      <c r="T14" s="97">
+        <v>60599.900261288341</v>
+      </c>
+      <c r="U14" s="97"/>
+      <c r="V14" s="97">
+        <v>60599.900261288341</v>
+      </c>
+      <c r="W14" s="97"/>
+      <c r="X14" s="97"/>
+      <c r="Y14" s="97"/>
+      <c r="Z14" s="97">
+        <v>312328.71909925138</v>
       </c>
     </row>
     <row r="15" spans="2:26" x14ac:dyDescent="0.25">
@@ -7376,55 +7405,55 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>8379.3951961578732</v>
+        <v>6441.2587627878174</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J15" s="1">
-        <v>1514568.1005203566</v>
-      </c>
-      <c r="K15" s="1">
-        <v>2264426.4478940237</v>
-      </c>
-      <c r="L15" s="1">
-        <v>2850332.892456138</v>
-      </c>
-      <c r="M15" s="1">
-        <v>6629327.4408705179</v>
+      <c r="J15" s="85">
+        <v>2186049.2084711557</v>
+      </c>
+      <c r="K15" s="85">
+        <v>1852290.5052405091</v>
+      </c>
+      <c r="L15" s="85">
+        <v>3145269.3521882156</v>
+      </c>
+      <c r="M15" s="85">
+        <v>7183609.0658998815</v>
       </c>
       <c r="P15" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="Q15">
-        <v>1185409.312632394</v>
-      </c>
-      <c r="R15">
-        <v>329158.78788796242</v>
-      </c>
-      <c r="S15">
-        <v>1514568.1005203566</v>
-      </c>
-      <c r="T15">
-        <v>2254938.5256581819</v>
-      </c>
-      <c r="U15">
-        <v>9487.9222358415536</v>
-      </c>
-      <c r="V15">
-        <v>2264426.4478940237</v>
-      </c>
-      <c r="W15">
-        <v>2158212.5319345072</v>
-      </c>
-      <c r="X15">
-        <v>692120.36052163108</v>
-      </c>
-      <c r="Y15">
-        <v>2850332.892456138</v>
-      </c>
-      <c r="Z15">
-        <v>6629327.4408705179</v>
+      <c r="Q15" s="97">
+        <v>1792487.1695881877</v>
+      </c>
+      <c r="R15" s="97">
+        <v>393562.03888296819</v>
+      </c>
+      <c r="S15" s="97">
+        <v>2186049.2084711557</v>
+      </c>
+      <c r="T15" s="97">
+        <v>1847934.7304568496</v>
+      </c>
+      <c r="U15" s="97">
+        <v>4355.7747836593626</v>
+      </c>
+      <c r="V15" s="97">
+        <v>1852290.5052405091</v>
+      </c>
+      <c r="W15" s="97">
+        <v>2361106.1966942395</v>
+      </c>
+      <c r="X15" s="97">
+        <v>784163.15549397597</v>
+      </c>
+      <c r="Y15" s="97">
+        <v>3145269.3521882156</v>
+      </c>
+      <c r="Z15" s="97">
+        <v>7183609.0658998815</v>
       </c>
     </row>
     <row r="16" spans="2:26" x14ac:dyDescent="0.25">
@@ -7438,10 +7467,10 @@
         <v>0</v>
       </c>
       <c r="E16" s="72">
-        <v>83737.789756864193</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+        <v>86787.19392694821</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="72">
         <v>3</v>
       </c>
@@ -7452,10 +7481,10 @@
         <v>1</v>
       </c>
       <c r="E17" s="71">
-        <v>8883.9776596539086</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+        <v>3859.4892108306631</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="72">
         <v>3</v>
       </c>
@@ -7466,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="E18" s="71">
-        <v>138701.40986357236</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+        <v>171454.29096303752</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="72">
         <v>3</v>
       </c>
@@ -7480,10 +7509,10 @@
         <v>1</v>
       </c>
       <c r="E19" s="71">
-        <v>28418.871129148032</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+        <v>27121.650050607841</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="72">
         <v>4</v>
       </c>
@@ -7494,10 +7523,10 @@
         <v>0</v>
       </c>
       <c r="E20" s="71">
-        <v>211570.34375830065</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+        <v>255989.88428071633</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" s="72">
         <v>4</v>
       </c>
@@ -7508,10 +7537,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="71">
-        <v>1475.6137896048408</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="72">
         <v>4</v>
       </c>
@@ -7522,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="71">
-        <v>431774.14292043669</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+        <v>485574.30636942881</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="72">
         <v>5</v>
       </c>
@@ -7536,10 +7565,10 @@
         <v>0</v>
       </c>
       <c r="E23" s="71">
-        <v>332378.65690771444</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+        <v>365408.67686414684</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" s="72">
         <v>5</v>
       </c>
@@ -7550,10 +7579,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="71">
-        <v>4051.085649701276</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" s="72">
         <v>5</v>
       </c>
@@ -7564,13 +7593,22 @@
         <v>0</v>
       </c>
       <c r="E25" s="72">
-        <v>546572.11236746656</v>
+        <v>580519.78521612787</v>
+      </c>
+      <c r="I25" t="s">
+        <v>79</v>
       </c>
       <c r="J25" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="K25" t="s">
+        <v>81</v>
+      </c>
+      <c r="P25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
         <v>6</v>
       </c>
@@ -7583,20 +7621,33 @@
       <c r="E26" s="2">
         <v>17630.20679</v>
       </c>
-      <c r="G26" s="70">
+      <c r="I26" s="1">
         <v>6</v>
       </c>
-      <c r="H26" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="70">
-        <v>72222.520364584547</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>17630.20679</v>
+      </c>
+      <c r="M26" s="2">
+        <v>6</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2">
+        <v>74995.978217831318</v>
+      </c>
+      <c r="Q26">
+        <f>P26/SUM($P$26:$P$29)</f>
+        <v>0.44888883357160519</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="2">
         <v>6</v>
       </c>
@@ -7609,20 +7660,33 @@
       <c r="E27" s="2">
         <v>123094.58867</v>
       </c>
-      <c r="G27" s="70">
+      <c r="I27" s="1">
         <v>6</v>
       </c>
-      <c r="H27" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="70">
-        <v>0</v>
-      </c>
-      <c r="J27" s="70">
-        <v>33940.420274901968</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
+        <v>123094.58867</v>
+      </c>
+      <c r="M27" s="2">
+        <v>6</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O27" s="2">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2">
+        <v>27888.048166248853</v>
+      </c>
+      <c r="Q27">
+        <f>P27/SUM($P$26:$P$29)</f>
+        <v>0.16692406325543088</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" s="2">
         <v>6</v>
       </c>
@@ -7635,20 +7699,33 @@
       <c r="E28" s="2">
         <v>17712.811699999998</v>
       </c>
-      <c r="G28" s="70">
+      <c r="I28" s="1">
         <v>6</v>
       </c>
-      <c r="H28" s="70" t="s">
+      <c r="J28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I28" s="70">
-        <v>0</v>
-      </c>
-      <c r="J28" s="70">
-        <v>47472.563701622763</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K28" s="1">
+        <v>17712.811699999998</v>
+      </c>
+      <c r="M28" s="2">
+        <v>6</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="O28" s="2">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2">
+        <v>59294.409690902619</v>
+      </c>
+      <c r="Q28">
+        <f>P28/SUM($P$26:$P$29)</f>
+        <v>0.35490701016201559</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" s="2">
         <v>7</v>
       </c>
@@ -7661,20 +7738,33 @@
       <c r="E29" s="2">
         <v>85466.730259999997</v>
       </c>
-      <c r="G29" s="2">
+      <c r="I29" s="1">
+        <v>7</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>85466.730259999997</v>
+      </c>
+      <c r="M29" s="2">
         <v>6</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="N29" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I29" s="2">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2">
-        <v>3084.7727136344511</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="O29" s="2">
+        <v>1</v>
+      </c>
+      <c r="P29" s="2">
+        <v>4891.8330184189444</v>
+      </c>
+      <c r="Q29">
+        <f>P29/SUM($P$26:$P$29)</f>
+        <v>2.928009301094818E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B30" s="2">
         <v>7</v>
       </c>
@@ -7687,20 +7777,33 @@
       <c r="E30" s="2">
         <v>665066.56470999995</v>
       </c>
-      <c r="G30" s="2">
+      <c r="I30" s="1">
         <v>7</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2">
-        <v>376623.4859888684</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1">
+        <v>665066.56470999995</v>
+      </c>
+      <c r="M30" s="2">
+        <v>7</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2">
+        <v>387248.05504112464</v>
+      </c>
+      <c r="Q30">
+        <f>P30/SUM($P$30:$P$32)</f>
+        <v>0.54320028697204004</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B31" s="2">
         <v>7</v>
       </c>
@@ -7713,20 +7816,33 @@
       <c r="E31" s="2">
         <v>64858.529419999999</v>
       </c>
-      <c r="G31" s="2">
+      <c r="I31" s="1">
         <v>7</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I31" s="2">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2">
-        <v>143164.10318128043</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K31" s="1">
+        <v>64858.529419999999</v>
+      </c>
+      <c r="M31" s="2">
+        <v>7</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O31" s="2">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2">
+        <v>156147.04247572814</v>
+      </c>
+      <c r="Q31">
+        <f>P31/SUM($P$30:$P$32)</f>
+        <v>0.21903045652132017</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B32" s="2">
         <v>8</v>
       </c>
@@ -7739,20 +7855,33 @@
       <c r="E32" s="2">
         <v>121625.49533999999</v>
       </c>
-      <c r="G32" s="70">
+      <c r="I32" s="1">
+        <v>8</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
+        <v>121625.49533999999</v>
+      </c>
+      <c r="M32" s="2">
         <v>7</v>
       </c>
-      <c r="H32" s="70" t="s">
+      <c r="N32" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I32" s="70">
-        <v>0</v>
-      </c>
-      <c r="J32" s="70">
-        <v>200582.18820823389</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="O32" s="2">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2">
+        <v>169505.952664399</v>
+      </c>
+      <c r="Q32">
+        <f>P32/SUM($P$30:$P$32)</f>
+        <v>0.23776925650663988</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="2">
         <v>8</v>
       </c>
@@ -7765,20 +7894,33 @@
       <c r="E33" s="2">
         <v>138048.92214000001</v>
       </c>
-      <c r="G33" s="70">
+      <c r="I33" s="1">
         <v>8</v>
       </c>
-      <c r="H33" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="I33" s="70">
-        <v>0</v>
-      </c>
-      <c r="J33" s="70">
-        <v>195874.13664410671</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>138048.92214000001</v>
+      </c>
+      <c r="M33" s="2">
+        <v>8</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2">
+        <v>251728.81883796302</v>
+      </c>
+      <c r="Q33">
+        <f>P33/SUM($P$33:$P$35)</f>
+        <v>0.6702113949827051</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B34" s="2">
         <v>8</v>
       </c>
@@ -7791,59 +7933,80 @@
       <c r="E34" s="2">
         <v>145623.69245999999</v>
       </c>
-      <c r="G34" s="70">
+      <c r="I34" s="1">
         <v>8</v>
       </c>
-      <c r="H34" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="70">
-        <v>0</v>
-      </c>
-      <c r="J34" s="70">
-        <v>49646.134411898798</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G35" s="70">
+      <c r="J34" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K34" s="1">
+        <v>145623.69245999999</v>
+      </c>
+      <c r="M34" s="2">
         <v>8</v>
       </c>
-      <c r="H35" s="70" t="s">
+      <c r="N34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O34" s="2">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2">
+        <v>60599.900261288341</v>
+      </c>
+      <c r="Q34">
+        <f>P34/SUM($P$33:$P$35)</f>
+        <v>0.16134324181640253</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B35" s="70"/>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="M35" s="70">
+        <v>8</v>
+      </c>
+      <c r="N35" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="I35" s="70">
-        <v>0</v>
-      </c>
-      <c r="J35" s="70">
-        <v>68040.576635037243</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="O35" s="70">
+        <v>0</v>
+      </c>
+      <c r="P35" s="70">
+        <v>63267.429701619018</v>
+      </c>
+      <c r="Q35">
+        <f>P35/SUM($P$33:$P$35)</f>
+        <v>0.16844536320089235</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
       <c r="G36" s="70"/>
       <c r="H36" s="70"/>
       <c r="I36" s="70"/>
       <c r="J36" s="70"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B37" s="70" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G37" s="70"/>
       <c r="H37" s="70"/>
       <c r="I37" s="70"/>
       <c r="J37" s="70"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B39" s="73" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>38</v>
       </c>
@@ -7851,13 +8014,13 @@
         <v>39</v>
       </c>
       <c r="D41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E41" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B42">
         <v>1</v>
       </c>
@@ -7868,10 +8031,10 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>46461.708278236401</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+        <v>42440.120223558901</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B43">
         <v>1</v>
       </c>
@@ -7881,11 +8044,11 @@
       <c r="D43">
         <v>1</v>
       </c>
-      <c r="E43">
-        <v>31976.636166590401</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E43" s="98">
+        <v>34949.717585521903</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B44">
         <v>1</v>
       </c>
@@ -7895,11 +8058,11 @@
       <c r="D44">
         <v>0</v>
       </c>
-      <c r="E44">
-        <v>170412.474047856</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E44" s="98">
+        <v>189035.97553224201</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B45">
         <v>1</v>
       </c>
@@ -7909,11 +8072,11 @@
       <c r="D45">
         <v>1</v>
       </c>
-      <c r="E45">
-        <v>11.8838844452088</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E45" s="98">
+        <v>11.895122060386599</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B46">
         <v>1</v>
       </c>
@@ -7923,11 +8086,11 @@
       <c r="D46">
         <v>0</v>
       </c>
-      <c r="E46">
-        <v>109732.720466367</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E46" s="98">
+        <v>127025.50700007399</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B47">
         <v>1</v>
       </c>
@@ -7938,10 +8101,10 @@
         <v>1</v>
       </c>
       <c r="E47">
-        <v>74913.947952794697</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+        <v>73855.196489790207</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B48">
         <v>2</v>
       </c>
@@ -7951,8 +8114,8 @@
       <c r="D48">
         <v>0</v>
       </c>
-      <c r="E48">
-        <v>17785.910240052999</v>
+      <c r="E48" s="98">
+        <v>18151.648592629001</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
@@ -7965,8 +8128,8 @@
       <c r="D49">
         <v>1</v>
       </c>
-      <c r="E49">
-        <v>7726.3175108171799</v>
+      <c r="E49" s="98">
+        <v>6812.8480415026997</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
@@ -7979,8 +8142,8 @@
       <c r="D50">
         <v>0</v>
       </c>
-      <c r="E50">
-        <v>45440.773548626799</v>
+      <c r="E50" s="98">
+        <v>53435.401330074703</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.25">
@@ -7993,8 +8156,8 @@
       <c r="D51">
         <v>0</v>
       </c>
-      <c r="E51">
-        <v>51386.6116113678</v>
+      <c r="E51" s="98">
+        <v>58618.953143026301</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
@@ -8007,8 +8170,8 @@
       <c r="D52">
         <v>1</v>
       </c>
-      <c r="E52">
-        <v>22494.757345504499</v>
+      <c r="E52" s="98">
+        <v>23297.767900950501</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.25">
@@ -8021,8 +8184,8 @@
       <c r="D53">
         <v>0</v>
       </c>
-      <c r="E53">
-        <v>7345.5100432113104</v>
+      <c r="E53" s="98">
+        <v>8720.9887555641799</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
@@ -8035,8 +8198,8 @@
       <c r="D54">
         <v>1</v>
       </c>
-      <c r="E54">
-        <v>410.16883116312903</v>
+      <c r="E54" s="98">
+        <v>806.16615826191799</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
@@ -8049,8 +8212,8 @@
       <c r="D55">
         <v>0</v>
       </c>
-      <c r="E55">
-        <v>14164.3070959255</v>
+      <c r="E55" s="98">
+        <v>16156.818333618099</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
@@ -8063,8 +8226,8 @@
       <c r="D56">
         <v>0</v>
       </c>
-      <c r="E56">
-        <v>26540.497260250198</v>
+      <c r="E56" s="98">
+        <v>37665.217608869498</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.25">
@@ -8077,8 +8240,8 @@
       <c r="D57">
         <v>1</v>
       </c>
-      <c r="E57">
-        <v>781.52700703979394</v>
+      <c r="E57" s="98">
+        <v>1273.4484078276701</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.25">
@@ -8091,8 +8254,8 @@
       <c r="D58">
         <v>0</v>
       </c>
-      <c r="E58">
-        <v>37002.563173153903</v>
+      <c r="E58" s="98">
+        <v>29363.848703914198</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.25">
@@ -8100,27 +8263,27 @@
         <v>4</v>
       </c>
       <c r="C59" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
-      <c r="E59">
-        <v>42.625773559872798</v>
+      <c r="E59" s="98">
+        <v>97455.557694488802</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C60" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
-      <c r="E60">
-        <v>79390.441029884198</v>
+      <c r="E60" s="98">
+        <v>77753.579838162696</v>
       </c>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.25">
@@ -8128,13 +8291,13 @@
         <v>5</v>
       </c>
       <c r="C61" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>78408.972944196896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.25">
@@ -8142,27 +8305,27 @@
         <v>5</v>
       </c>
       <c r="C62" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
-      <c r="E62">
-        <v>695.31082705381198</v>
+      <c r="E62" s="98">
+        <v>132899.43226001901</v>
       </c>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C63" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
-      <c r="E63">
-        <v>125742.648508129</v>
+      <c r="E63" s="98">
+        <v>15205.108031785499</v>
       </c>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.25">
@@ -8170,13 +8333,13 @@
         <v>6</v>
       </c>
       <c r="C64" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>15671.6166110227</v>
+        <v>9016.6041538972895</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.25">
@@ -8184,27 +8347,27 @@
         <v>6</v>
       </c>
       <c r="C65" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
-      <c r="E65">
-        <v>6221.1757188074698</v>
+      <c r="E65" s="98">
+        <v>5139.4604852474304</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C66" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
-      <c r="E66">
-        <v>4311.9995425217603</v>
+      <c r="E66" s="98">
+        <v>55865.187218413499</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.25">
@@ -8212,13 +8375,13 @@
         <v>7</v>
       </c>
       <c r="C67" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
-      <c r="E67">
-        <v>78772.083834900506</v>
+      <c r="E67" s="98">
+        <v>30708.7356188136</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.25">
@@ -8226,27 +8389,27 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
-      <c r="E68">
-        <v>27241.918511858199</v>
+      <c r="E68" s="98">
+        <v>24740.067184628599</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B69">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
-      <c r="E69">
-        <v>42181.392779463102</v>
+      <c r="E69" s="98">
+        <v>51528.465690210003</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.25">
@@ -8254,13 +8417,13 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
-      <c r="E70">
-        <v>35504.011948286301</v>
+      <c r="E70" s="98">
+        <v>11456.9494060052</v>
       </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.25">
@@ -8268,13 +8431,13 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
-      <c r="E71">
-        <v>13004.1052409407</v>
+      <c r="E71" s="98">
+        <v>13515.481201254101</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.25">
@@ -8293,12 +8456,12 @@
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B74" s="73" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.25">
@@ -8309,7 +8472,7 @@
         <v>39</v>
       </c>
       <c r="D76" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E76" t="s">
         <v>40</v>
@@ -8326,7 +8489,7 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>24572.509531814601</v>
+        <v>18423.688229470201</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.25">
@@ -8340,7 +8503,7 @@
         <v>1</v>
       </c>
       <c r="E78">
-        <v>10567.8171378835</v>
+        <v>12826.636511644099</v>
       </c>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.25">
@@ -8354,7 +8517,7 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>78345.237686593406</v>
+        <v>86859.504460985801</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.25">
@@ -8368,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>51590.246475068998</v>
+        <v>47374.704114529297</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.25">
@@ -8382,7 +8545,7 @@
         <v>1</v>
       </c>
       <c r="E81">
-        <v>35128.913041693697</v>
+        <v>26449.019526849301</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.25">
@@ -8396,7 +8559,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>7904.0955825845804</v>
+        <v>8252.02858894991</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.25">
@@ -8410,7 +8573,7 @@
         <v>1</v>
       </c>
       <c r="E83">
-        <v>3729.8539823606502</v>
+        <v>3211.1715946837398</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.25">
@@ -8424,7 +8587,7 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>19361.463437310002</v>
+        <v>25319.377984163901</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.25">
@@ -8438,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>22021.9988751204</v>
+        <v>31036.9645680748</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.25">
@@ -8452,7 +8615,7 @@
         <v>1</v>
       </c>
       <c r="E86">
-        <v>14139.904320571301</v>
+        <v>14512.6994471867</v>
       </c>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.25">
@@ -8466,7 +8629,7 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>3784.32049145988</v>
+        <v>5823.3363642717104</v>
       </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.25">
@@ -8480,7 +8643,7 @@
         <v>1</v>
       </c>
       <c r="E88">
-        <v>410.16883116312903</v>
+        <v>806.16615826191799</v>
       </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.25">
@@ -8494,7 +8657,7 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>4981.5072238973298</v>
+        <v>5758.0807288944297</v>
       </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.25">
@@ -8508,7 +8671,7 @@
         <v>0</v>
       </c>
       <c r="E90">
-        <v>14997.114855689801</v>
+        <v>24490.3952203263</v>
       </c>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.25">
@@ -8522,7 +8685,7 @@
         <v>1</v>
       </c>
       <c r="E91">
-        <v>607.26275684073801</v>
+        <v>835.26353516384199</v>
       </c>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.25">
@@ -8536,7 +8699,7 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>15155.9965446366</v>
+        <v>13636.966861654601</v>
       </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.25">
@@ -8544,27 +8707,27 @@
         <v>4</v>
       </c>
       <c r="C93" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>8.4144992351064101</v>
+        <v>55224.916452867503</v>
       </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C94" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>41235.721536969701</v>
+        <v>37793.863417332002</v>
       </c>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.25">
@@ -8572,13 +8735,13 @@
         <v>5</v>
       </c>
       <c r="C95" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95">
-        <v>38771.236525945598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.25">
@@ -8586,27 +8749,27 @@
         <v>5</v>
       </c>
       <c r="C96" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>82.232532700959894</v>
+        <v>47731.338847174498</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B97">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C97" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>49094.628872016401</v>
+        <v>5380.9214008935496</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.25">
@@ -8614,13 +8777,13 @@
         <v>6</v>
       </c>
       <c r="C98" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>11804.507433565501</v>
+        <v>9016.6041538972895</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.25">
@@ -8628,27 +8791,27 @@
         <v>6</v>
       </c>
       <c r="C99" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99">
-        <v>6221.1757188074698</v>
+        <v>4811.0820825373603</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B100">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C100" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100">
-        <v>4029.7854833043798</v>
+        <v>30415.8082419948</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.25">
@@ -8656,13 +8819,13 @@
         <v>7</v>
       </c>
       <c r="C101" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>42435.732096531297</v>
+        <v>18855.781344738702</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.25">
@@ -8670,27 +8833,27 @@
         <v>7</v>
       </c>
       <c r="C102" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102">
-        <v>15295.676628589599</v>
+        <v>12297.3767443243</v>
       </c>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B103">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C103" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103">
-        <v>18849.994438874299</v>
+        <v>37590.145706201001</v>
       </c>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.25">
@@ -8698,13 +8861,13 @@
         <v>8</v>
       </c>
       <c r="C104" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104">
-        <v>24697.6817937454</v>
+        <v>7775.3051060549496</v>
       </c>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.25">
@@ -8712,13 +8875,13 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>8106.8120891308899</v>
+        <v>6310.7216117747303</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.25">
@@ -8755,207 +8918,207 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="70" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="76" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="77" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="77" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="77" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="77" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="77" t="s">
-        <v>56</v>
-      </c>
       <c r="F2" s="77" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="78" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B3" s="79">
-        <v>1785</v>
+        <v>1851</v>
       </c>
       <c r="C3" s="79">
-        <v>134910.12735992792</v>
+        <v>175088.79114945314</v>
       </c>
       <c r="D3" s="79">
-        <v>6459</v>
+        <v>6747</v>
       </c>
       <c r="E3" s="79">
-        <v>527121.83669312263</v>
+        <v>618796.47005168837</v>
       </c>
       <c r="F3" s="80">
-        <v>0.25593727667645322</v>
+        <v>0.2829505332097772</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="78" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B4" s="79">
-        <v>700</v>
+        <v>722</v>
       </c>
       <c r="C4" s="79">
-        <v>79795.244272636832</v>
+        <v>102336.28714474203</v>
       </c>
       <c r="D4" s="79">
-        <v>2646</v>
+        <v>2737</v>
       </c>
       <c r="E4" s="79">
-        <v>387912.25847416482</v>
+        <v>485405.39103678789</v>
       </c>
       <c r="F4" s="80">
-        <v>0.20570436362724856</v>
+        <v>0.21082643298658002</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="78" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B5" s="79">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C5" s="79">
-        <v>18150.437019460118</v>
+        <v>16790.042504921126</v>
       </c>
       <c r="D5" s="79">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="E5" s="79">
-        <v>76730.215305508464</v>
+        <v>85116.492319974481</v>
       </c>
       <c r="F5" s="80">
-        <v>0.23654875653863958</v>
+        <v>0.19725956800243952</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="78" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B6" s="79">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C6" s="79">
-        <v>19921.328281283619</v>
+        <v>15931.332811289754</v>
       </c>
       <c r="D6" s="79">
-        <v>491</v>
+        <v>538</v>
       </c>
       <c r="E6" s="79">
-        <v>79381.242976798618</v>
+        <v>67434.573368253274</v>
       </c>
       <c r="F6" s="80">
-        <v>0.25095762593571608</v>
+        <v>0.23624873733967861</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="78" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B7" s="79">
-        <v>2406</v>
+        <v>2554</v>
       </c>
       <c r="C7" s="79">
-        <v>93343.078253586835</v>
+        <v>115512.35358695468</v>
       </c>
       <c r="D7" s="79">
-        <v>8533</v>
+        <v>9156</v>
       </c>
       <c r="E7" s="79">
-        <v>333456.42878065573</v>
+        <v>415924.20833286521</v>
       </c>
       <c r="F7" s="80">
-        <v>0.27992586196317409</v>
+        <v>0.27772452594177888</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="78" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B8" s="79">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C8" s="79">
-        <v>57109.907019570535</v>
+        <v>83868.719042961209</v>
       </c>
       <c r="D8" s="79">
-        <v>1454</v>
+        <v>1534</v>
       </c>
       <c r="E8" s="79">
-        <v>256313.49821076141</v>
+        <v>328653.86091417278</v>
       </c>
       <c r="F8" s="80">
-        <v>0.22281271730999597</v>
+        <v>0.25518860119176673</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="78" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B9" s="79">
-        <v>1296</v>
+        <v>1318</v>
       </c>
       <c r="C9" s="79">
-        <v>177995.29850058709</v>
+        <v>212000.62695556699</v>
       </c>
       <c r="D9" s="79">
-        <v>4791</v>
+        <v>4994</v>
       </c>
       <c r="E9" s="79">
-        <v>718053.7771786314</v>
+        <v>900685.42328621738</v>
       </c>
       <c r="F9" s="80">
-        <v>0.24788574917043701</v>
+        <v>0.23537699342581456</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="78" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B10" s="79">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="C10" s="79">
-        <v>22008.670770182624</v>
+        <v>26498.32226727761</v>
       </c>
       <c r="D10" s="79">
-        <v>1331</v>
+        <v>1417</v>
       </c>
       <c r="E10" s="79">
-        <v>138652.25370367654</v>
+        <v>183680.79294843943</v>
       </c>
       <c r="F10" s="80">
-        <v>0.15873287438384448</v>
+        <v>0.14426289130141054</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="78" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B11" s="79">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C11" s="79">
-        <v>24125.77584795974</v>
+        <v>30862.8913651404</v>
       </c>
       <c r="D11" s="79">
-        <v>807</v>
+        <v>864</v>
       </c>
       <c r="E11" s="79">
-        <v>178246.18190427235</v>
+        <v>217278.70849825043</v>
       </c>
       <c r="F11" s="80">
-        <v>0.13535087029755599</v>
+        <v>0.14204287009276342</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -8963,39 +9126,39 @@
         <v>4</v>
       </c>
       <c r="B12" s="82">
-        <v>7108</v>
+        <v>7417</v>
       </c>
       <c r="C12" s="82">
-        <v>627359.86732520536</v>
+        <v>778889.3668283131</v>
       </c>
       <c r="D12" s="82">
-        <v>26833</v>
+        <v>28338</v>
       </c>
       <c r="E12" s="82">
-        <v>2695867.6932275998</v>
+        <v>3302975.9207566227</v>
       </c>
       <c r="F12" s="83">
-        <v>0.23271166789869618</v>
+        <v>0.23581442478390535</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="84" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="84" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="73" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -9025,19 +9188,19 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
       <c r="F2" s="60"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="50" t="s">
@@ -9306,19 +9469,19 @@
       <c r="F13" s="50"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="96" t="s">
+      <c r="A14" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="96"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
       <c r="F14" s="60"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="94"/>
-      <c r="K14" s="94"/>
-      <c r="L14" s="94"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="50" t="s">
@@ -9580,19 +9743,19 @@
       <c r="A25" s="57"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="94" t="s">
+      <c r="A27" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="94"/>
-      <c r="C27" s="94"/>
-      <c r="D27" s="94"/>
-      <c r="E27" s="94"/>
+      <c r="B27" s="96"/>
+      <c r="C27" s="96"/>
+      <c r="D27" s="96"/>
+      <c r="E27" s="96"/>
       <c r="F27" s="56"/>
-      <c r="H27" s="94"/>
-      <c r="I27" s="94"/>
-      <c r="J27" s="94"/>
-      <c r="K27" s="94"/>
-      <c r="L27" s="94"/>
+      <c r="H27" s="96"/>
+      <c r="I27" s="96"/>
+      <c r="J27" s="96"/>
+      <c r="K27" s="96"/>
+      <c r="L27" s="96"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="46" t="s">
@@ -9622,20 +9785,20 @@
       <c r="A29" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="95">
+      <c r="B29" s="94">
         <v>0.79</v>
       </c>
-      <c r="C29" s="95">
+      <c r="C29" s="94">
         <v>0.12</v>
       </c>
-      <c r="D29" s="95">
+      <c r="D29" s="94">
         <v>0.09</v>
       </c>
-      <c r="E29" s="95">
+      <c r="E29" s="94">
         <f>SUM(B29:D29)</f>
         <v>1</v>
       </c>
-      <c r="F29" s="95">
+      <c r="F29" s="94">
         <v>0.47599999999999998</v>
       </c>
       <c r="I29" s="64"/>
@@ -9647,11 +9810,11 @@
       <c r="A30" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="95"/>
-      <c r="C30" s="95"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="95"/>
+      <c r="B30" s="94"/>
+      <c r="C30" s="94"/>
+      <c r="D30" s="94"/>
+      <c r="E30" s="94"/>
+      <c r="F30" s="94"/>
       <c r="I30" s="64"/>
       <c r="J30" s="64"/>
       <c r="K30" s="64"/>
@@ -9686,20 +9849,20 @@
       <c r="A32" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="95">
-        <v>0</v>
-      </c>
-      <c r="C32" s="95">
+      <c r="B32" s="94">
+        <v>0</v>
+      </c>
+      <c r="C32" s="94">
         <v>0.8</v>
       </c>
-      <c r="D32" s="95">
+      <c r="D32" s="94">
         <v>0.2</v>
       </c>
-      <c r="E32" s="95">
+      <c r="E32" s="94">
         <f>SUM(B32:D32)</f>
         <v>1</v>
       </c>
-      <c r="F32" s="95">
+      <c r="F32" s="94">
         <v>0.22600000000000001</v>
       </c>
       <c r="I32" s="64"/>
@@ -9711,11 +9874,11 @@
       <c r="A33" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="95"/>
-      <c r="C33" s="95"/>
-      <c r="D33" s="95"/>
-      <c r="E33" s="95"/>
-      <c r="F33" s="95"/>
+      <c r="B33" s="94"/>
+      <c r="C33" s="94"/>
+      <c r="D33" s="94"/>
+      <c r="E33" s="94"/>
+      <c r="F33" s="94"/>
       <c r="I33" s="64"/>
       <c r="J33" s="64"/>
       <c r="K33" s="64"/>
@@ -9725,20 +9888,20 @@
       <c r="A34" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="95">
+      <c r="B34" s="94">
         <v>0.65</v>
       </c>
-      <c r="C34" s="95">
+      <c r="C34" s="94">
         <v>0.2</v>
       </c>
-      <c r="D34" s="95">
+      <c r="D34" s="94">
         <v>0.15</v>
       </c>
-      <c r="E34" s="95">
+      <c r="E34" s="94">
         <f>SUM(B34:D34)</f>
         <v>1</v>
       </c>
-      <c r="F34" s="95">
+      <c r="F34" s="94">
         <v>0.246</v>
       </c>
       <c r="I34" s="64"/>
@@ -9750,11 +9913,11 @@
       <c r="A35" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="95"/>
-      <c r="C35" s="95"/>
-      <c r="D35" s="95"/>
-      <c r="E35" s="95"/>
-      <c r="F35" s="95"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="94"/>
+      <c r="D35" s="94"/>
+      <c r="E35" s="94"/>
+      <c r="F35" s="94"/>
       <c r="I35" s="64"/>
       <c r="J35" s="64"/>
       <c r="K35" s="64"/>
@@ -9764,11 +9927,11 @@
       <c r="A36" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="95"/>
-      <c r="C36" s="95"/>
-      <c r="D36" s="95"/>
-      <c r="E36" s="95"/>
-      <c r="F36" s="95"/>
+      <c r="B36" s="94"/>
+      <c r="C36" s="94"/>
+      <c r="D36" s="94"/>
+      <c r="E36" s="94"/>
+      <c r="F36" s="94"/>
       <c r="I36" s="64"/>
       <c r="J36" s="64"/>
       <c r="K36" s="64"/>
@@ -9828,11 +9991,11 @@
       <c r="F40" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="H40" s="94"/>
-      <c r="I40" s="94"/>
-      <c r="J40" s="94"/>
-      <c r="K40" s="94"/>
-      <c r="L40" s="94"/>
+      <c r="H40" s="96"/>
+      <c r="I40" s="96"/>
+      <c r="J40" s="96"/>
+      <c r="K40" s="96"/>
+      <c r="L40" s="96"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="46" t="s">
@@ -10120,11 +10283,11 @@
         <f>E40</f>
         <v>Total</v>
       </c>
-      <c r="H52" s="94"/>
-      <c r="I52" s="94"/>
-      <c r="J52" s="94"/>
-      <c r="K52" s="94"/>
-      <c r="L52" s="94"/>
+      <c r="H52" s="96"/>
+      <c r="I52" s="96"/>
+      <c r="J52" s="96"/>
+      <c r="K52" s="96"/>
+      <c r="L52" s="96"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="50" t="str">
@@ -10382,11 +10545,11 @@
         <f>SUM(E41:E42)/$E$49</f>
         <v>0.47599999999999992</v>
       </c>
-      <c r="H64" s="94"/>
-      <c r="I64" s="94"/>
-      <c r="J64" s="94"/>
-      <c r="K64" s="94"/>
-      <c r="L64" s="94"/>
+      <c r="H64" s="96"/>
+      <c r="I64" s="96"/>
+      <c r="J64" s="96"/>
+      <c r="K64" s="96"/>
+      <c r="L64" s="96"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="48" t="s">
@@ -10524,17 +10687,12 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="H52:L52"/>
+    <mergeCell ref="H64:L64"/>
+    <mergeCell ref="H40:L40"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="F34:F36"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="H27:L27"/>
     <mergeCell ref="F29:F30"/>
@@ -10542,12 +10700,17 @@
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="D32:D33"/>
     <mergeCell ref="E29:E30"/>
-    <mergeCell ref="H52:L52"/>
-    <mergeCell ref="H64:L64"/>
-    <mergeCell ref="H40:L40"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="C34:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/utilities/calibration/workbook_templates/04_CoordinatedDailyActivityPattern_2023_blank.xlsx
+++ b/utilities/calibration/workbook_templates/04_CoordinatedDailyActivityPattern_2023_blank.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\travel-model-one-tm1.7_calibration\utilities\calibration\workbook_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D98C216-63F8-429E-A504-7C491D81ABF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D06DF58-9916-4B5E-A7BD-6A25D6896A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="18" r:id="rId8"/>
+    <pivotCache cacheId="40" r:id="rId8"/>
+    <pivotCache cacheId="41" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -112,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="88">
   <si>
     <t>H</t>
   </si>
@@ -300,9 +301,6 @@
     <t>Sonoma</t>
   </si>
   <si>
-    <t>**Workers are defined as people with a work location</t>
-  </si>
-  <si>
     <t>**WFH Workers are defined as workers who make a WFH Choice (WFH Choice = 1)</t>
   </si>
   <si>
@@ -348,9 +346,6 @@
     <t>N_WFH_1</t>
   </si>
   <si>
-    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20261008_NoMon_rmo/ctramp_2023/BATS_Summaries/dap_summaries.csv</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -360,16 +355,28 @@
     <t>CHTS Values</t>
   </si>
   <si>
-    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20261008_NoMon_rmo/ctramp_2023/BATS_Summaries/BATS2023_person_type_summary_north_bay</t>
-  </si>
-  <si>
-    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20261008_NoMon_rmo/ctramp_2023/BATS_Summaries/BATS2023_person_type_summary_solano_napa</t>
-  </si>
-  <si>
     <t>WFH Share</t>
   </si>
   <si>
-    <t>Source: M:\Development\Travel Model One\Calibration\Version 1.7\2023_BATS_Summaries\pipeline_mt_20261008_NoMon_rmo\2023 BATS WFH Rates.xlsx</t>
+    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20261027/ctramp_2023/BATS_Summaries/dap_summaries.csv</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t>(blank) Total</t>
+  </si>
+  <si>
+    <t>Source: M:\Development\Travel Model One\Calibration\Version 1.7\2023_BATS_Summaries\pipeline_mt_20261027\2023 BATS WFH Rates.xlsx</t>
+  </si>
+  <si>
+    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20261027/ctramp_2023/BATS_Summaries/BATS2023_person_type_summary_north_bay</t>
+  </si>
+  <si>
+    <t>Source: M:/Development/Travel Model One/Calibration/Version 1.7/2023_BATS_Summaries/pipeline_mt_20261027/ctramp_2023/BATS_Summaries/BATS2023_person_type_summary_solano_napa</t>
+  </si>
+  <si>
+    <t>**Workers are defined as person who employment category is Full-Time or Part-Time</t>
   </si>
 </sst>
 </file>
@@ -661,7 +668,7 @@
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -800,17 +807,16 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -820,15 +826,15 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <font>
-        <sz val="10"/>
-      </font>
+      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+      <font>
+        <sz val="10"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -974,13 +980,13 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>1230105.2348854889</c:v>
+                  <c:v>1588701.5018570437</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>286903.59631397587</c:v>
+                  <c:v>319170.30364285648</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>90646.683137778877</c:v>
+                  <c:v>108654.68262759341</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1061,19 +1067,19 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>1343636.9371095512</c:v>
+                  <c:v>1105032.4743517339</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>303270.18710574182</c:v>
+                  <c:v>257636.156587979</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>198575.94101364535</c:v>
+                  <c:v>226287.47546042764</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>485574.30636942881</c:v>
+                  <c:v>572446.56056817796</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>580519.78521612787</c:v>
+                  <c:v>661707.41365374334</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>17712.811699999998</c:v>
@@ -1148,19 +1154,19 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>667739.48886334617</c:v>
+                  <c:v>487610.62722724717</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>114592.55289354955</c:v>
+                  <c:v>95209.139059101493</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>68345.75347247794</c:v>
+                  <c:v>77720.499217960678</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>255989.88428071633</c:v>
+                  <c:v>197443.74470609266</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>365408.67686414684</c:v>
+                  <c:v>292213.42803144874</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>17630.20679</c:v>
@@ -2328,9 +2334,55 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Melody Tsao" refreshedDate="46317.604928472225" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="32" xr:uid="{84CD7BB2-9CA5-4AA6-9C9F-5CF4C2983D11}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Melody Tsao" refreshedDate="46323.496529976852" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="32" xr:uid="{84CD7BB2-9CA5-4AA6-9C9F-5CF4C2983D11}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B2:E34" sheet="BATS 2023"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="person_type" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="8" count="9">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+        <n v="4"/>
+        <n v="5"/>
+        <n v="6"/>
+        <n v="7"/>
+        <n v="8"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="activity_pattern" numFmtId="0">
+      <sharedItems containsBlank="1" count="4">
+        <s v="H"/>
+        <s v="M"/>
+        <s v="N"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="wfh_choice" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1" count="3">
+        <n v="0"/>
+        <n v="1"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="num_pers" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="984.62712796797064" maxValue="1587716.8747290757"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Melody Tsao" refreshedDate="46323.496677314812" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="30" xr:uid="{703D3F0C-B7F8-4B14-AFD0-E3B65935C407}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="B2:E32" sheet="BATS 2023"/>
   </cacheSource>
   <cacheFields count="4">
     <cacheField name="person_type" numFmtId="0">
@@ -2353,13 +2405,10 @@
       </sharedItems>
     </cacheField>
     <cacheField name="wfh_choice" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1" count="2">
-        <n v="0"/>
-        <n v="1"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="num_pers" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="1229608.9493126601"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="984.62712796797064" maxValue="1587716.8747290757"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -2376,203 +2425,388 @@
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="311650.04052777553"/>
+    <n v="136311.22000007168"/>
   </r>
   <r>
     <x v="0"/>
     <x v="0"/>
     <x v="1"/>
-    <n v="356089.44833557063"/>
+    <n v="351299.40722717548"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="1229608.9493126601"/>
+    <n v="1587716.8747290757"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
     <x v="1"/>
-    <n v="496.28557282869974"/>
+    <n v="984.62712796797064"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="663899.41953010834"/>
+    <n v="304252.93481639534"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
     <x v="1"/>
-    <n v="679737.51757944282"/>
+    <n v="800779.53953533864"/>
   </r>
   <r>
     <x v="1"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="83561.221108939819"/>
+    <n v="66930.204190417149"/>
   </r>
   <r>
     <x v="1"/>
     <x v="0"/>
     <x v="1"/>
-    <n v="31031.331784609742"/>
+    <n v="28278.93486868434"/>
   </r>
   <r>
     <x v="1"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="286903.59631397587"/>
+    <n v="319170.30364285648"/>
   </r>
   <r>
     <x v="1"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="230858.03226023554"/>
+    <n v="168031.37265644112"/>
   </r>
   <r>
     <x v="1"/>
     <x v="2"/>
     <x v="1"/>
-    <n v="72412.154845506258"/>
+    <n v="89604.783931537895"/>
   </r>
   <r>
     <x v="2"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="61904.494709690123"/>
+    <n v="71929.739027474046"/>
   </r>
   <r>
     <x v="2"/>
     <x v="0"/>
     <x v="1"/>
-    <n v="6441.2587627878174"/>
+    <n v="5790.7601904866269"/>
   </r>
   <r>
     <x v="2"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="86787.19392694821"/>
+    <n v="102255.23741518278"/>
   </r>
   <r>
     <x v="2"/>
     <x v="1"/>
     <x v="1"/>
-    <n v="3859.4892108306631"/>
+    <n v="6399.4452124106274"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="171454.29096303752"/>
+    <n v="185077.07722946702"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
     <x v="1"/>
-    <n v="27121.650050607841"/>
+    <n v="41210.398230960629"/>
   </r>
   <r>
     <x v="3"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="255989.88428071633"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="0"/>
+    <n v="197443.74470609266"/>
   </r>
   <r>
     <x v="3"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="485574.30636942881"/>
+    <n v="572446.56056817796"/>
   </r>
   <r>
     <x v="4"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="365408.67686414684"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="0"/>
+    <n v="292213.42803144874"/>
   </r>
   <r>
     <x v="4"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="580519.78521612787"/>
+    <n v="661707.41365374334"/>
   </r>
   <r>
     <x v="5"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="74995.978217831318"/>
+    <n v="17630.20679"/>
   </r>
   <r>
     <x v="5"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="27888.048166248853"/>
+    <n v="123094.58867"/>
   </r>
   <r>
     <x v="5"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="59294.409690902619"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="2"/>
-    <x v="1"/>
-    <n v="4891.8330184189444"/>
+    <n v="17712.811699999998"/>
   </r>
   <r>
     <x v="6"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="387248.05504112464"/>
+    <n v="85466.730259999997"/>
   </r>
   <r>
     <x v="6"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="156147.04247572814"/>
+    <n v="665066.56470999995"/>
   </r>
   <r>
     <x v="6"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="169505.952664399"/>
+    <n v="64858.529419999999"/>
   </r>
   <r>
     <x v="7"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="251728.81883796302"/>
+    <n v="121625.49533999999"/>
   </r>
   <r>
     <x v="7"/>
     <x v="1"/>
     <x v="0"/>
-    <n v="60599.900261288341"/>
+    <n v="138048.92214000001"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="145623.69245999999"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="2"/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="30">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="136311.22000007168"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="351299.40722717548"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="0"/>
+    <n v="1587716.8747290757"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="984.62712796797064"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="0"/>
+    <n v="304252.93481639534"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1"/>
+    <n v="800779.53953533864"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="66930.204190417149"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="28278.93486868434"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="0"/>
+    <n v="319170.30364285648"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="0"/>
+    <n v="168031.37265644112"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1"/>
+    <n v="89604.783931537895"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="71929.739027474046"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="5790.7601904866269"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="0"/>
+    <n v="102255.23741518278"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="6399.4452124106274"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="0"/>
+    <n v="185077.07722946702"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="1"/>
+    <n v="41210.398230960629"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="197443.74470609266"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="0"/>
+    <n v="572446.56056817796"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="292213.42803144874"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <n v="0"/>
+    <n v="661707.41365374334"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="17630.20679"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="0"/>
+    <n v="123094.58867"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="2"/>
+    <n v="0"/>
+    <n v="17712.811699999998"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="85466.730259999997"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="0"/>
+    <n v="665066.56470999995"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="2"/>
+    <n v="0"/>
+    <n v="64858.529419999999"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="121625.49533999999"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="0"/>
+    <n v="138048.92214000001"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="2"/>
+    <n v="0"/>
+    <n v="145623.69245999999"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC85B2BF-B5A3-41FF-B478-F9EFC1F3C73E}" name="PivotTable1" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="P4:Z15" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC85B2BF-B5A3-41FF-B478-F9EFC1F3C73E}" name="PivotTable1" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="P4:AB16" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
-      <items count="9">
+      <items count="10">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -2581,6 +2815,16 @@
         <item x="5"/>
         <item x="6"/>
         <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2592,19 +2836,12 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
     <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="9">
+  <rowItems count="10">
     <i>
       <x/>
     </i>
@@ -2629,6 +2866,9 @@
     <i>
       <x v="7"/>
     </i>
+    <i>
+      <x v="8"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -2637,7 +2877,7 @@
     <field x="1"/>
     <field x="2"/>
   </colFields>
-  <colItems count="10">
+  <colItems count="12">
     <i>
       <x/>
       <x/>
@@ -2668,6 +2908,13 @@
     <i t="default">
       <x v="2"/>
     </i>
+    <i>
+      <x v="3"/>
+      <x v="2"/>
+    </i>
+    <i t="default">
+      <x v="3"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -2688,7 +2935,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA3A1326-2495-4C73-860A-CEF4C23C2B41}" name="PivotTable5" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FD0500BC-8277-4543-8FF3-B18D1357F7D3}" name="PivotTable5" cacheId="41" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="I5:M15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -2768,7 +3015,7 @@
     <dataField name="Sum of num_pers" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="0">
+    <format dxfId="2">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
     <format dxfId="1">
@@ -2778,7 +3025,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="0">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -3156,19 +3403,19 @@
       </c>
       <c r="C5" s="9">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A5,'BATS 2023'!$C$3:$C$34,calibration!C$3)</f>
-        <v>1230105.2348854889</v>
+        <v>1588701.5018570437</v>
       </c>
       <c r="D5" s="10">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A5,'BATS 2023'!$C$3:$C$34,calibration!D$3)</f>
-        <v>1343636.9371095512</v>
+        <v>1105032.4743517339</v>
       </c>
       <c r="E5" s="11">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A5,'BATS 2023'!$C$3:$C$34,calibration!E$3)</f>
-        <v>667739.48886334617</v>
+        <v>487610.62722724717</v>
       </c>
       <c r="F5" s="5">
         <f t="shared" ref="F5:F13" si="0">SUM(C5:E5)</f>
-        <v>3241481.6608583862</v>
+        <v>3181344.6034360249</v>
       </c>
       <c r="H5" s="9">
         <f>modeldata!C3</f>
@@ -3188,19 +3435,19 @@
       </c>
       <c r="M5" s="9">
         <f>IFERROR(H5-C5,0)</f>
-        <v>-1230104.2348854889</v>
+        <v>-1588700.5018570437</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" ref="N5:N13" si="1">IFERROR(I5-D5,0)</f>
-        <v>-1343635.9371095512</v>
+        <v>-1105031.4743517339</v>
       </c>
       <c r="O5" s="11">
         <f t="shared" ref="O5:O13" si="2">IFERROR(J5-E5,0)</f>
-        <v>-667738.48886334617</v>
+        <v>-487609.62722724717</v>
       </c>
       <c r="P5" s="5">
         <f t="shared" ref="P5:P13" si="3">IFERROR(K5-F5,0)</f>
-        <v>-3241478.6608583862</v>
+        <v>-3181341.6034360249</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -3212,19 +3459,19 @@
       </c>
       <c r="C6" s="12">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A6,'BATS 2023'!$C$3:$C$34,calibration!C$3)</f>
-        <v>286903.59631397587</v>
+        <v>319170.30364285648</v>
       </c>
       <c r="D6" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A6,'BATS 2023'!$C$3:$C$34,calibration!D$3)</f>
-        <v>303270.18710574182</v>
+        <v>257636.156587979</v>
       </c>
       <c r="E6" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A6,'BATS 2023'!$C$3:$C$34,calibration!E$3)</f>
-        <v>114592.55289354955</v>
+        <v>95209.139059101493</v>
       </c>
       <c r="F6" s="5">
         <f t="shared" si="0"/>
-        <v>704766.33631326724</v>
+        <v>672015.59928993694</v>
       </c>
       <c r="H6" s="12">
         <f>modeldata!C4</f>
@@ -3244,19 +3491,19 @@
       </c>
       <c r="M6" s="12">
         <f t="shared" ref="M6:M13" si="5">IFERROR(H6-C6,0)</f>
-        <v>-286902.59631397587</v>
+        <v>-319169.30364285648</v>
       </c>
       <c r="N6" s="5">
         <f t="shared" si="1"/>
-        <v>-303269.18710574182</v>
+        <v>-257635.156587979</v>
       </c>
       <c r="O6" s="13">
         <f t="shared" si="2"/>
-        <v>-114591.55289354955</v>
+        <v>-95208.139059101493</v>
       </c>
       <c r="P6" s="5">
         <f t="shared" si="3"/>
-        <v>-704763.33631326724</v>
+        <v>-672012.59928993694</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
@@ -3268,19 +3515,19 @@
       </c>
       <c r="C7" s="12">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A7,'BATS 2023'!$C$3:$C$34,calibration!C$3)</f>
-        <v>90646.683137778877</v>
+        <v>108654.68262759341</v>
       </c>
       <c r="D7" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A7,'BATS 2023'!$C$3:$C$34,calibration!D$3)</f>
-        <v>198575.94101364535</v>
+        <v>226287.47546042764</v>
       </c>
       <c r="E7" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A7,'BATS 2023'!$C$3:$C$34,calibration!E$3)</f>
-        <v>68345.75347247794</v>
+        <v>77720.499217960678</v>
       </c>
       <c r="F7" s="5">
         <f t="shared" si="0"/>
-        <v>357568.37762390217</v>
+        <v>412662.65730598173</v>
       </c>
       <c r="H7" s="12">
         <f>modeldata!C5</f>
@@ -3300,19 +3547,19 @@
       </c>
       <c r="M7" s="12">
         <f t="shared" si="5"/>
-        <v>-90645.683137778877</v>
+        <v>-108653.68262759341</v>
       </c>
       <c r="N7" s="5">
         <f t="shared" si="1"/>
-        <v>-198574.94101364535</v>
+        <v>-226286.47546042764</v>
       </c>
       <c r="O7" s="13">
         <f t="shared" si="2"/>
-        <v>-68344.75347247794</v>
+        <v>-77719.499217960678</v>
       </c>
       <c r="P7" s="5">
         <f t="shared" si="3"/>
-        <v>-357565.37762390217</v>
+        <v>-412659.65730598173</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -3328,15 +3575,15 @@
       </c>
       <c r="D8" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A8,'BATS 2023'!$C$3:$C$34,calibration!D$3)</f>
-        <v>485574.30636942881</v>
+        <v>572446.56056817796</v>
       </c>
       <c r="E8" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A8,'BATS 2023'!$C$3:$C$34,calibration!E$3)</f>
-        <v>255989.88428071633</v>
+        <v>197443.74470609266</v>
       </c>
       <c r="F8" s="5">
         <f t="shared" si="0"/>
-        <v>741564.19065014517</v>
+        <v>769890.30527427059</v>
       </c>
       <c r="H8" s="12">
         <f>modeldata!C6</f>
@@ -3360,15 +3607,15 @@
       </c>
       <c r="N8" s="5">
         <f t="shared" si="1"/>
-        <v>-485573.30636942881</v>
+        <v>-572445.56056817796</v>
       </c>
       <c r="O8" s="13">
         <f t="shared" si="2"/>
-        <v>-255988.88428071633</v>
+        <v>-197442.74470609266</v>
       </c>
       <c r="P8" s="5">
         <f t="shared" si="3"/>
-        <v>-741561.19065014517</v>
+        <v>-769887.30527427059</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
@@ -3384,15 +3631,15 @@
       </c>
       <c r="D9" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A9,'BATS 2023'!$C$3:$C$34,calibration!D$3)</f>
-        <v>580519.78521612787</v>
+        <v>661707.41365374334</v>
       </c>
       <c r="E9" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,calibration!$A9,'BATS 2023'!$C$3:$C$34,calibration!E$3)</f>
-        <v>365408.67686414684</v>
+        <v>292213.42803144874</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="0"/>
-        <v>945928.46208027471</v>
+        <v>953920.84168519208</v>
       </c>
       <c r="H9" s="12">
         <f>modeldata!C7</f>
@@ -3416,15 +3663,15 @@
       </c>
       <c r="N9" s="5">
         <f t="shared" si="1"/>
-        <v>-580518.78521612787</v>
+        <v>-661706.41365374334</v>
       </c>
       <c r="O9" s="13">
         <f t="shared" si="2"/>
-        <v>-365407.67686414684</v>
+        <v>-292212.42803144874</v>
       </c>
       <c r="P9" s="5">
         <f t="shared" si="3"/>
-        <v>-945925.46208027471</v>
+        <v>-953917.84168519208</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
@@ -3601,19 +3848,19 @@
       </c>
       <c r="C13" s="5">
         <f>SUM(C5:C12)</f>
-        <v>2533865.5898572435</v>
+        <v>2942736.5636474937</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" ref="D13:E13" si="6">SUM(D5:D12)</f>
-        <v>3139772.1903944951</v>
+        <v>3051305.1142020621</v>
       </c>
       <c r="E13" s="5">
         <f t="shared" si="6"/>
-        <v>1696798.7887642367</v>
+        <v>1374919.8706318506</v>
       </c>
       <c r="F13" s="5">
         <f t="shared" si="0"/>
-        <v>7370436.5690159751</v>
+        <v>7368961.5484814057</v>
       </c>
       <c r="H13" s="5">
         <f>SUM(H5:H12)</f>
@@ -3633,19 +3880,19 @@
       </c>
       <c r="M13" s="5">
         <f t="shared" si="5"/>
-        <v>-2533857.5898572435</v>
+        <v>-2942728.5636474937</v>
       </c>
       <c r="N13" s="5">
         <f t="shared" si="1"/>
-        <v>-3139764.1903944951</v>
+        <v>-3051297.1142020621</v>
       </c>
       <c r="O13" s="5">
         <f t="shared" si="2"/>
-        <v>-1696790.7887642367</v>
+        <v>-1374911.8706318506</v>
       </c>
       <c r="P13" s="5">
         <f t="shared" si="3"/>
-        <v>-7370412.5690159751</v>
+        <v>-7368937.5484814057</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
@@ -3695,15 +3942,15 @@
       </c>
       <c r="C17" s="18">
         <f>C5/$F5</f>
-        <v>0.37948856837269324</v>
+        <v>0.49938051355428764</v>
       </c>
       <c r="D17" s="19">
         <f t="shared" ref="D17:E17" si="8">D5/$F5</f>
-        <v>0.41451320034731859</v>
+        <v>0.34734761935511133</v>
       </c>
       <c r="E17" s="20">
         <f t="shared" si="8"/>
-        <v>0.2059982312799882</v>
+        <v>0.15327186709060101</v>
       </c>
       <c r="F17" s="17">
         <f>F5/$F5</f>
@@ -3727,15 +3974,15 @@
       </c>
       <c r="M17" s="18">
         <f>IFERROR(H17-C17,0)</f>
-        <v>-4.6155235039359921E-2</v>
+        <v>-0.16604718022095433</v>
       </c>
       <c r="N17" s="19">
         <f t="shared" ref="N17:N25" si="10">IFERROR(I17-D17,0)</f>
-        <v>-8.1179867013985274E-2</v>
+        <v>-1.4014286021778011E-2</v>
       </c>
       <c r="O17" s="20">
         <f t="shared" ref="O17:O25" si="11">IFERROR(J17-E17,0)</f>
-        <v>0.12733510205334511</v>
+        <v>0.18006146624273231</v>
       </c>
       <c r="P17" s="17">
         <f t="shared" ref="P17:P25" si="12">IFERROR(K17-F17,0)</f>
@@ -3748,15 +3995,15 @@
       </c>
       <c r="C18" s="21">
         <f t="shared" ref="C18:F18" si="13">C6/$F6</f>
-        <v>0.40709038092654837</v>
+        <v>0.47494478399027823</v>
       </c>
       <c r="D18" s="17">
         <f t="shared" si="13"/>
-        <v>0.43031310021445013</v>
+        <v>0.38337823833286272</v>
       </c>
       <c r="E18" s="22">
         <f t="shared" si="13"/>
-        <v>0.1625965188590015</v>
+        <v>0.14167697767685911</v>
       </c>
       <c r="F18" s="17">
         <f t="shared" si="13"/>
@@ -3780,15 +4027,15 @@
       </c>
       <c r="M18" s="21">
         <f t="shared" ref="M18:M25" si="15">IFERROR(H18-C18,0)</f>
-        <v>-7.3757047593215053E-2</v>
+        <v>-0.14161145065694491</v>
       </c>
       <c r="N18" s="17">
         <f t="shared" si="10"/>
-        <v>-9.6979766881116813E-2</v>
+        <v>-5.0044904999529405E-2</v>
       </c>
       <c r="O18" s="22">
         <f t="shared" si="11"/>
-        <v>0.17073681447433181</v>
+        <v>0.19165635565647421</v>
       </c>
       <c r="P18" s="17">
         <f t="shared" si="12"/>
@@ -3801,15 +4048,15 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:F19" si="16">C7/$F7</f>
-        <v>0.25350866802075805</v>
+        <v>0.26330146598902932</v>
       </c>
       <c r="D19" s="17">
         <f t="shared" si="16"/>
-        <v>0.55535095785934308</v>
+        <v>0.5483594685734785</v>
       </c>
       <c r="E19" s="22">
         <f t="shared" si="16"/>
-        <v>0.19114037411989887</v>
+        <v>0.18833906543749213</v>
       </c>
       <c r="F19" s="17">
         <f t="shared" si="16"/>
@@ -3833,15 +4080,15 @@
       </c>
       <c r="M19" s="21">
         <f t="shared" si="15"/>
-        <v>7.982466531257526E-2</v>
+        <v>7.0031867344304E-2</v>
       </c>
       <c r="N19" s="17">
         <f t="shared" si="10"/>
-        <v>-0.22201762452600976</v>
+        <v>-0.21502613524014519</v>
       </c>
       <c r="O19" s="22">
         <f t="shared" si="11"/>
-        <v>0.14219295921343444</v>
+        <v>0.14499426789584119</v>
       </c>
       <c r="P19" s="17">
         <f t="shared" si="12"/>
@@ -3858,11 +4105,11 @@
       </c>
       <c r="D20" s="17">
         <f t="shared" si="18"/>
-        <v>0.65479740323452706</v>
+        <v>0.7435430172928934</v>
       </c>
       <c r="E20" s="22">
         <f t="shared" si="18"/>
-        <v>0.34520259676547288</v>
+        <v>0.25645698270710665</v>
       </c>
       <c r="F20" s="17">
         <f t="shared" si="18"/>
@@ -3890,11 +4137,11 @@
       </c>
       <c r="N20" s="17">
         <f t="shared" si="10"/>
-        <v>-0.32146406990119375</v>
+        <v>-0.41020968395956009</v>
       </c>
       <c r="O20" s="22">
         <f t="shared" si="11"/>
-        <v>-1.1869263432139565E-2</v>
+        <v>7.6876350626226664E-2</v>
       </c>
       <c r="P20" s="17">
         <f t="shared" si="12"/>
@@ -3911,11 +4158,11 @@
       </c>
       <c r="D21" s="17">
         <f t="shared" si="20"/>
-        <v>0.61370368742204418</v>
+        <v>0.69367119863402305</v>
       </c>
       <c r="E21" s="22">
         <f t="shared" si="20"/>
-        <v>0.38629631257795582</v>
+        <v>0.30632880136597695</v>
       </c>
       <c r="F21" s="17">
         <f t="shared" si="20"/>
@@ -3943,11 +4190,11 @@
       </c>
       <c r="N21" s="17">
         <f t="shared" si="10"/>
-        <v>-0.28037035408871086</v>
+        <v>-0.36033786530068973</v>
       </c>
       <c r="O21" s="22">
         <f t="shared" si="11"/>
-        <v>-5.296297924462251E-2</v>
+        <v>2.700453196735636E-2</v>
       </c>
       <c r="P21" s="17">
         <f t="shared" si="12"/>
@@ -4119,15 +4366,15 @@
       </c>
       <c r="C25" s="17">
         <f t="shared" ref="C25:F25" si="28">C13/$F13</f>
-        <v>0.34378772086706111</v>
+        <v>0.39934209783655777</v>
       </c>
       <c r="D25" s="17">
         <f t="shared" si="28"/>
-        <v>0.42599541573881089</v>
+        <v>0.41407532039991096</v>
       </c>
       <c r="E25" s="17">
         <f t="shared" si="28"/>
-        <v>0.23021686339412806</v>
+        <v>0.18658258176353137</v>
       </c>
       <c r="F25" s="17">
         <f t="shared" si="28"/>
@@ -4151,15 +4398,15 @@
       </c>
       <c r="M25" s="17">
         <f t="shared" si="15"/>
-        <v>-1.0454387533727794E-2</v>
+        <v>-6.600876450322446E-2</v>
       </c>
       <c r="N25" s="17">
         <f t="shared" si="10"/>
-        <v>-9.2662082405477575E-2</v>
+        <v>-8.0741987066577647E-2</v>
       </c>
       <c r="O25" s="17">
         <f t="shared" si="11"/>
-        <v>0.10311646993920526</v>
+        <v>0.14675075156980194</v>
       </c>
       <c r="P25" s="17">
         <f t="shared" si="12"/>
@@ -4485,11 +4732,11 @@
     </row>
     <row r="41" spans="1:24" s="68" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B41" s="69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H41" s="69"/>
       <c r="K41" s="69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M41" s="69"/>
     </row>
@@ -4600,58 +4847,58 @@
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C45" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="E45" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F45" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="G45" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H45" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="H45" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="K45" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L45" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="L45" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="M45" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N45" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="N45" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="O45" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="P45" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="P45" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="S45" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="T45" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="T45" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="U45" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="V45" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="V45" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="W45" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="X45" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="X45" s="7" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.2">
@@ -4663,31 +4910,31 @@
       </c>
       <c r="C46" s="9">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A46,'BATS 2023'!$C$3:$C$34,C$42,'BATS 2023'!$D$3:$D$34,C$43)</f>
-        <v>1229608.9493126601</v>
+        <v>1587716.8747290757</v>
       </c>
       <c r="D46" s="10">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A46,'BATS 2023'!$C$3:$C$34,D$42,'BATS 2023'!$D$3:$D$34,D$43)</f>
-        <v>496.28557282869974</v>
+        <v>984.62712796797064</v>
       </c>
       <c r="E46" s="10">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A46,'BATS 2023'!$C$3:$C$34,E$42,'BATS 2023'!$D$3:$D$34,E$43)</f>
-        <v>663899.41953010834</v>
+        <v>304252.93481639534</v>
       </c>
       <c r="F46" s="10">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A46,'BATS 2023'!$C$3:$C$34,F$42,'BATS 2023'!$D$3:$D$34,F$43)</f>
-        <v>679737.51757944282</v>
+        <v>800779.53953533864</v>
       </c>
       <c r="G46" s="10">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A46,'BATS 2023'!$C$3:$C$34,G$42,'BATS 2023'!$D$3:$D$34,G$43)</f>
-        <v>311650.04052777553</v>
+        <v>136311.22000007168</v>
       </c>
       <c r="H46" s="11">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A46,'BATS 2023'!$C$3:$C$34,H$42,'BATS 2023'!$D$3:$D$34,H$43)</f>
-        <v>356089.44833557063</v>
+        <v>351299.40722717548</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" ref="I46:I54" si="32">SUM(C46:H46)</f>
-        <v>3241481.6608583862</v>
+        <v>3181344.6034360249</v>
       </c>
       <c r="K46" s="9">
         <f>modeldata!D15</f>
@@ -4719,27 +4966,27 @@
       </c>
       <c r="S46" s="9">
         <f>IFERROR(K46-C46,0)</f>
-        <v>-1229607.9493126601</v>
+        <v>-1587715.8747290757</v>
       </c>
       <c r="T46" s="10">
         <f t="shared" ref="T46:X46" si="33">IFERROR(L46-D46,0)</f>
-        <v>-495.28557282869974</v>
+        <v>-983.62712796797064</v>
       </c>
       <c r="U46" s="10">
         <f t="shared" si="33"/>
-        <v>-663898.41953010834</v>
+        <v>-304251.93481639534</v>
       </c>
       <c r="V46" s="10">
         <f t="shared" si="33"/>
-        <v>-679736.51757944282</v>
+        <v>-800778.53953533864</v>
       </c>
       <c r="W46" s="10">
         <f t="shared" si="33"/>
-        <v>-311649.04052777553</v>
+        <v>-136310.22000007168</v>
       </c>
       <c r="X46" s="11">
         <f t="shared" si="33"/>
-        <v>-356088.44833557063</v>
+        <v>-351298.40722717548</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.2">
@@ -4751,7 +4998,7 @@
       </c>
       <c r="C47" s="12">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A47,'BATS 2023'!$C$3:$C$34,C$42,'BATS 2023'!$D$3:$D$34,C$43)</f>
-        <v>286903.59631397587</v>
+        <v>319170.30364285648</v>
       </c>
       <c r="D47" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A47,'BATS 2023'!$C$3:$C$34,D$42,'BATS 2023'!$D$3:$D$34,D$43)</f>
@@ -4759,23 +5006,23 @@
       </c>
       <c r="E47" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A47,'BATS 2023'!$C$3:$C$34,E$42,'BATS 2023'!$D$3:$D$34,E$43)</f>
-        <v>230858.03226023554</v>
+        <v>168031.37265644112</v>
       </c>
       <c r="F47" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A47,'BATS 2023'!$C$3:$C$34,F$42,'BATS 2023'!$D$3:$D$34,F$43)</f>
-        <v>72412.154845506258</v>
+        <v>89604.783931537895</v>
       </c>
       <c r="G47" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A47,'BATS 2023'!$C$3:$C$34,G$42,'BATS 2023'!$D$3:$D$34,G$43)</f>
-        <v>83561.221108939819</v>
+        <v>66930.204190417149</v>
       </c>
       <c r="H47" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A47,'BATS 2023'!$C$3:$C$34,H$42,'BATS 2023'!$D$3:$D$34,H$43)</f>
-        <v>31031.331784609742</v>
+        <v>28278.93486868434</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" si="32"/>
-        <v>704766.33631326724</v>
+        <v>672015.59928993706</v>
       </c>
       <c r="K47" s="12">
         <f>modeldata!D16</f>
@@ -4807,7 +5054,7 @@
       </c>
       <c r="S47" s="12">
         <f t="shared" ref="S47:S53" si="35">IFERROR(K47-C47,0)</f>
-        <v>-286902.59631397587</v>
+        <v>-319169.30364285648</v>
       </c>
       <c r="T47" s="5">
         <f t="shared" ref="T47:T53" si="36">IFERROR(L47-D47,0)</f>
@@ -4815,19 +5062,19 @@
       </c>
       <c r="U47" s="5">
         <f t="shared" ref="U47:U53" si="37">IFERROR(M47-E47,0)</f>
-        <v>-230857.03226023554</v>
+        <v>-168030.37265644112</v>
       </c>
       <c r="V47" s="5">
         <f t="shared" ref="V47:V53" si="38">IFERROR(N47-F47,0)</f>
-        <v>-72411.154845506258</v>
+        <v>-89603.783931537895</v>
       </c>
       <c r="W47" s="5">
         <f t="shared" ref="W47:W53" si="39">IFERROR(O47-G47,0)</f>
-        <v>-83560.221108939819</v>
+        <v>-66929.204190417149</v>
       </c>
       <c r="X47" s="13">
         <f t="shared" ref="X47:X53" si="40">IFERROR(P47-H47,0)</f>
-        <v>-31030.331784609742</v>
+        <v>-28277.93486868434</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.2">
@@ -4839,31 +5086,31 @@
       </c>
       <c r="C48" s="12">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A48,'BATS 2023'!$C$3:$C$34,C$42,'BATS 2023'!$D$3:$D$34,C$43)</f>
-        <v>86787.19392694821</v>
+        <v>102255.23741518278</v>
       </c>
       <c r="D48" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A48,'BATS 2023'!$C$3:$C$34,D$42,'BATS 2023'!$D$3:$D$34,D$43)</f>
-        <v>3859.4892108306631</v>
+        <v>6399.4452124106274</v>
       </c>
       <c r="E48" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A48,'BATS 2023'!$C$3:$C$34,E$42,'BATS 2023'!$D$3:$D$34,E$43)</f>
-        <v>171454.29096303752</v>
+        <v>185077.07722946702</v>
       </c>
       <c r="F48" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A48,'BATS 2023'!$C$3:$C$34,F$42,'BATS 2023'!$D$3:$D$34,F$43)</f>
-        <v>27121.650050607841</v>
+        <v>41210.398230960629</v>
       </c>
       <c r="G48" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A48,'BATS 2023'!$C$3:$C$34,G$42,'BATS 2023'!$D$3:$D$34,G$43)</f>
-        <v>61904.494709690123</v>
+        <v>71929.739027474046</v>
       </c>
       <c r="H48" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A48,'BATS 2023'!$C$3:$C$34,H$42,'BATS 2023'!$D$3:$D$34,H$43)</f>
-        <v>6441.2587627878174</v>
+        <v>5790.7601904866269</v>
       </c>
       <c r="I48" s="5">
         <f t="shared" si="32"/>
-        <v>357568.37762390217</v>
+        <v>412662.65730598179</v>
       </c>
       <c r="K48" s="12">
         <f>modeldata!D17</f>
@@ -4895,27 +5142,27 @@
       </c>
       <c r="S48" s="12">
         <f t="shared" si="35"/>
-        <v>-86786.19392694821</v>
+        <v>-102254.23741518278</v>
       </c>
       <c r="T48" s="5">
         <f t="shared" si="36"/>
-        <v>-3858.4892108306631</v>
+        <v>-6398.4452124106274</v>
       </c>
       <c r="U48" s="5">
         <f t="shared" si="37"/>
-        <v>-171453.29096303752</v>
+        <v>-185076.07722946702</v>
       </c>
       <c r="V48" s="5">
         <f t="shared" si="38"/>
-        <v>-27120.650050607841</v>
+        <v>-41209.398230960629</v>
       </c>
       <c r="W48" s="5">
         <f t="shared" si="39"/>
-        <v>-61903.494709690123</v>
+        <v>-71928.739027474046</v>
       </c>
       <c r="X48" s="13">
         <f t="shared" si="40"/>
-        <v>-6440.2587627878174</v>
+        <v>-5789.7601904866269</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.2">
@@ -4935,7 +5182,7 @@
       </c>
       <c r="E49" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A49,'BATS 2023'!$C$3:$C$34,E$42,'BATS 2023'!$D$3:$D$34,E$43)</f>
-        <v>485574.30636942881</v>
+        <v>572446.56056817796</v>
       </c>
       <c r="F49" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A49,'BATS 2023'!$C$3:$C$34,F$42,'BATS 2023'!$D$3:$D$34,F$43)</f>
@@ -4943,7 +5190,7 @@
       </c>
       <c r="G49" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A49,'BATS 2023'!$C$3:$C$34,G$42,'BATS 2023'!$D$3:$D$34,G$43)</f>
-        <v>255989.88428071633</v>
+        <v>197443.74470609266</v>
       </c>
       <c r="H49" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A49,'BATS 2023'!$C$3:$C$34,H$42,'BATS 2023'!$D$3:$D$34,H$43)</f>
@@ -4951,7 +5198,7 @@
       </c>
       <c r="I49" s="5">
         <f t="shared" si="32"/>
-        <v>741564.19065014517</v>
+        <v>769890.30527427059</v>
       </c>
       <c r="K49" s="12">
         <f>modeldata!D18</f>
@@ -4991,7 +5238,7 @@
       </c>
       <c r="U49" s="5">
         <f t="shared" si="37"/>
-        <v>-485573.30636942881</v>
+        <v>-572445.56056817796</v>
       </c>
       <c r="V49" s="5">
         <f t="shared" si="38"/>
@@ -4999,7 +5246,7 @@
       </c>
       <c r="W49" s="5">
         <f t="shared" si="39"/>
-        <v>-255988.88428071633</v>
+        <v>-197442.74470609266</v>
       </c>
       <c r="X49" s="13">
         <f t="shared" si="40"/>
@@ -5023,7 +5270,7 @@
       </c>
       <c r="E50" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A50,'BATS 2023'!$C$3:$C$34,E$42,'BATS 2023'!$D$3:$D$34,E$43)</f>
-        <v>580519.78521612787</v>
+        <v>661707.41365374334</v>
       </c>
       <c r="F50" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A50,'BATS 2023'!$C$3:$C$34,F$42,'BATS 2023'!$D$3:$D$34,F$43)</f>
@@ -5031,7 +5278,7 @@
       </c>
       <c r="G50" s="5">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A50,'BATS 2023'!$C$3:$C$34,G$42,'BATS 2023'!$D$3:$D$34,G$43)</f>
-        <v>365408.67686414684</v>
+        <v>292213.42803144874</v>
       </c>
       <c r="H50" s="13">
         <f>SUMIFS('BATS 2023'!$E$3:$E$34,'BATS 2023'!$B$3:$B$34,$A50,'BATS 2023'!$C$3:$C$34,H$42,'BATS 2023'!$D$3:$D$34,H$43)</f>
@@ -5039,7 +5286,7 @@
       </c>
       <c r="I50" s="5">
         <f t="shared" si="32"/>
-        <v>945928.46208027471</v>
+        <v>953920.84168519208</v>
       </c>
       <c r="K50" s="12">
         <f>modeldata!D19</f>
@@ -5079,7 +5326,7 @@
       </c>
       <c r="U50" s="5">
         <f t="shared" si="37"/>
-        <v>-580518.78521612787</v>
+        <v>-661706.41365374334</v>
       </c>
       <c r="V50" s="5">
         <f t="shared" si="38"/>
@@ -5087,7 +5334,7 @@
       </c>
       <c r="W50" s="5">
         <f t="shared" si="39"/>
-        <v>-365407.67686414684</v>
+        <v>-292212.42803144874</v>
       </c>
       <c r="X50" s="13">
         <f t="shared" si="40"/>
@@ -5364,31 +5611,31 @@
       </c>
       <c r="C54" s="5">
         <f>SUM(C46:C53)</f>
-        <v>2529509.8150735842</v>
+        <v>2935352.4913071152</v>
       </c>
       <c r="D54" s="5">
         <f t="shared" ref="D54" si="41">SUM(D46:D53)</f>
-        <v>4355.7747836593626</v>
+        <v>7384.0723403785978</v>
       </c>
       <c r="E54" s="5">
         <f t="shared" ref="E54" si="42">SUM(E46:E53)</f>
-        <v>2360500.8679189379</v>
+        <v>2119710.392504225</v>
       </c>
       <c r="F54" s="5">
         <f t="shared" ref="F54" si="43">SUM(F46:F53)</f>
-        <v>779271.32247555698</v>
+        <v>931594.72169783711</v>
       </c>
       <c r="G54" s="5">
         <f t="shared" ref="G54" si="44">SUM(G46:G53)</f>
-        <v>1303236.7498812687</v>
+        <v>989550.76834550418</v>
       </c>
       <c r="H54" s="5">
         <f t="shared" ref="H54" si="45">SUM(H46:H53)</f>
-        <v>393562.03888296819</v>
+        <v>385369.10228634643</v>
       </c>
       <c r="I54" s="5">
         <f t="shared" si="32"/>
-        <v>7370436.5690159751</v>
+        <v>7368961.5484814057</v>
       </c>
       <c r="K54" s="5">
         <f>SUM(K46:K53)</f>
@@ -5416,19 +5663,19 @@
       </c>
       <c r="S54" s="5">
         <f>IFERROR(K54-C54,0)</f>
-        <v>-2529501.8150735842</v>
+        <v>-2935344.4913071152</v>
       </c>
       <c r="T54" s="5">
         <f>IFERROR(L54-D54,0)</f>
-        <v>-4347.7747836593626</v>
+        <v>-7376.0723403785978</v>
       </c>
       <c r="U54" s="5">
         <f>IFERROR(M54-E54,0)</f>
-        <v>-2360492.8679189379</v>
+        <v>-2119702.392504225</v>
       </c>
       <c r="V54" s="5">
         <f>IFERROR(N54-I54,0)</f>
-        <v>-7370428.5690159751</v>
+        <v>-7368953.5484814057</v>
       </c>
       <c r="W54" s="5">
         <f t="shared" ref="W54:X54" si="47">IFERROR(O54-J54,0)</f>
@@ -5506,58 +5753,58 @@
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C58" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="E58" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F58" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F58" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="G58" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H58" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="H58" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="K58" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L58" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="L58" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="M58" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N58" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="N58" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="O58" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="P58" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="P58" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="S58" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="T58" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="T58" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="U58" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="V58" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="V58" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="W58" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="X58" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="X58" s="7" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.2">
@@ -5566,31 +5813,31 @@
       </c>
       <c r="C59" s="18">
         <f t="shared" ref="C59:E67" si="48">C46/$I46</f>
-        <v>0.37933546382830491</v>
+        <v>0.49907101324837783</v>
       </c>
       <c r="D59" s="19">
         <f t="shared" si="48"/>
-        <v>1.5310454438828352E-4</v>
+        <v>3.095003059098093E-4</v>
       </c>
       <c r="E59" s="19">
         <f t="shared" si="48"/>
-        <v>0.20481356644612303</v>
+        <v>9.5636585388387554E-2</v>
       </c>
       <c r="F59" s="19">
         <f t="shared" ref="F59:H59" si="49">F46/$I46</f>
-        <v>0.20969963390119553</v>
+        <v>0.25171103396672379</v>
       </c>
       <c r="G59" s="19">
         <f t="shared" si="49"/>
-        <v>9.6144317054456696E-2</v>
+        <v>4.2847046451003193E-2</v>
       </c>
       <c r="H59" s="20">
         <f t="shared" si="49"/>
-        <v>0.10985391422553152</v>
+        <v>0.11042482063959781</v>
       </c>
       <c r="I59" s="17">
         <f>SUM(C59:H59)</f>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="K59" s="18">
         <f>IFERROR(K46/$Q46,0)</f>
@@ -5622,31 +5869,31 @@
       </c>
       <c r="S59" s="18">
         <f t="shared" ref="S59:S67" si="51">IFERROR(K59-C59,0)</f>
-        <v>-0.21266879716163825</v>
+        <v>-0.33240434658171114</v>
       </c>
       <c r="T59" s="19">
         <f t="shared" ref="T59:T67" si="52">IFERROR(L59-D59,0)</f>
-        <v>0.16651356212227839</v>
+        <v>0.16635716636075684</v>
       </c>
       <c r="U59" s="19">
         <f t="shared" ref="U59:U67" si="53">IFERROR(M59-E59,0)</f>
-        <v>-3.8146899779456372E-2</v>
+        <v>7.1030081278279103E-2</v>
       </c>
       <c r="V59" s="19">
         <f t="shared" ref="V59:X67" si="54">IFERROR(N59-F59,0)</f>
-        <v>-4.3032967234528874E-2</v>
+        <v>-8.5044367300057128E-2</v>
       </c>
       <c r="W59" s="19">
         <f t="shared" si="54"/>
-        <v>7.0522349612209961E-2</v>
+        <v>0.12381962021566346</v>
       </c>
       <c r="X59" s="20">
         <f t="shared" si="54"/>
-        <v>5.6812752441135136E-2</v>
+        <v>5.6241846027068845E-2</v>
       </c>
       <c r="Y59" s="93">
         <f>IFERROR(Q59-I59,0)</f>
-        <v>0</v>
+        <v>-1.1102230246251565E-16</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.2">
@@ -5655,7 +5902,7 @@
       </c>
       <c r="C60" s="21">
         <f t="shared" si="48"/>
-        <v>0.40709038092654837</v>
+        <v>0.47494478399027817</v>
       </c>
       <c r="D60" s="17">
         <f t="shared" si="48"/>
@@ -5663,23 +5910,23 @@
       </c>
       <c r="E60" s="17">
         <f t="shared" si="48"/>
-        <v>0.32756676981464056</v>
+        <v>0.25004088124440249</v>
       </c>
       <c r="F60" s="17">
         <f t="shared" ref="F60:H60" si="55">F47/$I47</f>
-        <v>0.10274633039980956</v>
+        <v>0.13333735708846017</v>
       </c>
       <c r="G60" s="17">
         <f t="shared" si="55"/>
-        <v>0.11856585197593351</v>
+        <v>9.9596206190952594E-2</v>
       </c>
       <c r="H60" s="22">
         <f t="shared" si="55"/>
-        <v>4.4030666883068004E-2</v>
+        <v>4.2080771485906485E-2</v>
       </c>
       <c r="I60" s="17">
         <f t="shared" ref="I60:I66" si="56">SUM(C60:H60)</f>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="K60" s="21">
         <f t="shared" ref="K60:P60" si="57">IFERROR(K47/$Q47,0)</f>
@@ -5711,7 +5958,7 @@
       </c>
       <c r="S60" s="21">
         <f t="shared" si="51"/>
-        <v>-0.24042371425988171</v>
+        <v>-0.30827811732361154</v>
       </c>
       <c r="T60" s="17">
         <f t="shared" si="52"/>
@@ -5719,23 +5966,23 @@
       </c>
       <c r="U60" s="17">
         <f t="shared" si="53"/>
-        <v>-0.1609001031479739</v>
+        <v>-8.3374214577735833E-2</v>
       </c>
       <c r="V60" s="17">
         <f t="shared" si="54"/>
-        <v>6.39203362668571E-2</v>
+        <v>3.3329309578206484E-2</v>
       </c>
       <c r="W60" s="17">
         <f t="shared" si="54"/>
-        <v>4.8100814690733143E-2</v>
+        <v>6.7070460475714064E-2</v>
       </c>
       <c r="X60" s="22">
         <f t="shared" si="54"/>
-        <v>0.12263599978359865</v>
+        <v>0.12458589518076017</v>
       </c>
       <c r="Y60" s="93">
         <f t="shared" ref="Y60:Y66" si="59">IFERROR(Q60-I60,0)</f>
-        <v>-1.1102230246251565E-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.2">
@@ -5744,27 +5991,27 @@
       </c>
       <c r="C61" s="21">
         <f t="shared" si="48"/>
-        <v>0.24271495847497113</v>
+        <v>0.24779377441793188</v>
       </c>
       <c r="D61" s="17">
         <f t="shared" si="48"/>
-        <v>1.0793709545786942E-2</v>
+        <v>1.5507691571097397E-2</v>
       </c>
       <c r="E61" s="17">
         <f t="shared" si="48"/>
-        <v>0.47950071005265654</v>
+        <v>0.4484948515519197</v>
       </c>
       <c r="F61" s="17">
         <f t="shared" ref="F61:H61" si="60">F48/$I48</f>
-        <v>7.5850247806686519E-2</v>
+        <v>9.9864617021558785E-2</v>
       </c>
       <c r="G61" s="17">
         <f t="shared" si="60"/>
-        <v>0.17312631257007452</v>
+        <v>0.17430639228918518</v>
       </c>
       <c r="H61" s="22">
         <f t="shared" si="60"/>
-        <v>1.8014061549824371E-2</v>
+        <v>1.4032673148306909E-2</v>
       </c>
       <c r="I61" s="17">
         <f t="shared" si="56"/>
@@ -5800,27 +6047,27 @@
       </c>
       <c r="S61" s="21">
         <f t="shared" si="51"/>
-        <v>-7.6048291808304469E-2</v>
+        <v>-8.1127107751265221E-2</v>
       </c>
       <c r="T61" s="17">
         <f t="shared" si="52"/>
-        <v>0.15587295712087973</v>
+        <v>0.15115897509556925</v>
       </c>
       <c r="U61" s="17">
         <f t="shared" si="53"/>
-        <v>-0.31283404338598986</v>
+        <v>-0.28182818488525307</v>
       </c>
       <c r="V61" s="17">
         <f t="shared" si="54"/>
-        <v>9.0816418859980139E-2</v>
+        <v>6.6802049645107872E-2</v>
       </c>
       <c r="W61" s="17">
         <f t="shared" si="54"/>
-        <v>-6.4596459034078624E-3</v>
+        <v>-7.6397256225185228E-3</v>
       </c>
       <c r="X61" s="22">
         <f t="shared" si="54"/>
-        <v>0.14865260511684228</v>
+        <v>0.15263399351835974</v>
       </c>
       <c r="Y61" s="93">
         <f t="shared" si="59"/>
@@ -5841,7 +6088,7 @@
       </c>
       <c r="E62" s="17">
         <f t="shared" si="48"/>
-        <v>0.65479740323452706</v>
+        <v>0.7435430172928934</v>
       </c>
       <c r="F62" s="17">
         <f t="shared" ref="F62:H62" si="62">F49/$I49</f>
@@ -5849,7 +6096,7 @@
       </c>
       <c r="G62" s="17">
         <f t="shared" si="62"/>
-        <v>0.34520259676547288</v>
+        <v>0.25645698270710665</v>
       </c>
       <c r="H62" s="22">
         <f t="shared" si="62"/>
@@ -5897,7 +6144,7 @@
       </c>
       <c r="U62" s="17">
         <f t="shared" si="53"/>
-        <v>-0.48813073656786043</v>
+        <v>-0.57687635062622677</v>
       </c>
       <c r="V62" s="17">
         <f t="shared" si="54"/>
@@ -5905,7 +6152,7 @@
       </c>
       <c r="W62" s="17">
         <f t="shared" si="54"/>
-        <v>-0.17853593009880622</v>
+        <v>-8.9790316040439994E-2</v>
       </c>
       <c r="X62" s="22">
         <f t="shared" si="54"/>
@@ -5930,7 +6177,7 @@
       </c>
       <c r="E63" s="17">
         <f t="shared" si="48"/>
-        <v>0.61370368742204418</v>
+        <v>0.69367119863402305</v>
       </c>
       <c r="F63" s="17">
         <f t="shared" ref="F63:H63" si="64">F50/$I50</f>
@@ -5938,7 +6185,7 @@
       </c>
       <c r="G63" s="17">
         <f t="shared" si="64"/>
-        <v>0.38629631257795582</v>
+        <v>0.30632880136597695</v>
       </c>
       <c r="H63" s="22">
         <f t="shared" si="64"/>
@@ -5986,7 +6233,7 @@
       </c>
       <c r="U63" s="17">
         <f t="shared" si="53"/>
-        <v>-0.44703702075537755</v>
+        <v>-0.52700453196735642</v>
       </c>
       <c r="V63" s="17">
         <f t="shared" si="54"/>
@@ -5994,7 +6241,7 @@
       </c>
       <c r="W63" s="17">
         <f t="shared" si="54"/>
-        <v>-0.21962964591128917</v>
+        <v>-0.1396621346993103</v>
       </c>
       <c r="X63" s="22">
         <f t="shared" si="54"/>
@@ -6278,27 +6525,27 @@
       </c>
       <c r="C67" s="17">
         <f t="shared" si="48"/>
-        <v>0.34319674165668834</v>
+        <v>0.39834004723664657</v>
       </c>
       <c r="D67" s="17">
         <f t="shared" si="48"/>
-        <v>5.9097921037273111E-4</v>
+        <v>1.0020505999112327E-3</v>
       </c>
       <c r="E67" s="17">
         <f t="shared" si="48"/>
-        <v>0.32026608543679358</v>
+        <v>0.28765388156232874</v>
       </c>
       <c r="F67" s="17">
         <f>F54/$I54</f>
-        <v>0.10572933030201728</v>
+        <v>0.1264214388375822</v>
       </c>
       <c r="G67" s="17">
         <f>G54/$I54</f>
-        <v>0.17681947842273657</v>
+        <v>0.13428632539810587</v>
       </c>
       <c r="H67" s="17">
         <f>H54/$I54</f>
-        <v>5.3397384971391529E-2</v>
+        <v>5.2296256365425495E-2</v>
       </c>
       <c r="I67" s="17">
         <f>SUM(C67:H67)</f>
@@ -6330,27 +6577,27 @@
       </c>
       <c r="S67" s="17">
         <f t="shared" si="51"/>
-        <v>0.65680325834331166</v>
+        <v>0.60165995276335349</v>
       </c>
       <c r="T67" s="17">
         <f t="shared" si="52"/>
-        <v>0.99940902078962723</v>
+        <v>0.99899794940008879</v>
       </c>
       <c r="U67" s="17">
         <f t="shared" si="53"/>
-        <v>0.67973391456320642</v>
+        <v>0.71234611843767126</v>
       </c>
       <c r="V67" s="17">
         <f t="shared" si="54"/>
-        <v>0.89427066969798275</v>
+        <v>0.87357856116241783</v>
       </c>
       <c r="W67" s="17">
         <f t="shared" si="54"/>
-        <v>0.8231805215772634</v>
+        <v>0.86571367460189408</v>
       </c>
       <c r="X67" s="17">
         <f t="shared" si="54"/>
-        <v>0.94660261502860843</v>
+        <v>0.94770374363457455</v>
       </c>
     </row>
   </sheetData>
@@ -6534,22 +6781,22 @@
         <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s">
         <v>72</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6747,7 +6994,7 @@
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="B1:Z106"/>
+  <dimension ref="B1:AB103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -6758,17 +7005,18 @@
     <col min="15" max="15" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="26" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="25" width="12" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="2:26" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>38</v>
       </c>
@@ -6782,7 +7030,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>1</v>
       </c>
@@ -6793,10 +7041,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>311650.04052777553</v>
-      </c>
-    </row>
-    <row r="4" spans="2:26" x14ac:dyDescent="0.25">
+        <v>136311.22000007168</v>
+      </c>
+    </row>
+    <row r="4" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1</v>
       </c>
@@ -6807,7 +7055,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>356089.44833557063</v>
+        <v>351299.40722717548</v>
       </c>
       <c r="P4" s="74" t="s">
         <v>44</v>
@@ -6816,7 +7064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
@@ -6827,7 +7075,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1229608.9493126601</v>
+        <v>1587716.8747290757</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>44</v>
@@ -6857,10 +7105,16 @@
         <v>47</v>
       </c>
       <c r="Z5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1</v>
       </c>
@@ -6871,7 +7125,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>496.28557282869974</v>
+        <v>984.62712796797064</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>3</v>
@@ -6909,8 +7163,11 @@
       <c r="X6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="Z6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1</v>
       </c>
@@ -6921,7 +7178,7 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>663899.41953010834</v>
+        <v>304252.93481639534</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>6</v>
@@ -6930,52 +7187,52 @@
         <v>1</v>
       </c>
       <c r="J7" s="85">
-        <v>667739.48886334617</v>
+        <v>487610.62722724717</v>
       </c>
       <c r="K7" s="85">
-        <v>1230105.2348854889</v>
+        <v>1588701.5018570437</v>
       </c>
       <c r="L7" s="85">
-        <v>1343636.9371095512</v>
+        <v>1105032.4743517339</v>
       </c>
       <c r="M7" s="85">
-        <v>3241481.6608583862</v>
+        <v>3181344.6034360249</v>
       </c>
       <c r="P7" s="75">
         <v>1</v>
       </c>
-      <c r="Q7" s="97">
-        <v>311650.04052777553</v>
-      </c>
-      <c r="R7" s="97">
-        <v>356089.44833557063</v>
-      </c>
-      <c r="S7" s="97">
-        <v>667739.48886334617</v>
-      </c>
-      <c r="T7" s="97">
-        <v>1229608.9493126601</v>
-      </c>
-      <c r="U7" s="97">
-        <v>496.28557282869974</v>
-      </c>
-      <c r="V7" s="97">
-        <v>1230105.2348854889</v>
-      </c>
-      <c r="W7" s="97">
-        <v>663899.41953010834</v>
-      </c>
-      <c r="X7" s="97">
-        <v>679737.51757944282</v>
-      </c>
-      <c r="Y7" s="97">
-        <v>1343636.9371095512</v>
-      </c>
-      <c r="Z7" s="97">
-        <v>3241481.6608583862</v>
-      </c>
-    </row>
-    <row r="8" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="Q7">
+        <v>136311.22000007168</v>
+      </c>
+      <c r="R7">
+        <v>351299.40722717548</v>
+      </c>
+      <c r="S7">
+        <v>487610.62722724717</v>
+      </c>
+      <c r="T7">
+        <v>1587716.8747290757</v>
+      </c>
+      <c r="U7">
+        <v>984.62712796797064</v>
+      </c>
+      <c r="V7">
+        <v>1588701.5018570437</v>
+      </c>
+      <c r="W7">
+        <v>304252.93481639534</v>
+      </c>
+      <c r="X7">
+        <v>800779.53953533864</v>
+      </c>
+      <c r="Y7">
+        <v>1105032.4743517339</v>
+      </c>
+      <c r="AB7">
+        <v>3181344.6034360249</v>
+      </c>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1</v>
       </c>
@@ -6986,7 +7243,7 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>679737.51757944282</v>
+        <v>800779.53953533864</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>7</v>
@@ -6995,50 +7252,49 @@
         <v>2</v>
       </c>
       <c r="J8" s="85">
-        <v>114592.55289354955</v>
+        <v>95209.139059101493</v>
       </c>
       <c r="K8" s="85">
-        <v>286903.59631397587</v>
+        <v>319170.30364285648</v>
       </c>
       <c r="L8" s="85">
-        <v>303270.18710574182</v>
+        <v>257636.156587979</v>
       </c>
       <c r="M8" s="85">
-        <v>704766.33631326724</v>
+        <v>672015.59928993694</v>
       </c>
       <c r="P8" s="75">
         <v>2</v>
       </c>
-      <c r="Q8" s="97">
-        <v>83561.221108939819</v>
-      </c>
-      <c r="R8" s="97">
-        <v>31031.331784609742</v>
-      </c>
-      <c r="S8" s="97">
-        <v>114592.55289354955</v>
-      </c>
-      <c r="T8" s="97">
-        <v>286903.59631397587</v>
-      </c>
-      <c r="U8" s="97"/>
-      <c r="V8" s="97">
-        <v>286903.59631397587</v>
-      </c>
-      <c r="W8" s="97">
-        <v>230858.03226023554</v>
-      </c>
-      <c r="X8" s="97">
-        <v>72412.154845506258</v>
-      </c>
-      <c r="Y8" s="97">
-        <v>303270.18710574182</v>
-      </c>
-      <c r="Z8" s="97">
-        <v>704766.33631326724</v>
-      </c>
-    </row>
-    <row r="9" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="Q8">
+        <v>66930.204190417149</v>
+      </c>
+      <c r="R8">
+        <v>28278.93486868434</v>
+      </c>
+      <c r="S8">
+        <v>95209.139059101493</v>
+      </c>
+      <c r="T8">
+        <v>319170.30364285648</v>
+      </c>
+      <c r="V8">
+        <v>319170.30364285648</v>
+      </c>
+      <c r="W8">
+        <v>168031.37265644112</v>
+      </c>
+      <c r="X8">
+        <v>89604.783931537895</v>
+      </c>
+      <c r="Y8">
+        <v>257636.156587979</v>
+      </c>
+      <c r="AB8">
+        <v>672015.59928993706</v>
+      </c>
+    </row>
+    <row r="9" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>2</v>
       </c>
@@ -7049,7 +7305,7 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>83561.221108939819</v>
+        <v>66930.204190417149</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>8</v>
@@ -7058,52 +7314,52 @@
         <v>3</v>
       </c>
       <c r="J9" s="85">
-        <v>68345.75347247794</v>
+        <v>77720.499217960678</v>
       </c>
       <c r="K9" s="85">
-        <v>90646.683137778877</v>
+        <v>108654.68262759341</v>
       </c>
       <c r="L9" s="85">
-        <v>198575.94101364535</v>
+        <v>226287.47546042764</v>
       </c>
       <c r="M9" s="85">
-        <v>357568.37762390217</v>
+        <v>412662.65730598173</v>
       </c>
       <c r="P9" s="75">
         <v>3</v>
       </c>
-      <c r="Q9" s="97">
-        <v>61904.494709690123</v>
-      </c>
-      <c r="R9" s="97">
-        <v>6441.2587627878174</v>
-      </c>
-      <c r="S9" s="97">
-        <v>68345.75347247794</v>
-      </c>
-      <c r="T9" s="97">
-        <v>86787.19392694821</v>
-      </c>
-      <c r="U9" s="97">
-        <v>3859.4892108306631</v>
-      </c>
-      <c r="V9" s="97">
-        <v>90646.683137778877</v>
-      </c>
-      <c r="W9" s="97">
-        <v>171454.29096303752</v>
-      </c>
-      <c r="X9" s="97">
-        <v>27121.650050607841</v>
-      </c>
-      <c r="Y9" s="97">
-        <v>198575.94101364535</v>
-      </c>
-      <c r="Z9" s="97">
-        <v>357568.37762390217</v>
-      </c>
-    </row>
-    <row r="10" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="Q9">
+        <v>71929.739027474046</v>
+      </c>
+      <c r="R9">
+        <v>5790.7601904866269</v>
+      </c>
+      <c r="S9">
+        <v>77720.499217960678</v>
+      </c>
+      <c r="T9">
+        <v>102255.23741518278</v>
+      </c>
+      <c r="U9">
+        <v>6399.4452124106274</v>
+      </c>
+      <c r="V9">
+        <v>108654.68262759341</v>
+      </c>
+      <c r="W9">
+        <v>185077.07722946702</v>
+      </c>
+      <c r="X9">
+        <v>41210.398230960629</v>
+      </c>
+      <c r="Y9">
+        <v>226287.47546042764</v>
+      </c>
+      <c r="AB9">
+        <v>412662.65730598173</v>
+      </c>
+    </row>
+    <row r="10" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>2</v>
       </c>
@@ -7114,7 +7370,7 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>31031.331784609742</v>
+        <v>28278.93486868434</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>9</v>
@@ -7123,46 +7379,35 @@
         <v>4</v>
       </c>
       <c r="J10" s="85">
-        <v>255989.88428071633</v>
-      </c>
-      <c r="K10" s="85">
-        <v>0</v>
-      </c>
+        <v>197443.74470609266</v>
+      </c>
+      <c r="K10" s="85"/>
       <c r="L10" s="85">
-        <v>485574.30636942881</v>
+        <v>572446.56056817796</v>
       </c>
       <c r="M10" s="85">
-        <v>741564.19065014517</v>
+        <v>769890.30527427059</v>
       </c>
       <c r="P10" s="75">
         <v>4</v>
       </c>
-      <c r="Q10" s="97">
-        <v>255989.88428071633</v>
-      </c>
-      <c r="R10" s="97"/>
-      <c r="S10" s="97">
-        <v>255989.88428071633</v>
-      </c>
-      <c r="T10" s="97">
-        <v>0</v>
-      </c>
-      <c r="U10" s="97"/>
-      <c r="V10" s="97">
-        <v>0</v>
-      </c>
-      <c r="W10" s="97">
-        <v>485574.30636942881</v>
-      </c>
-      <c r="X10" s="97"/>
-      <c r="Y10" s="97">
-        <v>485574.30636942881</v>
-      </c>
-      <c r="Z10" s="97">
-        <v>741564.19065014517</v>
-      </c>
-    </row>
-    <row r="11" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="Q10">
+        <v>197443.74470609266</v>
+      </c>
+      <c r="S10">
+        <v>197443.74470609266</v>
+      </c>
+      <c r="W10">
+        <v>572446.56056817796</v>
+      </c>
+      <c r="Y10">
+        <v>572446.56056817796</v>
+      </c>
+      <c r="AB10">
+        <v>769890.30527427059</v>
+      </c>
+    </row>
+    <row r="11" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>2</v>
       </c>
@@ -7173,7 +7418,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>286903.59631397587</v>
+        <v>319170.30364285648</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>10</v>
@@ -7182,46 +7427,35 @@
         <v>5</v>
       </c>
       <c r="J11" s="85">
-        <v>365408.67686414684</v>
-      </c>
-      <c r="K11" s="85">
-        <v>0</v>
-      </c>
+        <v>292213.42803144874</v>
+      </c>
+      <c r="K11" s="85"/>
       <c r="L11" s="85">
-        <v>580519.78521612787</v>
+        <v>661707.41365374334</v>
       </c>
       <c r="M11" s="85">
-        <v>945928.46208027471</v>
+        <v>953920.84168519208</v>
       </c>
       <c r="P11" s="75">
         <v>5</v>
       </c>
-      <c r="Q11" s="97">
-        <v>365408.67686414684</v>
-      </c>
-      <c r="R11" s="97"/>
-      <c r="S11" s="97">
-        <v>365408.67686414684</v>
-      </c>
-      <c r="T11" s="97">
-        <v>0</v>
-      </c>
-      <c r="U11" s="97"/>
-      <c r="V11" s="97">
-        <v>0</v>
-      </c>
-      <c r="W11" s="97">
-        <v>580519.78521612787</v>
-      </c>
-      <c r="X11" s="97"/>
-      <c r="Y11" s="97">
-        <v>580519.78521612787</v>
-      </c>
-      <c r="Z11" s="97">
-        <v>945928.46208027471</v>
-      </c>
-    </row>
-    <row r="12" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="Q11">
+        <v>292213.42803144874</v>
+      </c>
+      <c r="S11">
+        <v>292213.42803144874</v>
+      </c>
+      <c r="W11">
+        <v>661707.41365374334</v>
+      </c>
+      <c r="Y11">
+        <v>661707.41365374334</v>
+      </c>
+      <c r="AB11">
+        <v>953920.84168519208</v>
+      </c>
+    </row>
+    <row r="12" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>2</v>
       </c>
@@ -7232,7 +7466,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>230858.03226023554</v>
+        <v>168031.37265644112</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>11</v>
@@ -7241,48 +7475,43 @@
         <v>6</v>
       </c>
       <c r="J12" s="85">
-        <v>74995.978217831318</v>
+        <v>17630.20679</v>
       </c>
       <c r="K12" s="85">
-        <v>27888.048166248853</v>
+        <v>123094.58867</v>
       </c>
       <c r="L12" s="85">
-        <v>64186.242709321567</v>
+        <v>17712.811699999998</v>
       </c>
       <c r="M12" s="85">
-        <v>167070.26909340173</v>
+        <v>158437.60715999999</v>
       </c>
       <c r="P12" s="75">
         <v>6</v>
       </c>
-      <c r="Q12" s="97">
-        <v>74995.978217831318</v>
-      </c>
-      <c r="R12" s="97"/>
-      <c r="S12" s="97">
-        <v>74995.978217831318</v>
-      </c>
-      <c r="T12" s="97">
-        <v>27888.048166248853</v>
-      </c>
-      <c r="U12" s="97"/>
-      <c r="V12" s="97">
-        <v>27888.048166248853</v>
-      </c>
-      <c r="W12" s="97">
-        <v>59294.409690902619</v>
-      </c>
-      <c r="X12" s="97">
-        <v>4891.8330184189444</v>
-      </c>
-      <c r="Y12" s="97">
-        <v>64186.242709321567</v>
-      </c>
-      <c r="Z12" s="97">
-        <v>167070.26909340176</v>
-      </c>
-    </row>
-    <row r="13" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="Q12">
+        <v>17630.20679</v>
+      </c>
+      <c r="S12">
+        <v>17630.20679</v>
+      </c>
+      <c r="T12">
+        <v>123094.58867</v>
+      </c>
+      <c r="V12">
+        <v>123094.58867</v>
+      </c>
+      <c r="W12">
+        <v>17712.811699999998</v>
+      </c>
+      <c r="Y12">
+        <v>17712.811699999998</v>
+      </c>
+      <c r="AB12">
+        <v>158437.60715999999</v>
+      </c>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>2</v>
       </c>
@@ -7293,7 +7522,7 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>72412.154845506258</v>
+        <v>89604.783931537895</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>12</v>
@@ -7302,46 +7531,43 @@
         <v>7</v>
       </c>
       <c r="J13" s="85">
-        <v>387248.05504112464</v>
+        <v>85466.730259999997</v>
       </c>
       <c r="K13" s="85">
-        <v>156147.04247572814</v>
+        <v>665066.56470999995</v>
       </c>
       <c r="L13" s="85">
-        <v>169505.952664399</v>
+        <v>64858.529419999999</v>
       </c>
       <c r="M13" s="85">
-        <v>712901.05018125172</v>
+        <v>815391.82438999997</v>
       </c>
       <c r="P13" s="75">
         <v>7</v>
       </c>
-      <c r="Q13" s="97">
-        <v>387248.05504112464</v>
-      </c>
-      <c r="R13" s="97"/>
-      <c r="S13" s="97">
-        <v>387248.05504112464</v>
-      </c>
-      <c r="T13" s="97">
-        <v>156147.04247572814</v>
-      </c>
-      <c r="U13" s="97"/>
-      <c r="V13" s="97">
-        <v>156147.04247572814</v>
-      </c>
-      <c r="W13" s="97">
-        <v>169505.952664399</v>
-      </c>
-      <c r="X13" s="97"/>
-      <c r="Y13" s="97">
-        <v>169505.952664399</v>
-      </c>
-      <c r="Z13" s="97">
-        <v>712901.05018125172</v>
-      </c>
-    </row>
-    <row r="14" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="Q13">
+        <v>85466.730259999997</v>
+      </c>
+      <c r="S13">
+        <v>85466.730259999997</v>
+      </c>
+      <c r="T13">
+        <v>665066.56470999995</v>
+      </c>
+      <c r="V13">
+        <v>665066.56470999995</v>
+      </c>
+      <c r="W13">
+        <v>64858.529419999999</v>
+      </c>
+      <c r="Y13">
+        <v>64858.529419999999</v>
+      </c>
+      <c r="AB13">
+        <v>815391.82438999997</v>
+      </c>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>3</v>
       </c>
@@ -7352,7 +7578,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>61904.494709690123</v>
+        <v>71929.739027474046</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -7361,40 +7587,43 @@
         <v>8</v>
       </c>
       <c r="J14" s="85">
-        <v>251728.81883796302</v>
+        <v>121625.49533999999</v>
       </c>
       <c r="K14" s="85">
-        <v>60599.900261288341</v>
-      </c>
-      <c r="L14" s="85"/>
+        <v>138048.92214000001</v>
+      </c>
+      <c r="L14" s="85">
+        <v>145623.69245999999</v>
+      </c>
       <c r="M14" s="85">
-        <v>312328.71909925138</v>
+        <v>405298.10993999999</v>
       </c>
       <c r="P14" s="75">
         <v>8</v>
       </c>
-      <c r="Q14" s="97">
-        <v>251728.81883796302</v>
-      </c>
-      <c r="R14" s="97"/>
-      <c r="S14" s="97">
-        <v>251728.81883796302</v>
-      </c>
-      <c r="T14" s="97">
-        <v>60599.900261288341</v>
-      </c>
-      <c r="U14" s="97"/>
-      <c r="V14" s="97">
-        <v>60599.900261288341</v>
-      </c>
-      <c r="W14" s="97"/>
-      <c r="X14" s="97"/>
-      <c r="Y14" s="97"/>
-      <c r="Z14" s="97">
-        <v>312328.71909925138</v>
-      </c>
-    </row>
-    <row r="15" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="Q14">
+        <v>121625.49533999999</v>
+      </c>
+      <c r="S14">
+        <v>121625.49533999999</v>
+      </c>
+      <c r="T14">
+        <v>138048.92214000001</v>
+      </c>
+      <c r="V14">
+        <v>138048.92214000001</v>
+      </c>
+      <c r="W14">
+        <v>145623.69245999999</v>
+      </c>
+      <c r="Y14">
+        <v>145623.69245999999</v>
+      </c>
+      <c r="AB14">
+        <v>405298.10993999999</v>
+      </c>
+    </row>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>3</v>
       </c>
@@ -7405,58 +7634,28 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>6441.2587627878174</v>
+        <v>5790.7601904866269</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>4</v>
       </c>
       <c r="J15" s="85">
-        <v>2186049.2084711557</v>
+        <v>1374919.8706318506</v>
       </c>
       <c r="K15" s="85">
-        <v>1852290.5052405091</v>
+        <v>2942736.5636474937</v>
       </c>
       <c r="L15" s="85">
-        <v>3145269.3521882156</v>
+        <v>3051305.1142020621</v>
       </c>
       <c r="M15" s="85">
-        <v>7183609.0658998815</v>
+        <v>7368961.5484814057</v>
       </c>
       <c r="P15" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="97">
-        <v>1792487.1695881877</v>
-      </c>
-      <c r="R15" s="97">
-        <v>393562.03888296819</v>
-      </c>
-      <c r="S15" s="97">
-        <v>2186049.2084711557</v>
-      </c>
-      <c r="T15" s="97">
-        <v>1847934.7304568496</v>
-      </c>
-      <c r="U15" s="97">
-        <v>4355.7747836593626</v>
-      </c>
-      <c r="V15" s="97">
-        <v>1852290.5052405091</v>
-      </c>
-      <c r="W15" s="97">
-        <v>2361106.1966942395</v>
-      </c>
-      <c r="X15" s="97">
-        <v>784163.15549397597</v>
-      </c>
-      <c r="Y15" s="97">
-        <v>3145269.3521882156</v>
-      </c>
-      <c r="Z15" s="97">
-        <v>7183609.0658998815</v>
-      </c>
-    </row>
-    <row r="16" spans="2:26" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B16" s="72">
         <v>3</v>
       </c>
@@ -7467,7 +7666,40 @@
         <v>0</v>
       </c>
       <c r="E16" s="72">
-        <v>86787.19392694821</v>
+        <v>102255.23741518278</v>
+      </c>
+      <c r="P16" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q16">
+        <v>989550.76834550418</v>
+      </c>
+      <c r="R16">
+        <v>385369.10228634643</v>
+      </c>
+      <c r="S16">
+        <v>1374919.8706318506</v>
+      </c>
+      <c r="T16">
+        <v>2935352.4913071152</v>
+      </c>
+      <c r="U16">
+        <v>7384.0723403785978</v>
+      </c>
+      <c r="V16">
+        <v>2942736.5636474937</v>
+      </c>
+      <c r="W16">
+        <v>2119710.392504225</v>
+      </c>
+      <c r="X16">
+        <v>931594.72169783711</v>
+      </c>
+      <c r="Y16">
+        <v>3051305.1142020621</v>
+      </c>
+      <c r="AB16">
+        <v>7368961.5484814057</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
@@ -7481,7 +7713,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="71">
-        <v>3859.4892108306631</v>
+        <v>6399.4452124106274</v>
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
@@ -7495,7 +7727,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="71">
-        <v>171454.29096303752</v>
+        <v>185077.07722946702</v>
       </c>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
@@ -7509,7 +7741,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="71">
-        <v>27121.650050607841</v>
+        <v>41210.398230960629</v>
       </c>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
@@ -7523,7 +7755,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="71">
-        <v>255989.88428071633</v>
+        <v>197443.74470609266</v>
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.25">
@@ -7531,27 +7763,27 @@
         <v>4</v>
       </c>
       <c r="C21" s="72" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="71">
         <v>0</v>
       </c>
       <c r="E21" s="71">
-        <v>0</v>
+        <v>572446.56056817796</v>
       </c>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" s="72" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22" s="71">
         <v>0</v>
       </c>
       <c r="E22" s="71">
-        <v>485574.30636942881</v>
+        <v>292213.42803144874</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
@@ -7559,53 +7791,103 @@
         <v>5</v>
       </c>
       <c r="C23" s="72" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" s="71">
         <v>0</v>
       </c>
       <c r="E23" s="71">
-        <v>365408.67686414684</v>
+        <v>661707.41365374334</v>
+      </c>
+      <c r="I23" t="s">
+        <v>77</v>
+      </c>
+      <c r="J23" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" t="s">
+        <v>79</v>
+      </c>
+      <c r="P23" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B24" s="72">
-        <v>5</v>
-      </c>
-      <c r="C24" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="71">
-        <v>0</v>
-      </c>
-      <c r="E24" s="71">
-        <v>0</v>
+      <c r="B24" s="2">
+        <v>6</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>17630.20679</v>
+      </c>
+      <c r="I24" s="1">
+        <v>6</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>17630.20679</v>
+      </c>
+      <c r="M24" s="70">
+        <v>6</v>
+      </c>
+      <c r="N24" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2">
+        <v>79476.998163805052</v>
+      </c>
+      <c r="Q24">
+        <f>P24/SUM($P$24:$P$27)</f>
+        <v>0.4387200187566811</v>
       </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B25" s="72">
-        <v>5</v>
-      </c>
-      <c r="C25" s="72" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="71">
-        <v>0</v>
-      </c>
-      <c r="E25" s="72">
-        <v>580519.78521612787</v>
-      </c>
-      <c r="I25" t="s">
-        <v>79</v>
-      </c>
-      <c r="J25" t="s">
-        <v>80</v>
-      </c>
-      <c r="K25" t="s">
-        <v>81</v>
-      </c>
-      <c r="P25" t="s">
-        <v>66</v>
+      <c r="B25" s="2">
+        <v>6</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <v>123094.58867</v>
+      </c>
+      <c r="I25" s="1">
+        <v>6</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="1">
+        <v>123094.58867</v>
+      </c>
+      <c r="M25" s="70">
+        <v>6</v>
+      </c>
+      <c r="N25" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="O25" s="2">
+        <v>0</v>
+      </c>
+      <c r="P25" s="70">
+        <v>47573.543353445326</v>
+      </c>
+      <c r="Q25">
+        <f>P25/SUM($P$24:$P$27)</f>
+        <v>0.26261014274002203</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
@@ -7613,116 +7895,116 @@
         <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="2">
-        <v>17630.20679</v>
+        <v>17712.811699999998</v>
       </c>
       <c r="I26" s="1">
         <v>6</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" s="1">
-        <v>17630.20679</v>
+        <v>17712.811699999998</v>
       </c>
       <c r="M26" s="2">
         <v>6</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O26" s="2">
         <v>0</v>
       </c>
       <c r="P26" s="2">
-        <v>74995.978217831318</v>
+        <v>47942.381665766166</v>
       </c>
       <c r="Q26">
-        <f>P26/SUM($P$26:$P$29)</f>
-        <v>0.44888883357160519</v>
+        <f>P26/SUM($P$24:$P$27)</f>
+        <v>0.26464616265821361</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2">
-        <v>123094.58867</v>
+        <v>85466.730259999997</v>
       </c>
       <c r="I27" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>123094.58867</v>
+        <v>85466.730259999997</v>
       </c>
       <c r="M27" s="2">
         <v>6</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" s="2">
-        <v>27888.048166248853</v>
+        <v>6163.6112031744433</v>
       </c>
       <c r="Q27">
-        <f>P27/SUM($P$26:$P$29)</f>
-        <v>0.16692406325543088</v>
+        <f>P27/SUM($P$24:$P$27)</f>
+        <v>3.402367584508327E-2</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2">
-        <v>17712.811699999998</v>
+        <v>665066.56470999995</v>
       </c>
       <c r="I28" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K28" s="1">
-        <v>17712.811699999998</v>
+        <v>665066.56470999995</v>
       </c>
       <c r="M28" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O28" s="2">
         <v>0</v>
       </c>
       <c r="P28" s="2">
-        <v>59294.409690902619</v>
+        <v>219255.12553260915</v>
       </c>
       <c r="Q28">
-        <f>P28/SUM($P$26:$P$29)</f>
-        <v>0.35490701016201559</v>
+        <f>P28/SUM($P$28:$P$30)</f>
+        <v>0.28930447707863988</v>
       </c>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
@@ -7730,116 +8012,116 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2">
-        <v>85466.730259999997</v>
+        <v>64858.529419999999</v>
       </c>
       <c r="I29" s="1">
         <v>7</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" s="1">
-        <v>85466.730259999997</v>
+        <v>64858.529419999999</v>
       </c>
       <c r="M29" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="2">
-        <v>4891.8330184189444</v>
+        <v>209062.28496210426</v>
       </c>
       <c r="Q29">
-        <f>P29/SUM($P$26:$P$29)</f>
-        <v>2.928009301094818E-2</v>
+        <f>P29/SUM($P$28:$P$30)</f>
+        <v>0.27585514765460645</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B30" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2">
-        <v>665066.56470999995</v>
+        <v>121625.49533999999</v>
       </c>
       <c r="I30" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>665066.56470999995</v>
+        <v>121625.49533999999</v>
       </c>
       <c r="M30" s="2">
         <v>7</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" s="2">
         <v>0</v>
       </c>
       <c r="P30" s="2">
-        <v>387248.05504112464</v>
+        <v>329552.38725822768</v>
       </c>
       <c r="Q30">
-        <f>P30/SUM($P$30:$P$32)</f>
-        <v>0.54320028697204004</v>
+        <f>P30/SUM($P$28:$P$30)</f>
+        <v>0.43484037526675379</v>
       </c>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B31" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2">
-        <v>64858.529419999999</v>
+        <v>138048.92214000001</v>
       </c>
       <c r="I31" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31" s="1">
-        <v>64858.529419999999</v>
+        <v>138048.92214000001</v>
       </c>
       <c r="M31" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="2">
         <v>0</v>
       </c>
       <c r="P31" s="2">
-        <v>156147.04247572814</v>
+        <v>142223.23421915792</v>
       </c>
       <c r="Q31">
-        <f>P31/SUM($P$30:$P$32)</f>
-        <v>0.21903045652132017</v>
+        <f>P31/SUM($P$31:$P$33)</f>
+        <v>0.37290802650444999</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
@@ -7847,149 +8129,87 @@
         <v>8</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2">
-        <v>121625.49533999999</v>
+        <v>145623.69245999999</v>
       </c>
       <c r="I32" s="1">
         <v>8</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" s="1">
-        <v>121625.49533999999</v>
+        <v>145623.69245999999</v>
       </c>
       <c r="M32" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O32" s="2">
         <v>0</v>
       </c>
       <c r="P32" s="2">
-        <v>169505.952664399</v>
+        <v>90316.834178362391</v>
       </c>
       <c r="Q32">
-        <f>P32/SUM($P$30:$P$32)</f>
-        <v>0.23776925650663988</v>
+        <f>P32/SUM($P$31:$P$33)</f>
+        <v>0.23680991772191037</v>
       </c>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B33" s="2">
-        <v>8</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="2">
-        <v>0</v>
-      </c>
-      <c r="E33" s="2">
-        <v>138048.92214000001</v>
-      </c>
-      <c r="I33" s="1">
-        <v>8</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>138048.92214000001</v>
-      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
       <c r="M33" s="2">
         <v>8</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O33" s="2">
         <v>0</v>
       </c>
       <c r="P33" s="2">
-        <v>251728.81883796302</v>
+        <v>148849.50788037386</v>
       </c>
       <c r="Q33">
-        <f>P33/SUM($P$33:$P$35)</f>
-        <v>0.6702113949827051</v>
+        <f>P33/SUM($P$31:$P$33)</f>
+        <v>0.39028205577363956</v>
       </c>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="2">
-        <v>8</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34" s="2">
-        <v>0</v>
-      </c>
-      <c r="E34" s="2">
-        <v>145623.69245999999</v>
-      </c>
-      <c r="I34" s="1">
-        <v>8</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K34" s="1">
-        <v>145623.69245999999</v>
-      </c>
-      <c r="M34" s="2">
-        <v>8</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O34" s="2">
-        <v>0</v>
-      </c>
-      <c r="P34" s="2">
-        <v>60599.900261288341</v>
-      </c>
-      <c r="Q34">
-        <f>P34/SUM($P$33:$P$35)</f>
-        <v>0.16134324181640253</v>
-      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" s="70"/>
       <c r="C35" s="70"/>
       <c r="D35" s="70"/>
       <c r="E35" s="70"/>
-      <c r="M35" s="70">
-        <v>8</v>
-      </c>
-      <c r="N35" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="O35" s="70">
-        <v>0</v>
-      </c>
-      <c r="P35" s="70">
-        <v>63267.429701619018</v>
-      </c>
-      <c r="Q35">
-        <f>P35/SUM($P$33:$P$35)</f>
-        <v>0.16844536320089235</v>
-      </c>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.25">
       <c r="G36" s="70"/>
       <c r="H36" s="70"/>
       <c r="I36" s="70"/>
       <c r="J36" s="70"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B37" s="70" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G37" s="70"/>
       <c r="H37" s="70"/>
@@ -8003,7 +8223,7 @@
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
@@ -8031,7 +8251,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>42440.120223558901</v>
+        <v>15840.4281040845</v>
       </c>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.25">
@@ -8044,8 +8264,8 @@
       <c r="D43">
         <v>1</v>
       </c>
-      <c r="E43" s="98">
-        <v>34949.717585521903</v>
+      <c r="E43">
+        <v>42291.265971363297</v>
       </c>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
@@ -8058,8 +8278,8 @@
       <c r="D44">
         <v>0</v>
       </c>
-      <c r="E44" s="98">
-        <v>189035.97553224201</v>
+      <c r="E44">
+        <v>239109.16080890701</v>
       </c>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.25">
@@ -8072,8 +8292,8 @@
       <c r="D45">
         <v>1</v>
       </c>
-      <c r="E45" s="98">
-        <v>11.895122060386599</v>
+      <c r="E45">
+        <v>29.433608446848101</v>
       </c>
     </row>
     <row r="46" spans="2:17" x14ac:dyDescent="0.25">
@@ -8086,8 +8306,8 @@
       <c r="D46">
         <v>0</v>
       </c>
-      <c r="E46" s="98">
-        <v>127025.50700007399</v>
+      <c r="E46">
+        <v>54382.727881302497</v>
       </c>
     </row>
     <row r="47" spans="2:17" x14ac:dyDescent="0.25">
@@ -8101,7 +8321,7 @@
         <v>1</v>
       </c>
       <c r="E47">
-        <v>73855.196489790207</v>
+        <v>105773.742807145</v>
       </c>
     </row>
     <row r="48" spans="2:17" x14ac:dyDescent="0.25">
@@ -8114,8 +8334,8 @@
       <c r="D48">
         <v>0</v>
       </c>
-      <c r="E48" s="98">
-        <v>18151.648592629001</v>
+      <c r="E48">
+        <v>12872.7590378851</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
@@ -8128,8 +8348,8 @@
       <c r="D49">
         <v>1</v>
       </c>
-      <c r="E49" s="98">
-        <v>6812.8480415026997</v>
+      <c r="E49">
+        <v>4729.3436371940998</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
@@ -8142,8 +8362,8 @@
       <c r="D50">
         <v>0</v>
       </c>
-      <c r="E50" s="98">
-        <v>53435.401330074703</v>
+      <c r="E50">
+        <v>76130.525172190901</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.25">
@@ -8156,8 +8376,8 @@
       <c r="D51">
         <v>0</v>
       </c>
-      <c r="E51" s="98">
-        <v>58618.953143026301</v>
+      <c r="E51">
+        <v>46235.407312189003</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
@@ -8170,8 +8390,8 @@
       <c r="D52">
         <v>1</v>
       </c>
-      <c r="E52" s="98">
-        <v>23297.767900950501</v>
+      <c r="E52">
+        <v>32753.098171755599</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.25">
@@ -8184,8 +8404,8 @@
       <c r="D53">
         <v>0</v>
       </c>
-      <c r="E53" s="98">
-        <v>8720.9887555641799</v>
+      <c r="E53">
+        <v>7834.86206485408</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
@@ -8193,13 +8413,13 @@
         <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54" s="98">
-        <v>806.16615826191799</v>
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>15606.9746375787</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
@@ -8207,13 +8427,13 @@
         <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
-      <c r="E55" s="98">
-        <v>16156.818333618099</v>
+      <c r="E55">
+        <v>34799.615949567502</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
@@ -8224,24 +8444,24 @@
         <v>2</v>
       </c>
       <c r="D56">
-        <v>0</v>
-      </c>
-      <c r="E56" s="98">
-        <v>37665.217608869498</v>
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>2575.3532892364601</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>1</v>
-      </c>
-      <c r="E57" s="98">
-        <v>1273.4484078276701</v>
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>17657.873961773501</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.25">
@@ -8249,27 +8469,27 @@
         <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
-      <c r="E58" s="98">
-        <v>29363.848703914198</v>
+      <c r="E58">
+        <v>94825.753969989106</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C59" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
-      <c r="E59" s="98">
-        <v>97455.557694488802</v>
+      <c r="E59">
+        <v>67915.080254266693</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.25">
@@ -8277,41 +8497,41 @@
         <v>5</v>
       </c>
       <c r="C60" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
-      <c r="E60" s="98">
-        <v>77753.579838162696</v>
+      <c r="E60">
+        <v>152227.03225911799</v>
       </c>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C61" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>15735.791344601799</v>
       </c>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C62" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
-      <c r="E62" s="98">
-        <v>132899.43226001901</v>
+      <c r="E62">
+        <v>9225.1121388998199</v>
       </c>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.25">
@@ -8319,41 +8539,41 @@
         <v>6</v>
       </c>
       <c r="C63" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
-      <c r="E63" s="98">
-        <v>15205.108031785499</v>
+      <c r="E63">
+        <v>6355.30767320838</v>
       </c>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>9016.6041538972895</v>
+        <v>42617.8169504576</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
-      <c r="E65" s="98">
-        <v>5139.4604852474304</v>
+      <c r="E65">
+        <v>33918.475741165399</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.25">
@@ -8361,41 +8581,41 @@
         <v>7</v>
       </c>
       <c r="C66" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
-      <c r="E66" s="98">
-        <v>55865.187218413499</v>
+      <c r="E66">
+        <v>40981.064262153399</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B67">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
-      <c r="E67" s="98">
-        <v>30708.7356188136</v>
+      <c r="E67">
+        <v>20382.0880554668</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B68">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
-      <c r="E68" s="98">
-        <v>24740.067184628599</v>
+      <c r="E68">
+        <v>15043.534577631301</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.25">
@@ -8403,56 +8623,20 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
-      <c r="E69" s="98">
-        <v>51528.465690210003</v>
+      <c r="E69">
+        <v>39984.288925164103</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B70">
-        <v>8</v>
-      </c>
-      <c r="C70" t="s">
-        <v>1</v>
-      </c>
-      <c r="D70">
-        <v>0</v>
-      </c>
-      <c r="E70" s="98">
-        <v>11456.9494060052</v>
-      </c>
+      <c r="E70" s="94"/>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B71">
-        <v>8</v>
-      </c>
-      <c r="C71" t="s">
-        <v>2</v>
-      </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-      <c r="E71" s="98">
-        <v>13515.481201254101</v>
-      </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B72">
-        <v>8</v>
-      </c>
-      <c r="C72" t="s">
-        <v>2</v>
-      </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-      <c r="E72">
-        <v>15265.0597842961</v>
-      </c>
+      <c r="E71" s="94"/>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B74" s="73" t="s">
@@ -8461,7 +8645,7 @@
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.25">
@@ -8489,7 +8673,7 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>18423.688229470201</v>
+        <v>7771.1701771007201</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.25">
@@ -8503,7 +8687,7 @@
         <v>1</v>
       </c>
       <c r="E78">
-        <v>12826.636511644099</v>
+        <v>12133.736545715399</v>
       </c>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.25">
@@ -8517,7 +8701,7 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>86859.504460985801</v>
+        <v>105247.399391086</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.25">
@@ -8531,7 +8715,7 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>47374.704114529297</v>
+        <v>33482.9982159051</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.25">
@@ -8545,7 +8729,7 @@
         <v>1</v>
       </c>
       <c r="E81">
-        <v>26449.019526849301</v>
+        <v>40909.198567273597</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.25">
@@ -8559,7 +8743,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>8252.02858894991</v>
+        <v>5043.2374935630596</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.25">
@@ -8573,7 +8757,7 @@
         <v>1</v>
       </c>
       <c r="E83">
-        <v>3211.1715946837398</v>
+        <v>1917.9792327446801</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.25">
@@ -8587,7 +8771,7 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>25319.377984163901</v>
+        <v>37981.938161258899</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.25">
@@ -8601,7 +8785,7 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>31036.9645680748</v>
+        <v>26519.879369735001</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.25">
@@ -8615,7 +8799,7 @@
         <v>1</v>
       </c>
       <c r="E86">
-        <v>14512.6994471867</v>
+        <v>19152.801571471398</v>
       </c>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.25">
@@ -8629,7 +8813,7 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>5823.3363642717104</v>
+        <v>5375.1442120899201</v>
       </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.25">
@@ -8637,13 +8821,13 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88">
-        <v>806.16615826191799</v>
+        <v>7566.4585628538098</v>
       </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.25">
@@ -8651,13 +8835,13 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>5758.0807288944297</v>
+        <v>14892.168350243201</v>
       </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.25">
@@ -8668,24 +8852,24 @@
         <v>2</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90">
-        <v>24490.3952203263</v>
+        <v>2046.6289687767601</v>
       </c>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B91">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C91" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91">
-        <v>835.26353516384199</v>
+        <v>5078.4237421033304</v>
       </c>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.25">
@@ -8693,27 +8877,27 @@
         <v>4</v>
       </c>
       <c r="C92" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92">
-        <v>13636.966861654601</v>
+        <v>46651.402993393902</v>
       </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B93">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C93" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>55224.916452867503</v>
+        <v>32838.070865366099</v>
       </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.25">
@@ -8721,41 +8905,41 @@
         <v>5</v>
       </c>
       <c r="C94" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>37793.863417332002</v>
+        <v>52044.7970040043</v>
       </c>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B95">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C95" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>4273.7288095000304</v>
       </c>
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B96">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C96" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>47731.338847174498</v>
+        <v>9225.1121388998199</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.25">
@@ -8763,41 +8947,41 @@
         <v>6</v>
       </c>
       <c r="C97" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>5380.9214008935496</v>
+        <v>5902.8537974040501</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B98">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C98" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>9016.6041538972895</v>
+        <v>13932.747583134</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B99">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C99" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99">
-        <v>4811.0820825373603</v>
+        <v>25007.815574345001</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.25">
@@ -8805,41 +8989,41 @@
         <v>7</v>
       </c>
       <c r="C100" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100">
-        <v>30415.8082419948</v>
+        <v>20841.0108796063</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B101">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>18855.781344738702</v>
+        <v>19458.931215990098</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B102">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C102" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102">
-        <v>12297.3767443243</v>
+        <v>10689.9224547064</v>
       </c>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.25">
@@ -8847,55 +9031,13 @@
         <v>8</v>
       </c>
       <c r="C103" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103">
-        <v>37590.145706201001</v>
-      </c>
-    </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B104">
-        <v>8</v>
-      </c>
-      <c r="C104" t="s">
-        <v>1</v>
-      </c>
-      <c r="D104">
-        <v>0</v>
-      </c>
-      <c r="E104">
-        <v>7775.3051060549496</v>
-      </c>
-    </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B105">
-        <v>8</v>
-      </c>
-      <c r="C105" t="s">
-        <v>2</v>
-      </c>
-      <c r="D105">
-        <v>0</v>
-      </c>
-      <c r="E105">
-        <v>6310.7216117747303</v>
-      </c>
-    </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B106">
-        <v>8</v>
-      </c>
-      <c r="C106" t="s">
-        <v>2</v>
-      </c>
-      <c r="D106">
-        <v>0</v>
-      </c>
-      <c r="E106">
-        <v>3369.9224068047401</v>
+        <v>7711.8873396231202</v>
       </c>
     </row>
   </sheetData>
@@ -8918,7 +9060,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="70" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -8938,7 +9080,7 @@
         <v>52</v>
       </c>
       <c r="F2" s="77" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -8946,19 +9088,19 @@
         <v>53</v>
       </c>
       <c r="B3" s="79">
-        <v>1851</v>
+        <v>1360</v>
       </c>
       <c r="C3" s="79">
-        <v>175088.79114945314</v>
+        <v>3432</v>
       </c>
       <c r="D3" s="79">
-        <v>6747</v>
+        <v>304421.99763732235</v>
       </c>
       <c r="E3" s="79">
-        <v>618796.47005168837</v>
+        <v>800915.15494383848</v>
       </c>
       <c r="F3" s="80">
-        <v>0.2829505332097772</v>
+        <v>0.38009269241342869</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -8966,19 +9108,19 @@
         <v>54</v>
       </c>
       <c r="B4" s="79">
-        <v>722</v>
+        <v>578</v>
       </c>
       <c r="C4" s="79">
-        <v>102336.28714474203</v>
+        <v>1457</v>
       </c>
       <c r="D4" s="79">
-        <v>2737</v>
+        <v>173987.35424489487</v>
       </c>
       <c r="E4" s="79">
-        <v>485405.39103678789</v>
+        <v>611033.37948007206</v>
       </c>
       <c r="F4" s="80">
-        <v>0.21082643298658002</v>
+        <v>0.2847427981642181</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -8986,19 +9128,19 @@
         <v>55</v>
       </c>
       <c r="B5" s="79">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C5" s="79">
-        <v>16790.042504921126</v>
+        <v>172</v>
       </c>
       <c r="D5" s="79">
-        <v>351</v>
+        <v>53866.299671725523</v>
       </c>
       <c r="E5" s="79">
-        <v>85116.492319974481</v>
+        <v>119215.37289623305</v>
       </c>
       <c r="F5" s="80">
-        <v>0.19725956800243952</v>
+        <v>0.45184021458886486</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -9006,19 +9148,19 @@
         <v>56</v>
       </c>
       <c r="B6" s="79">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C6" s="79">
-        <v>15931.332811289754</v>
+        <v>301</v>
       </c>
       <c r="D6" s="79">
-        <v>538</v>
+        <v>20733.381152913807</v>
       </c>
       <c r="E6" s="79">
-        <v>67434.573368253274</v>
+        <v>88110.623540651999</v>
       </c>
       <c r="F6" s="80">
-        <v>0.23624873733967861</v>
+        <v>0.23531079817347922</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -9026,19 +9168,19 @@
         <v>57</v>
       </c>
       <c r="B7" s="79">
-        <v>2554</v>
+        <v>1968</v>
       </c>
       <c r="C7" s="79">
-        <v>115512.35358695468</v>
+        <v>4906</v>
       </c>
       <c r="D7" s="79">
-        <v>9156</v>
+        <v>195932.9025997557</v>
       </c>
       <c r="E7" s="79">
-        <v>415924.20833286521</v>
+        <v>516743.65071058011</v>
       </c>
       <c r="F7" s="80">
-        <v>0.27772452594177888</v>
+        <v>0.37916847614929772</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -9046,19 +9188,19 @@
         <v>58</v>
       </c>
       <c r="B8" s="79">
-        <v>377</v>
+        <v>285</v>
       </c>
       <c r="C8" s="79">
-        <v>83868.719042961209</v>
+        <v>776</v>
       </c>
       <c r="D8" s="79">
-        <v>1534</v>
+        <v>128274.17290144144</v>
       </c>
       <c r="E8" s="79">
-        <v>328653.86091417278</v>
+        <v>379469.69085999526</v>
       </c>
       <c r="F8" s="80">
-        <v>0.25518860119176673</v>
+        <v>0.33803535826730297</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -9066,19 +9208,19 @@
         <v>59</v>
       </c>
       <c r="B9" s="79">
-        <v>1318</v>
+        <v>883</v>
       </c>
       <c r="C9" s="79">
-        <v>212000.62695556699</v>
+        <v>2493</v>
       </c>
       <c r="D9" s="79">
-        <v>4994</v>
+        <v>339742.8426591836</v>
       </c>
       <c r="E9" s="79">
-        <v>900685.42328621738</v>
+        <v>1108207.589417631</v>
       </c>
       <c r="F9" s="80">
-        <v>0.23537699342581456</v>
+        <v>0.30656967693004139</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -9086,19 +9228,19 @@
         <v>60</v>
       </c>
       <c r="B10" s="79">
-        <v>283</v>
+        <v>232</v>
       </c>
       <c r="C10" s="79">
-        <v>26498.32226727761</v>
+        <v>742</v>
       </c>
       <c r="D10" s="79">
-        <v>1417</v>
+        <v>55426.963733068318</v>
       </c>
       <c r="E10" s="79">
-        <v>183680.79294843943</v>
+        <v>223746.2027772938</v>
       </c>
       <c r="F10" s="80">
-        <v>0.14426289130141054</v>
+        <v>0.24772247772284012</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -9106,19 +9248,19 @@
         <v>61</v>
       </c>
       <c r="B11" s="79">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="C11" s="79">
-        <v>30862.8913651404</v>
+        <v>506</v>
       </c>
       <c r="D11" s="79">
-        <v>864</v>
+        <v>58125.592927433994</v>
       </c>
       <c r="E11" s="79">
-        <v>217278.70849825043</v>
+        <v>242664.31116634503</v>
       </c>
       <c r="F11" s="80">
-        <v>0.14204287009276342</v>
+        <v>0.23953086734533927</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -9126,39 +9268,39 @@
         <v>4</v>
       </c>
       <c r="B12" s="82">
-        <v>7417</v>
+        <v>5628</v>
       </c>
       <c r="C12" s="82">
-        <v>778889.3668283131</v>
+        <v>14785</v>
       </c>
       <c r="D12" s="82">
-        <v>28338</v>
+        <v>1330511.5075277372</v>
       </c>
       <c r="E12" s="82">
-        <v>3302975.9207566227</v>
+        <v>4090105.9757926245</v>
       </c>
       <c r="F12" s="83">
-        <v>0.23581442478390535</v>
+        <v>0.32530000821553179</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="84" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="84" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="73" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -9188,19 +9330,19 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="95" t="s">
+      <c r="A2" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
       <c r="F2" s="60"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="50" t="s">
@@ -9469,19 +9611,19 @@
       <c r="F13" s="50"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="95" t="s">
+      <c r="A14" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="97"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="97"/>
       <c r="F14" s="60"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="96"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="95"/>
+      <c r="L14" s="95"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="50" t="s">
@@ -9743,19 +9885,19 @@
       <c r="A25" s="57"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="96" t="s">
+      <c r="A27" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="96"/>
-      <c r="C27" s="96"/>
-      <c r="D27" s="96"/>
-      <c r="E27" s="96"/>
+      <c r="B27" s="95"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="95"/>
       <c r="F27" s="56"/>
-      <c r="H27" s="96"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="96"/>
-      <c r="K27" s="96"/>
-      <c r="L27" s="96"/>
+      <c r="H27" s="95"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="95"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="46" t="s">
@@ -9785,20 +9927,20 @@
       <c r="A29" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="94">
+      <c r="B29" s="96">
         <v>0.79</v>
       </c>
-      <c r="C29" s="94">
+      <c r="C29" s="96">
         <v>0.12</v>
       </c>
-      <c r="D29" s="94">
+      <c r="D29" s="96">
         <v>0.09</v>
       </c>
-      <c r="E29" s="94">
+      <c r="E29" s="96">
         <f>SUM(B29:D29)</f>
         <v>1</v>
       </c>
-      <c r="F29" s="94">
+      <c r="F29" s="96">
         <v>0.47599999999999998</v>
       </c>
       <c r="I29" s="64"/>
@@ -9810,11 +9952,11 @@
       <c r="A30" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="94"/>
-      <c r="C30" s="94"/>
-      <c r="D30" s="94"/>
-      <c r="E30" s="94"/>
-      <c r="F30" s="94"/>
+      <c r="B30" s="96"/>
+      <c r="C30" s="96"/>
+      <c r="D30" s="96"/>
+      <c r="E30" s="96"/>
+      <c r="F30" s="96"/>
       <c r="I30" s="64"/>
       <c r="J30" s="64"/>
       <c r="K30" s="64"/>
@@ -9849,20 +9991,20 @@
       <c r="A32" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="94">
-        <v>0</v>
-      </c>
-      <c r="C32" s="94">
+      <c r="B32" s="96">
+        <v>0</v>
+      </c>
+      <c r="C32" s="96">
         <v>0.8</v>
       </c>
-      <c r="D32" s="94">
+      <c r="D32" s="96">
         <v>0.2</v>
       </c>
-      <c r="E32" s="94">
+      <c r="E32" s="96">
         <f>SUM(B32:D32)</f>
         <v>1</v>
       </c>
-      <c r="F32" s="94">
+      <c r="F32" s="96">
         <v>0.22600000000000001</v>
       </c>
       <c r="I32" s="64"/>
@@ -9874,11 +10016,11 @@
       <c r="A33" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="94"/>
-      <c r="C33" s="94"/>
-      <c r="D33" s="94"/>
-      <c r="E33" s="94"/>
-      <c r="F33" s="94"/>
+      <c r="B33" s="96"/>
+      <c r="C33" s="96"/>
+      <c r="D33" s="96"/>
+      <c r="E33" s="96"/>
+      <c r="F33" s="96"/>
       <c r="I33" s="64"/>
       <c r="J33" s="64"/>
       <c r="K33" s="64"/>
@@ -9888,20 +10030,20 @@
       <c r="A34" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="94">
+      <c r="B34" s="96">
         <v>0.65</v>
       </c>
-      <c r="C34" s="94">
+      <c r="C34" s="96">
         <v>0.2</v>
       </c>
-      <c r="D34" s="94">
+      <c r="D34" s="96">
         <v>0.15</v>
       </c>
-      <c r="E34" s="94">
+      <c r="E34" s="96">
         <f>SUM(B34:D34)</f>
         <v>1</v>
       </c>
-      <c r="F34" s="94">
+      <c r="F34" s="96">
         <v>0.246</v>
       </c>
       <c r="I34" s="64"/>
@@ -9913,11 +10055,11 @@
       <c r="A35" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="94"/>
-      <c r="C35" s="94"/>
-      <c r="D35" s="94"/>
-      <c r="E35" s="94"/>
-      <c r="F35" s="94"/>
+      <c r="B35" s="96"/>
+      <c r="C35" s="96"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="96"/>
+      <c r="F35" s="96"/>
       <c r="I35" s="64"/>
       <c r="J35" s="64"/>
       <c r="K35" s="64"/>
@@ -9927,11 +10069,11 @@
       <c r="A36" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="94"/>
-      <c r="C36" s="94"/>
-      <c r="D36" s="94"/>
-      <c r="E36" s="94"/>
-      <c r="F36" s="94"/>
+      <c r="B36" s="96"/>
+      <c r="C36" s="96"/>
+      <c r="D36" s="96"/>
+      <c r="E36" s="96"/>
+      <c r="F36" s="96"/>
       <c r="I36" s="64"/>
       <c r="J36" s="64"/>
       <c r="K36" s="64"/>
@@ -9991,11 +10133,11 @@
       <c r="F40" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="H40" s="96"/>
-      <c r="I40" s="96"/>
-      <c r="J40" s="96"/>
-      <c r="K40" s="96"/>
-      <c r="L40" s="96"/>
+      <c r="H40" s="95"/>
+      <c r="I40" s="95"/>
+      <c r="J40" s="95"/>
+      <c r="K40" s="95"/>
+      <c r="L40" s="95"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="46" t="s">
@@ -10283,11 +10425,11 @@
         <f>E40</f>
         <v>Total</v>
       </c>
-      <c r="H52" s="96"/>
-      <c r="I52" s="96"/>
-      <c r="J52" s="96"/>
-      <c r="K52" s="96"/>
-      <c r="L52" s="96"/>
+      <c r="H52" s="95"/>
+      <c r="I52" s="95"/>
+      <c r="J52" s="95"/>
+      <c r="K52" s="95"/>
+      <c r="L52" s="95"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="50" t="str">
@@ -10545,11 +10687,11 @@
         <f>SUM(E41:E42)/$E$49</f>
         <v>0.47599999999999992</v>
       </c>
-      <c r="H64" s="96"/>
-      <c r="I64" s="96"/>
-      <c r="J64" s="96"/>
-      <c r="K64" s="96"/>
-      <c r="L64" s="96"/>
+      <c r="H64" s="95"/>
+      <c r="I64" s="95"/>
+      <c r="J64" s="95"/>
+      <c r="K64" s="95"/>
+      <c r="L64" s="95"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="48" t="s">
@@ -10687,12 +10829,17 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="H52:L52"/>
-    <mergeCell ref="H64:L64"/>
-    <mergeCell ref="H40:L40"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="A27:E27"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="H27:L27"/>
     <mergeCell ref="F29:F30"/>
@@ -10700,17 +10847,12 @@
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="D32:D33"/>
     <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="H52:L52"/>
+    <mergeCell ref="H64:L64"/>
+    <mergeCell ref="H40:L40"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="F34:F36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/utilities/calibration/workbook_templates/04_CoordinatedDailyActivityPattern_2023_blank.xlsx
+++ b/utilities/calibration/workbook_templates/04_CoordinatedDailyActivityPattern_2023_blank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\travel-model-one-tm1.7_calibration\utilities\calibration\workbook_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D06DF58-9916-4B5E-A7BD-6A25D6896A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1330CBA-E079-4F3E-9BDD-2031FF7E0A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration" sheetId="1" r:id="rId1"/>
@@ -32,8 +32,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="40" r:id="rId8"/>
-    <pivotCache cacheId="41" r:id="rId9"/>
+    <pivotCache cacheId="66" r:id="rId8"/>
+    <pivotCache cacheId="67" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -808,13 +808,13 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2802,7 +2802,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC85B2BF-B5A3-41FF-B478-F9EFC1F3C73E}" name="PivotTable1" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC85B2BF-B5A3-41FF-B478-F9EFC1F3C73E}" name="PivotTable1" cacheId="66" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="P4:AB16" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -2935,7 +2935,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FD0500BC-8277-4543-8FF3-B18D1357F7D3}" name="PivotTable5" cacheId="41" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FD0500BC-8277-4543-8FF3-B18D1357F7D3}" name="PivotTable5" cacheId="67" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="I5:M15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -5661,6 +5661,10 @@
         <f t="shared" si="46"/>
         <v>8</v>
       </c>
+      <c r="Q54" s="5">
+        <f>SUM(Q46:Q53)</f>
+        <v>48</v>
+      </c>
       <c r="S54" s="5">
         <f>IFERROR(K54-C54,0)</f>
         <v>-2935344.4913071152</v>
@@ -6552,52 +6556,52 @@
         <v>1</v>
       </c>
       <c r="K67" s="17">
-        <f>IFERROR(K54/$N54,0)</f>
-        <v>1</v>
+        <f>IFERROR(K54/$Q54,0)</f>
+        <v>0.16666666666666666</v>
       </c>
       <c r="L67" s="17">
-        <f>IFERROR(L54/$N54,0)</f>
-        <v>1</v>
+        <f t="shared" ref="L67:P67" si="72">IFERROR(L54/$Q54,0)</f>
+        <v>0.16666666666666666</v>
       </c>
       <c r="M67" s="17">
-        <f>IFERROR(M54/$N54,0)</f>
-        <v>1</v>
+        <f t="shared" si="72"/>
+        <v>0.16666666666666666</v>
       </c>
       <c r="N67" s="17">
-        <f>IFERROR(N54/$N54,0)</f>
-        <v>1</v>
+        <f t="shared" si="72"/>
+        <v>0.16666666666666666</v>
       </c>
       <c r="O67" s="17">
-        <f t="shared" ref="O67:P67" si="72">IFERROR(O54/$N54,0)</f>
-        <v>1</v>
+        <f t="shared" si="72"/>
+        <v>0.16666666666666666</v>
       </c>
       <c r="P67" s="17">
         <f t="shared" si="72"/>
-        <v>1</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="S67" s="17">
         <f t="shared" si="51"/>
-        <v>0.60165995276335349</v>
+        <v>-0.23167338056997991</v>
       </c>
       <c r="T67" s="17">
         <f t="shared" si="52"/>
-        <v>0.99899794940008879</v>
+        <v>0.16566461606675542</v>
       </c>
       <c r="U67" s="17">
         <f t="shared" si="53"/>
-        <v>0.71234611843767126</v>
+        <v>-0.12098721489566208</v>
       </c>
       <c r="V67" s="17">
         <f t="shared" si="54"/>
-        <v>0.87357856116241783</v>
+        <v>4.0245227829084462E-2</v>
       </c>
       <c r="W67" s="17">
         <f t="shared" si="54"/>
-        <v>0.86571367460189408</v>
+        <v>3.2380341268560792E-2</v>
       </c>
       <c r="X67" s="17">
         <f t="shared" si="54"/>
-        <v>0.94770374363457455</v>
+        <v>0.11437041030124116</v>
       </c>
     </row>
   </sheetData>
@@ -9330,19 +9334,19 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
       <c r="F2" s="60"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="50" t="s">
@@ -9611,19 +9615,19 @@
       <c r="F13" s="50"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="97" t="s">
+      <c r="A14" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="97"/>
-      <c r="C14" s="97"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="97"/>
+      <c r="B14" s="96"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="96"/>
       <c r="F14" s="60"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="95"/>
-      <c r="K14" s="95"/>
-      <c r="L14" s="95"/>
+      <c r="H14" s="97"/>
+      <c r="I14" s="97"/>
+      <c r="J14" s="97"/>
+      <c r="K14" s="97"/>
+      <c r="L14" s="97"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="50" t="s">
@@ -9885,19 +9889,19 @@
       <c r="A25" s="57"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="95" t="s">
+      <c r="A27" s="97" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="95"/>
-      <c r="C27" s="95"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="95"/>
+      <c r="B27" s="97"/>
+      <c r="C27" s="97"/>
+      <c r="D27" s="97"/>
+      <c r="E27" s="97"/>
       <c r="F27" s="56"/>
-      <c r="H27" s="95"/>
-      <c r="I27" s="95"/>
-      <c r="J27" s="95"/>
-      <c r="K27" s="95"/>
-      <c r="L27" s="95"/>
+      <c r="H27" s="97"/>
+      <c r="I27" s="97"/>
+      <c r="J27" s="97"/>
+      <c r="K27" s="97"/>
+      <c r="L27" s="97"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="46" t="s">
@@ -9927,20 +9931,20 @@
       <c r="A29" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="96">
+      <c r="B29" s="95">
         <v>0.79</v>
       </c>
-      <c r="C29" s="96">
+      <c r="C29" s="95">
         <v>0.12</v>
       </c>
-      <c r="D29" s="96">
+      <c r="D29" s="95">
         <v>0.09</v>
       </c>
-      <c r="E29" s="96">
+      <c r="E29" s="95">
         <f>SUM(B29:D29)</f>
         <v>1</v>
       </c>
-      <c r="F29" s="96">
+      <c r="F29" s="95">
         <v>0.47599999999999998</v>
       </c>
       <c r="I29" s="64"/>
@@ -9952,11 +9956,11 @@
       <c r="A30" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="96"/>
-      <c r="C30" s="96"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="96"/>
+      <c r="B30" s="95"/>
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="95"/>
       <c r="I30" s="64"/>
       <c r="J30" s="64"/>
       <c r="K30" s="64"/>
@@ -9991,20 +9995,20 @@
       <c r="A32" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="96">
-        <v>0</v>
-      </c>
-      <c r="C32" s="96">
+      <c r="B32" s="95">
+        <v>0</v>
+      </c>
+      <c r="C32" s="95">
         <v>0.8</v>
       </c>
-      <c r="D32" s="96">
+      <c r="D32" s="95">
         <v>0.2</v>
       </c>
-      <c r="E32" s="96">
+      <c r="E32" s="95">
         <f>SUM(B32:D32)</f>
         <v>1</v>
       </c>
-      <c r="F32" s="96">
+      <c r="F32" s="95">
         <v>0.22600000000000001</v>
       </c>
       <c r="I32" s="64"/>
@@ -10016,11 +10020,11 @@
       <c r="A33" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="96"/>
-      <c r="C33" s="96"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="96"/>
-      <c r="F33" s="96"/>
+      <c r="B33" s="95"/>
+      <c r="C33" s="95"/>
+      <c r="D33" s="95"/>
+      <c r="E33" s="95"/>
+      <c r="F33" s="95"/>
       <c r="I33" s="64"/>
       <c r="J33" s="64"/>
       <c r="K33" s="64"/>
@@ -10030,20 +10034,20 @@
       <c r="A34" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="96">
+      <c r="B34" s="95">
         <v>0.65</v>
       </c>
-      <c r="C34" s="96">
+      <c r="C34" s="95">
         <v>0.2</v>
       </c>
-      <c r="D34" s="96">
+      <c r="D34" s="95">
         <v>0.15</v>
       </c>
-      <c r="E34" s="96">
+      <c r="E34" s="95">
         <f>SUM(B34:D34)</f>
         <v>1</v>
       </c>
-      <c r="F34" s="96">
+      <c r="F34" s="95">
         <v>0.246</v>
       </c>
       <c r="I34" s="64"/>
@@ -10055,11 +10059,11 @@
       <c r="A35" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="96"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="96"/>
-      <c r="F35" s="96"/>
+      <c r="B35" s="95"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="95"/>
+      <c r="E35" s="95"/>
+      <c r="F35" s="95"/>
       <c r="I35" s="64"/>
       <c r="J35" s="64"/>
       <c r="K35" s="64"/>
@@ -10069,11 +10073,11 @@
       <c r="A36" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="96"/>
-      <c r="C36" s="96"/>
-      <c r="D36" s="96"/>
-      <c r="E36" s="96"/>
-      <c r="F36" s="96"/>
+      <c r="B36" s="95"/>
+      <c r="C36" s="95"/>
+      <c r="D36" s="95"/>
+      <c r="E36" s="95"/>
+      <c r="F36" s="95"/>
       <c r="I36" s="64"/>
       <c r="J36" s="64"/>
       <c r="K36" s="64"/>
@@ -10133,11 +10137,11 @@
       <c r="F40" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="H40" s="95"/>
-      <c r="I40" s="95"/>
-      <c r="J40" s="95"/>
-      <c r="K40" s="95"/>
-      <c r="L40" s="95"/>
+      <c r="H40" s="97"/>
+      <c r="I40" s="97"/>
+      <c r="J40" s="97"/>
+      <c r="K40" s="97"/>
+      <c r="L40" s="97"/>
     </row>
     <row r="41" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="46" t="s">
@@ -10425,11 +10429,11 @@
         <f>E40</f>
         <v>Total</v>
       </c>
-      <c r="H52" s="95"/>
-      <c r="I52" s="95"/>
-      <c r="J52" s="95"/>
-      <c r="K52" s="95"/>
-      <c r="L52" s="95"/>
+      <c r="H52" s="97"/>
+      <c r="I52" s="97"/>
+      <c r="J52" s="97"/>
+      <c r="K52" s="97"/>
+      <c r="L52" s="97"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="50" t="str">
@@ -10687,11 +10691,11 @@
         <f>SUM(E41:E42)/$E$49</f>
         <v>0.47599999999999992</v>
       </c>
-      <c r="H64" s="95"/>
-      <c r="I64" s="95"/>
-      <c r="J64" s="95"/>
-      <c r="K64" s="95"/>
-      <c r="L64" s="95"/>
+      <c r="H64" s="97"/>
+      <c r="I64" s="97"/>
+      <c r="J64" s="97"/>
+      <c r="K64" s="97"/>
+      <c r="L64" s="97"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="48" t="s">
@@ -10829,17 +10833,12 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="H52:L52"/>
+    <mergeCell ref="H64:L64"/>
+    <mergeCell ref="H40:L40"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="F34:F36"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="H27:L27"/>
     <mergeCell ref="F29:F30"/>
@@ -10847,12 +10846,17 @@
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="D32:D33"/>
     <mergeCell ref="E29:E30"/>
-    <mergeCell ref="H52:L52"/>
-    <mergeCell ref="H64:L64"/>
-    <mergeCell ref="H40:L40"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="C34:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
